--- a/app/templates/Template_GE_GRUESO.xlsx
+++ b/app/templates/Template_GE_GRUESO.xlsx
@@ -13709,7 +13709,6 @@
       <c r="R93" s="89"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="i/kUJ6VfpXKJuiSP0WJSGBrMWCozhWShZyGCHU+hpPItkPU6KvbPe+ubzWKF2Vs79yRk3xi1/2TQ6U184HSf2Q==" saltValue="swsyvAPqiyXdkmhH+B/H+g==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="6">
     <mergeCell ref="L68:M68"/>
     <mergeCell ref="L79:M79"/>

--- a/app/templates/Template_GE_GRUESO.xlsx
+++ b/app/templates/Template_GE_GRUESO.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24332"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27928"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Mi unidad\3.0 Formatos e informes\2026\1.0 Informe de ensayo\1.2 Informe agregados\INFORME ACREDITADO-E ISO\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo\Documents\crmnew\api-geofal-crm\app\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1E58996-AA76-4370-9E40-7747ACC107D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89D688AF-C396-4282-9C66-1488F868A017}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="723" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -100,7 +100,7 @@
     <definedName name="W" localSheetId="3">#REF!</definedName>
     <definedName name="W">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" calcMode="auto" fullCalcOnLoad="1" forceFullCalc="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -141,7 +141,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="514" uniqueCount="238">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="520" uniqueCount="244">
   <si>
     <t>LABORATORIO DE ENSAYO DE MATERIALES</t>
   </si>
@@ -1180,6 +1180,80 @@
   <si>
     <t>SI [ ]                NO [ ]</t>
   </si>
+  <si>
+    <t>REVISADO POR:</t>
+  </si>
+  <si>
+    <t>FABIAN LA ROSA</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>APROBADO POR</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>:</t>
+    </r>
+  </si>
+  <si>
+    <t>IRMA COAQUIRA</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>FECHA DE REVISIÓN</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>:</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>FECHA DE APROBACIÓN</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>:</t>
+    </r>
+  </si>
 </sst>
 </file>
 
@@ -1204,7 +1278,7 @@
     <numFmt numFmtId="179" formatCode="000&quot;-AG-26&quot;"/>
     <numFmt numFmtId="180" formatCode="&quot;FORMATO F-LEM-P-SU-11.01&quot;"/>
   </numFmts>
-  <fonts count="51" x14ac:knownFonts="1">
+  <fonts count="53" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -1452,13 +1526,6 @@
     </font>
     <font>
       <b/>
-      <sz val="14"/>
-      <color rgb="FFFF0000"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
       <vertAlign val="superscript"/>
       <sz val="11"/>
       <name val="Arial"/>
@@ -1518,6 +1585,26 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <u/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <color theme="0"/>
     </font>
   </fonts>
   <fills count="7">
@@ -2148,12 +2235,12 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="49" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="top"/>
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="550">
+  <cellXfs count="563">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="3" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="10" xfId="3" applyFill="1" applyBorder="1"/>
@@ -3081,7 +3168,6 @@
       <alignment horizontal="center" vertical="center"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="40" fillId="2" borderId="0" xfId="3" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -3220,7 +3306,7 @@
     <xf numFmtId="0" fontId="10" fillId="6" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="1" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="1" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1" applyProtection="1">
@@ -3262,11 +3348,11 @@
       <alignment vertical="center"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="47" fillId="0" borderId="3" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="3" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="47" fillId="0" borderId="2" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="2" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
       <protection hidden="1"/>
     </xf>
@@ -3280,7 +3366,7 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="2" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="47" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
       <protection hidden="1"/>
     </xf>
@@ -3331,7 +3417,7 @@
     <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="48" fillId="2" borderId="0" xfId="4" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="47" fillId="2" borderId="0" xfId="4" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection hidden="1"/>
     </xf>
@@ -3465,6 +3551,268 @@
     <xf numFmtId="0" fontId="7" fillId="2" borderId="13" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="11" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="10" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="12" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="0" xfId="6" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="13" fillId="0" borderId="0" xfId="6" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="11" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="10" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="1" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="11" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="11" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="12" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="10" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="4" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="5" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="8" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="2" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="9" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="0" borderId="11" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="0" borderId="10" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="11" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="11" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="12" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="11" xfId="2" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="2" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="2" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="11" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection hidden="1"/>
@@ -3486,268 +3834,6 @@
     <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="11" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="11" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="12" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="11" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="11" xfId="2" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="2" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="2" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="11" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="11" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="12" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="10" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="4" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="5" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="8" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="2" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="9" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="11" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="10" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="0" xfId="6" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="13" fillId="0" borderId="0" xfId="6" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="11" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="10" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="0" borderId="1" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="11" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="10" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="12" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="4" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -3793,53 +3879,6 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="9" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="1" fontId="9" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="3" fontId="33" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="175" fontId="9" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="33" fillId="4" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="33" fillId="4" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="11" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -3880,6 +3919,53 @@
     <xf numFmtId="165" fontId="9" fillId="0" borderId="10" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="9" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="1" fontId="9" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="3" fontId="33" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="175" fontId="9" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="33" fillId="4" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="33" fillId="4" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3949,6 +4035,49 @@
     </xf>
     <xf numFmtId="0" fontId="30" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="20" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="20" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="3" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="3" fillId="2" borderId="11" xfId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="3" fillId="2" borderId="10" xfId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="8">
@@ -4203,7 +4332,7 @@
                 </a:solidFill>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="es-ES"/>
+            <a:endParaRPr lang="es-PE"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="125309312"/>
@@ -4238,7 +4367,7 @@
                 </a:solidFill>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="es-ES"/>
+            <a:endParaRPr lang="es-PE"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="123935360"/>
@@ -4277,7 +4406,7 @@
           <a:cs typeface="Calibri"/>
         </a:defRPr>
       </a:pPr>
-      <a:endParaRPr lang="es-ES"/>
+      <a:endParaRPr lang="es-PE"/>
     </a:p>
   </c:txPr>
   <c:printSettings>
@@ -4421,7 +4550,7 @@
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
-            <a:endParaRPr lang="es-ES"/>
+            <a:endParaRPr lang="es-PE"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="123495168"/>
@@ -4452,7 +4581,7 @@
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
-            <a:endParaRPr lang="es-ES"/>
+            <a:endParaRPr lang="es-PE"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="123485184"/>
@@ -4491,7 +4620,7 @@
           <a:cs typeface="Calibri"/>
         </a:defRPr>
       </a:pPr>
-      <a:endParaRPr lang="es-ES"/>
+      <a:endParaRPr lang="es-PE"/>
     </a:p>
   </c:txPr>
   <c:printSettings>
@@ -4646,7 +4775,7 @@
                 <a:cs typeface="Arial"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="es-ES"/>
+            <a:endParaRPr lang="es-PE"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="123517952"/>
@@ -4683,7 +4812,7 @@
                 <a:cs typeface="Calibri"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="es-ES"/>
+            <a:endParaRPr lang="es-PE"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="123516416"/>
@@ -4722,7 +4851,7 @@
           <a:cs typeface="Calibri"/>
         </a:defRPr>
       </a:pPr>
-      <a:endParaRPr lang="es-ES"/>
+      <a:endParaRPr lang="es-PE"/>
     </a:p>
   </c:txPr>
   <c:printSettings>
@@ -4877,7 +5006,7 @@
                 <a:cs typeface="Arial"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="es-ES"/>
+            <a:endParaRPr lang="es-PE"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="123557376"/>
@@ -4915,7 +5044,7 @@
                 <a:cs typeface="Calibri"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="es-ES"/>
+            <a:endParaRPr lang="es-PE"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="123555840"/>
@@ -4954,7 +5083,7 @@
           <a:cs typeface="Calibri"/>
         </a:defRPr>
       </a:pPr>
-      <a:endParaRPr lang="es-ES"/>
+      <a:endParaRPr lang="es-PE"/>
     </a:p>
   </c:txPr>
   <c:printSettings>
@@ -6398,7 +6527,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="-------"/>
@@ -6457,7 +6586,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="datos de ecuacion del anillo"/>
@@ -6576,7 +6705,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink3.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="-------"/>
@@ -6627,7 +6756,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink4.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="-------"/>
@@ -6679,7 +6808,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink5.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="BGA"/>
@@ -6711,7 +6840,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink6.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="-------"/>
@@ -8367,846 +8496,846 @@
   <dimension ref="A1:AB55"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="1" style="389" customWidth="1"/>
-    <col min="2" max="2" width="6.33203125" style="389" customWidth="1"/>
-    <col min="3" max="3" width="9.44140625" style="389" customWidth="1"/>
-    <col min="4" max="4" width="12.88671875" style="389" customWidth="1"/>
-    <col min="5" max="5" width="10.33203125" style="389" customWidth="1"/>
-    <col min="6" max="6" width="10.6640625" style="389" customWidth="1"/>
-    <col min="7" max="7" width="0.6640625" style="389" customWidth="1"/>
-    <col min="8" max="8" width="10" style="389" customWidth="1"/>
-    <col min="9" max="9" width="4.109375" style="389" customWidth="1"/>
-    <col min="10" max="10" width="0.88671875" style="389" customWidth="1"/>
-    <col min="11" max="11" width="7" style="389" customWidth="1"/>
-    <col min="12" max="12" width="7.109375" style="389" customWidth="1"/>
-    <col min="13" max="13" width="0.6640625" style="389" customWidth="1"/>
-    <col min="14" max="14" width="13.44140625" style="389" customWidth="1"/>
-    <col min="15" max="15" width="15.5546875" style="389" customWidth="1"/>
-    <col min="16" max="16" width="8.88671875" style="389"/>
-    <col min="17" max="17" width="9.6640625" style="389" customWidth="1"/>
-    <col min="18" max="18" width="11.6640625" style="389" customWidth="1"/>
-    <col min="19" max="20" width="8.88671875" style="389"/>
-    <col min="21" max="21" width="10.5546875" style="389" customWidth="1"/>
-    <col min="22" max="16384" width="8.88671875" style="389"/>
+    <col min="1" max="1" width="1" style="388" customWidth="1"/>
+    <col min="2" max="2" width="6.33203125" style="388" customWidth="1"/>
+    <col min="3" max="3" width="9.44140625" style="388" customWidth="1"/>
+    <col min="4" max="4" width="12.88671875" style="388" customWidth="1"/>
+    <col min="5" max="5" width="10.33203125" style="388" customWidth="1"/>
+    <col min="6" max="6" width="10.6640625" style="388" customWidth="1"/>
+    <col min="7" max="7" width="0.6640625" style="388" customWidth="1"/>
+    <col min="8" max="8" width="10" style="388" customWidth="1"/>
+    <col min="9" max="9" width="4.109375" style="388" customWidth="1"/>
+    <col min="10" max="10" width="0.88671875" style="388" customWidth="1"/>
+    <col min="11" max="11" width="7" style="388" customWidth="1"/>
+    <col min="12" max="12" width="7.109375" style="388" customWidth="1"/>
+    <col min="13" max="13" width="0.6640625" style="388" customWidth="1"/>
+    <col min="14" max="14" width="13.44140625" style="388" customWidth="1"/>
+    <col min="15" max="15" width="15.5546875" style="388" customWidth="1"/>
+    <col min="16" max="16" width="8.88671875" style="388"/>
+    <col min="17" max="17" width="9.6640625" style="388" customWidth="1"/>
+    <col min="18" max="18" width="11.6640625" style="388" customWidth="1"/>
+    <col min="19" max="20" width="8.88671875" style="388"/>
+    <col min="21" max="21" width="10.5546875" style="388" customWidth="1"/>
+    <col min="22" max="16384" width="8.88671875" style="388"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" s="326" customFormat="1" ht="15" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="322"/>
-      <c r="B1" s="323"/>
-      <c r="C1" s="323"/>
-      <c r="D1" s="323"/>
-      <c r="E1" s="324"/>
-      <c r="F1" s="324"/>
-      <c r="G1" s="324"/>
-      <c r="H1" s="324"/>
-      <c r="I1" s="324"/>
-      <c r="J1" s="324"/>
-      <c r="K1" s="324"/>
-      <c r="L1" s="324"/>
-      <c r="M1" s="324"/>
-      <c r="N1" s="324"/>
-      <c r="O1" s="325"/>
-    </row>
-    <row r="2" spans="1:21" s="326" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="327"/>
-      <c r="B2" s="328"/>
-      <c r="C2" s="328"/>
-      <c r="D2" s="328"/>
-      <c r="E2" s="329"/>
-      <c r="F2" s="329"/>
-      <c r="G2" s="329"/>
-      <c r="H2" s="329"/>
-      <c r="I2" s="329"/>
-      <c r="J2" s="329"/>
-      <c r="K2" s="329"/>
-      <c r="L2" s="329"/>
-      <c r="M2" s="329"/>
-      <c r="N2" s="329"/>
-      <c r="O2" s="330"/>
-      <c r="T2" s="401" t="s">
+    <row r="1" spans="1:21" s="325" customFormat="1" ht="15" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="321"/>
+      <c r="B1" s="322"/>
+      <c r="C1" s="322"/>
+      <c r="D1" s="322"/>
+      <c r="E1" s="323"/>
+      <c r="F1" s="323"/>
+      <c r="G1" s="323"/>
+      <c r="H1" s="323"/>
+      <c r="I1" s="323"/>
+      <c r="J1" s="323"/>
+      <c r="K1" s="323"/>
+      <c r="L1" s="323"/>
+      <c r="M1" s="323"/>
+      <c r="N1" s="323"/>
+      <c r="O1" s="324"/>
+    </row>
+    <row r="2" spans="1:21" s="325" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="326"/>
+      <c r="B2" s="327"/>
+      <c r="C2" s="327"/>
+      <c r="D2" s="327"/>
+      <c r="E2" s="328"/>
+      <c r="F2" s="328"/>
+      <c r="G2" s="328"/>
+      <c r="H2" s="328"/>
+      <c r="I2" s="328"/>
+      <c r="J2" s="328"/>
+      <c r="K2" s="328"/>
+      <c r="L2" s="328"/>
+      <c r="M2" s="328"/>
+      <c r="N2" s="328"/>
+      <c r="O2" s="329"/>
+      <c r="T2" s="400" t="s">
         <v>1</v>
       </c>
-      <c r="U2" s="402"/>
-    </row>
-    <row r="3" spans="1:21" s="326" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="327"/>
-      <c r="B3" s="328"/>
-      <c r="C3" s="328"/>
-      <c r="D3" s="328"/>
-      <c r="E3" s="329"/>
-      <c r="F3" s="329"/>
-      <c r="G3" s="329"/>
-      <c r="H3" s="329"/>
-      <c r="I3" s="329"/>
-      <c r="J3" s="329"/>
-      <c r="K3" s="329"/>
-      <c r="L3" s="329"/>
-      <c r="M3" s="329"/>
-      <c r="N3" s="329"/>
-      <c r="O3" s="330"/>
-      <c r="T3" s="401" t="s">
+      <c r="U2" s="401"/>
+    </row>
+    <row r="3" spans="1:21" s="325" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="326"/>
+      <c r="B3" s="327"/>
+      <c r="C3" s="327"/>
+      <c r="D3" s="327"/>
+      <c r="E3" s="328"/>
+      <c r="F3" s="328"/>
+      <c r="G3" s="328"/>
+      <c r="H3" s="328"/>
+      <c r="I3" s="328"/>
+      <c r="J3" s="328"/>
+      <c r="K3" s="328"/>
+      <c r="L3" s="328"/>
+      <c r="M3" s="328"/>
+      <c r="N3" s="328"/>
+      <c r="O3" s="329"/>
+      <c r="T3" s="400" t="s">
         <v>4</v>
       </c>
-      <c r="U3" s="403"/>
-    </row>
-    <row r="4" spans="1:21" s="326" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="327"/>
-      <c r="B4" s="328"/>
-      <c r="C4" s="328"/>
-      <c r="D4" s="328"/>
-      <c r="E4" s="329"/>
-      <c r="F4" s="329"/>
-      <c r="G4" s="329"/>
-      <c r="H4" s="329"/>
-      <c r="I4" s="329"/>
-      <c r="J4" s="329"/>
-      <c r="K4" s="329"/>
-      <c r="L4" s="329"/>
-      <c r="M4" s="329"/>
-      <c r="N4" s="329"/>
-      <c r="O4" s="330"/>
-      <c r="Q4" s="331" t="s">
+      <c r="U3" s="402"/>
+    </row>
+    <row r="4" spans="1:21" s="325" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="326"/>
+      <c r="B4" s="327"/>
+      <c r="C4" s="327"/>
+      <c r="D4" s="327"/>
+      <c r="E4" s="328"/>
+      <c r="F4" s="328"/>
+      <c r="G4" s="328"/>
+      <c r="H4" s="328"/>
+      <c r="I4" s="328"/>
+      <c r="J4" s="328"/>
+      <c r="K4" s="328"/>
+      <c r="L4" s="328"/>
+      <c r="M4" s="328"/>
+      <c r="N4" s="328"/>
+      <c r="O4" s="329"/>
+      <c r="Q4" s="330" t="s">
         <v>159</v>
       </c>
-      <c r="R4" s="331" t="s">
+      <c r="R4" s="330" t="s">
         <v>158</v>
       </c>
-      <c r="T4" s="401" t="s">
+      <c r="T4" s="400" t="s">
         <v>5</v>
       </c>
-      <c r="U4" s="403"/>
-    </row>
-    <row r="5" spans="1:21" s="326" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="332"/>
-      <c r="B5" s="333"/>
-      <c r="C5" s="333"/>
-      <c r="D5" s="333"/>
-      <c r="E5" s="333"/>
-      <c r="F5" s="333"/>
-      <c r="G5" s="333"/>
-      <c r="H5" s="333"/>
-      <c r="I5" s="333"/>
-      <c r="J5" s="333"/>
-      <c r="K5" s="333"/>
-      <c r="L5" s="333"/>
-      <c r="M5" s="333"/>
-      <c r="N5" s="333"/>
-      <c r="O5" s="334"/>
-      <c r="Q5" s="331" t="s">
+      <c r="U4" s="402"/>
+    </row>
+    <row r="5" spans="1:21" s="325" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="331"/>
+      <c r="B5" s="332"/>
+      <c r="C5" s="332"/>
+      <c r="D5" s="332"/>
+      <c r="E5" s="332"/>
+      <c r="F5" s="332"/>
+      <c r="G5" s="332"/>
+      <c r="H5" s="332"/>
+      <c r="I5" s="332"/>
+      <c r="J5" s="332"/>
+      <c r="K5" s="332"/>
+      <c r="L5" s="332"/>
+      <c r="M5" s="332"/>
+      <c r="N5" s="332"/>
+      <c r="O5" s="333"/>
+      <c r="Q5" s="330" t="s">
         <v>161</v>
       </c>
-      <c r="R5" s="331" t="s">
+      <c r="R5" s="330" t="s">
         <v>160</v>
       </c>
-      <c r="T5" s="401" t="s">
+      <c r="T5" s="400" t="s">
         <v>7</v>
       </c>
-      <c r="U5" s="403"/>
-    </row>
-    <row r="6" spans="1:21" s="326" customFormat="1" ht="12" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="335"/>
-      <c r="B6" s="335"/>
-      <c r="C6" s="335"/>
-      <c r="D6" s="335"/>
-      <c r="E6" s="335"/>
-      <c r="F6" s="335"/>
-      <c r="G6" s="335"/>
-      <c r="H6" s="335"/>
-      <c r="I6" s="335"/>
-      <c r="J6" s="335"/>
-      <c r="K6" s="335"/>
-      <c r="L6" s="335"/>
-      <c r="M6" s="335"/>
-      <c r="N6" s="335"/>
-      <c r="O6" s="335"/>
-      <c r="Q6" s="336" t="s">
+      <c r="U5" s="402"/>
+    </row>
+    <row r="6" spans="1:21" s="325" customFormat="1" ht="12" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="334"/>
+      <c r="B6" s="334"/>
+      <c r="C6" s="334"/>
+      <c r="D6" s="334"/>
+      <c r="E6" s="334"/>
+      <c r="F6" s="334"/>
+      <c r="G6" s="334"/>
+      <c r="H6" s="334"/>
+      <c r="I6" s="334"/>
+      <c r="J6" s="334"/>
+      <c r="K6" s="334"/>
+      <c r="L6" s="334"/>
+      <c r="M6" s="334"/>
+      <c r="N6" s="334"/>
+      <c r="O6" s="334"/>
+      <c r="Q6" s="335" t="s">
         <v>144</v>
       </c>
-      <c r="R6" s="336">
+      <c r="R6" s="335">
         <v>40</v>
       </c>
-      <c r="T6" s="404"/>
-      <c r="U6" s="405"/>
-    </row>
-    <row r="7" spans="1:21" s="326" customFormat="1" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="465" t="s">
+      <c r="T6" s="403"/>
+      <c r="U6" s="404"/>
+    </row>
+    <row r="7" spans="1:21" s="325" customFormat="1" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="425" t="s">
         <v>0</v>
       </c>
-      <c r="B7" s="465"/>
-      <c r="C7" s="465"/>
-      <c r="D7" s="465"/>
-      <c r="E7" s="465"/>
-      <c r="F7" s="465"/>
-      <c r="G7" s="465"/>
-      <c r="H7" s="465"/>
-      <c r="I7" s="465"/>
-      <c r="J7" s="465"/>
-      <c r="K7" s="465"/>
-      <c r="L7" s="465"/>
-      <c r="M7" s="465"/>
-      <c r="N7" s="465"/>
-      <c r="O7" s="465"/>
-      <c r="Q7" s="336" t="s">
+      <c r="B7" s="425"/>
+      <c r="C7" s="425"/>
+      <c r="D7" s="425"/>
+      <c r="E7" s="425"/>
+      <c r="F7" s="425"/>
+      <c r="G7" s="425"/>
+      <c r="H7" s="425"/>
+      <c r="I7" s="425"/>
+      <c r="J7" s="425"/>
+      <c r="K7" s="425"/>
+      <c r="L7" s="425"/>
+      <c r="M7" s="425"/>
+      <c r="N7" s="425"/>
+      <c r="O7" s="425"/>
+      <c r="Q7" s="335" t="s">
         <v>143</v>
       </c>
-      <c r="R7" s="336">
+      <c r="R7" s="335">
         <v>25</v>
       </c>
-      <c r="T7" s="401" t="s">
+      <c r="T7" s="400" t="s">
         <v>155</v>
       </c>
-      <c r="U7" s="405"/>
-    </row>
-    <row r="8" spans="1:21" s="326" customFormat="1" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="466" t="s">
+      <c r="U7" s="404"/>
+    </row>
+    <row r="8" spans="1:21" s="325" customFormat="1" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="426" t="s">
         <v>191</v>
       </c>
-      <c r="B8" s="466"/>
-      <c r="C8" s="466"/>
-      <c r="D8" s="466"/>
-      <c r="E8" s="466"/>
-      <c r="F8" s="466"/>
-      <c r="G8" s="466"/>
-      <c r="H8" s="466"/>
-      <c r="I8" s="466"/>
-      <c r="J8" s="466"/>
-      <c r="K8" s="466"/>
-      <c r="L8" s="466"/>
-      <c r="M8" s="466"/>
-      <c r="N8" s="466"/>
-      <c r="O8" s="466"/>
-      <c r="Q8" s="336" t="s">
+      <c r="B8" s="426"/>
+      <c r="C8" s="426"/>
+      <c r="D8" s="426"/>
+      <c r="E8" s="426"/>
+      <c r="F8" s="426"/>
+      <c r="G8" s="426"/>
+      <c r="H8" s="426"/>
+      <c r="I8" s="426"/>
+      <c r="J8" s="426"/>
+      <c r="K8" s="426"/>
+      <c r="L8" s="426"/>
+      <c r="M8" s="426"/>
+      <c r="N8" s="426"/>
+      <c r="O8" s="426"/>
+      <c r="Q8" s="335" t="s">
         <v>142</v>
       </c>
-      <c r="R8" s="336">
+      <c r="R8" s="335">
         <v>18</v>
       </c>
-      <c r="T8" s="401" t="s">
+      <c r="T8" s="400" t="s">
         <v>235</v>
       </c>
-      <c r="U8" s="406"/>
-    </row>
-    <row r="9" spans="1:21" s="326" customFormat="1" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="337"/>
-      <c r="B9" s="337"/>
-      <c r="C9" s="337"/>
-      <c r="E9" s="337"/>
-      <c r="F9" s="337"/>
-      <c r="G9" s="337"/>
-      <c r="H9" s="337"/>
-      <c r="I9" s="337"/>
-      <c r="J9" s="337"/>
-      <c r="K9" s="337"/>
-      <c r="L9" s="337"/>
-      <c r="M9" s="337"/>
-      <c r="N9" s="337"/>
-      <c r="O9" s="337"/>
-      <c r="Q9" s="338">
+      <c r="U8" s="405"/>
+    </row>
+    <row r="9" spans="1:21" s="325" customFormat="1" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="336"/>
+      <c r="B9" s="336"/>
+      <c r="C9" s="336"/>
+      <c r="E9" s="336"/>
+      <c r="F9" s="336"/>
+      <c r="G9" s="336"/>
+      <c r="H9" s="336"/>
+      <c r="I9" s="336"/>
+      <c r="J9" s="336"/>
+      <c r="K9" s="336"/>
+      <c r="L9" s="336"/>
+      <c r="M9" s="336"/>
+      <c r="N9" s="336"/>
+      <c r="O9" s="336"/>
+      <c r="Q9" s="337">
         <v>2.5</v>
       </c>
-      <c r="R9" s="336">
+      <c r="R9" s="335">
         <v>12</v>
       </c>
-      <c r="T9" s="401" t="s">
+      <c r="T9" s="400" t="s">
         <v>156</v>
       </c>
-      <c r="U9" s="405"/>
-    </row>
-    <row r="10" spans="1:21" s="326" customFormat="1" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C10" s="339"/>
-      <c r="E10" s="340" t="s">
+      <c r="U9" s="404"/>
+    </row>
+    <row r="10" spans="1:21" s="325" customFormat="1" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C10" s="338"/>
+      <c r="E10" s="339" t="s">
         <v>192</v>
       </c>
-      <c r="F10" s="467" t="s">
+      <c r="F10" s="427" t="s">
         <v>193</v>
       </c>
-      <c r="G10" s="468"/>
-      <c r="H10" s="340" t="s">
+      <c r="G10" s="428"/>
+      <c r="H10" s="339" t="s">
         <v>194</v>
       </c>
-      <c r="I10" s="469" t="s">
+      <c r="I10" s="429" t="s">
         <v>195</v>
       </c>
-      <c r="J10" s="469"/>
-      <c r="K10" s="469"/>
-      <c r="L10" s="339"/>
-      <c r="M10" s="470"/>
-      <c r="N10" s="470"/>
-      <c r="O10" s="470"/>
-      <c r="P10" s="341"/>
-      <c r="Q10" s="342" t="s">
+      <c r="J10" s="429"/>
+      <c r="K10" s="429"/>
+      <c r="L10" s="338"/>
+      <c r="M10" s="417"/>
+      <c r="N10" s="417"/>
+      <c r="O10" s="417"/>
+      <c r="P10" s="340"/>
+      <c r="Q10" s="341" t="s">
         <v>138</v>
       </c>
-      <c r="R10" s="336">
+      <c r="R10" s="335">
         <v>8</v>
       </c>
-      <c r="T10" s="404"/>
-      <c r="U10" s="405"/>
-    </row>
-    <row r="11" spans="1:21" s="326" customFormat="1" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="343"/>
-      <c r="B11" s="470"/>
-      <c r="C11" s="470"/>
-      <c r="D11" s="470"/>
-      <c r="E11" s="344"/>
-      <c r="F11" s="480"/>
-      <c r="G11" s="481"/>
-      <c r="H11" s="345"/>
-      <c r="I11" s="480"/>
-      <c r="J11" s="482"/>
-      <c r="K11" s="481"/>
-      <c r="L11" s="339"/>
-      <c r="M11" s="470"/>
-      <c r="N11" s="470"/>
-      <c r="O11" s="470"/>
-      <c r="P11" s="341"/>
-      <c r="Q11" s="342" t="s">
+      <c r="T10" s="403"/>
+      <c r="U10" s="404"/>
+    </row>
+    <row r="11" spans="1:21" s="325" customFormat="1" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="342"/>
+      <c r="B11" s="417"/>
+      <c r="C11" s="417"/>
+      <c r="D11" s="417"/>
+      <c r="E11" s="343"/>
+      <c r="F11" s="418"/>
+      <c r="G11" s="419"/>
+      <c r="H11" s="344"/>
+      <c r="I11" s="418"/>
+      <c r="J11" s="420"/>
+      <c r="K11" s="419"/>
+      <c r="L11" s="338"/>
+      <c r="M11" s="417"/>
+      <c r="N11" s="417"/>
+      <c r="O11" s="417"/>
+      <c r="P11" s="340"/>
+      <c r="Q11" s="341" t="s">
         <v>62</v>
       </c>
-      <c r="R11" s="336">
+      <c r="R11" s="335">
         <v>5</v>
       </c>
-      <c r="T11" s="401" t="s">
+      <c r="T11" s="400" t="s">
         <v>11</v>
       </c>
-      <c r="U11" s="405"/>
-    </row>
-    <row r="12" spans="1:21" s="326" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="343"/>
-      <c r="B12" s="339"/>
-      <c r="C12" s="346"/>
-      <c r="D12" s="346"/>
-      <c r="E12" s="346"/>
-      <c r="F12" s="346"/>
-      <c r="G12" s="346"/>
-      <c r="H12" s="346"/>
-      <c r="I12" s="346"/>
-      <c r="J12" s="346"/>
-      <c r="K12" s="346"/>
-      <c r="L12" s="346"/>
-      <c r="M12" s="346"/>
-      <c r="N12" s="346"/>
-      <c r="O12" s="347"/>
-      <c r="P12" s="341"/>
-      <c r="Q12" s="342" t="s">
+      <c r="U11" s="404"/>
+    </row>
+    <row r="12" spans="1:21" s="325" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="342"/>
+      <c r="B12" s="338"/>
+      <c r="C12" s="345"/>
+      <c r="D12" s="345"/>
+      <c r="E12" s="345"/>
+      <c r="F12" s="345"/>
+      <c r="G12" s="345"/>
+      <c r="H12" s="345"/>
+      <c r="I12" s="345"/>
+      <c r="J12" s="345"/>
+      <c r="K12" s="345"/>
+      <c r="L12" s="345"/>
+      <c r="M12" s="345"/>
+      <c r="N12" s="345"/>
+      <c r="O12" s="346"/>
+      <c r="P12" s="340"/>
+      <c r="Q12" s="341" t="s">
         <v>139</v>
       </c>
-      <c r="R12" s="336">
+      <c r="R12" s="335">
         <v>4</v>
       </c>
-      <c r="T12" s="401" t="s">
+      <c r="T12" s="400" t="s">
         <v>13</v>
       </c>
-      <c r="U12" s="406"/>
-    </row>
-    <row r="13" spans="1:21" s="326" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="483" t="s">
+      <c r="U12" s="405"/>
+    </row>
+    <row r="13" spans="1:21" s="325" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="421" t="s">
         <v>196</v>
       </c>
-      <c r="B13" s="484"/>
-      <c r="C13" s="484"/>
-      <c r="D13" s="484"/>
-      <c r="E13" s="484"/>
-      <c r="F13" s="484"/>
-      <c r="G13" s="484"/>
-      <c r="H13" s="484"/>
-      <c r="I13" s="484"/>
-      <c r="J13" s="484"/>
-      <c r="K13" s="484"/>
-      <c r="L13" s="484"/>
-      <c r="M13" s="484"/>
-      <c r="N13" s="484"/>
-      <c r="O13" s="485"/>
-      <c r="P13" s="341"/>
-      <c r="Q13" s="342" t="s">
+      <c r="B13" s="422"/>
+      <c r="C13" s="422"/>
+      <c r="D13" s="422"/>
+      <c r="E13" s="422"/>
+      <c r="F13" s="422"/>
+      <c r="G13" s="422"/>
+      <c r="H13" s="422"/>
+      <c r="I13" s="422"/>
+      <c r="J13" s="422"/>
+      <c r="K13" s="422"/>
+      <c r="L13" s="422"/>
+      <c r="M13" s="422"/>
+      <c r="N13" s="422"/>
+      <c r="O13" s="423"/>
+      <c r="P13" s="340"/>
+      <c r="Q13" s="341" t="s">
         <v>137</v>
       </c>
-      <c r="R13" s="336">
+      <c r="R13" s="335">
         <v>3</v>
       </c>
-      <c r="T13" s="401" t="s">
+      <c r="T13" s="400" t="s">
         <v>14</v>
       </c>
-      <c r="U13" s="406"/>
-    </row>
-    <row r="14" spans="1:21" s="326" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="471" t="s">
+      <c r="U13" s="405"/>
+    </row>
+    <row r="14" spans="1:21" s="325" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="408" t="s">
         <v>197</v>
       </c>
-      <c r="B14" s="472"/>
-      <c r="C14" s="472"/>
-      <c r="D14" s="472"/>
-      <c r="E14" s="472"/>
-      <c r="F14" s="472"/>
-      <c r="G14" s="472"/>
-      <c r="H14" s="472"/>
-      <c r="I14" s="472"/>
-      <c r="J14" s="472"/>
-      <c r="K14" s="472"/>
-      <c r="L14" s="472"/>
-      <c r="M14" s="472"/>
-      <c r="N14" s="472"/>
-      <c r="O14" s="473"/>
-      <c r="P14" s="341"/>
-      <c r="Q14" s="342" t="s">
+      <c r="B14" s="409"/>
+      <c r="C14" s="409"/>
+      <c r="D14" s="409"/>
+      <c r="E14" s="409"/>
+      <c r="F14" s="409"/>
+      <c r="G14" s="409"/>
+      <c r="H14" s="409"/>
+      <c r="I14" s="409"/>
+      <c r="J14" s="409"/>
+      <c r="K14" s="409"/>
+      <c r="L14" s="409"/>
+      <c r="M14" s="409"/>
+      <c r="N14" s="409"/>
+      <c r="O14" s="410"/>
+      <c r="P14" s="340"/>
+      <c r="Q14" s="341" t="s">
         <v>183</v>
       </c>
-      <c r="R14" s="336">
+      <c r="R14" s="335">
         <v>2</v>
       </c>
-      <c r="T14" s="404"/>
-      <c r="U14" s="405"/>
-    </row>
-    <row r="15" spans="1:21" s="326" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="348"/>
-      <c r="B15" s="348"/>
-      <c r="C15" s="348"/>
-      <c r="D15" s="348"/>
-      <c r="E15" s="348"/>
-      <c r="F15" s="348"/>
-      <c r="G15" s="348"/>
-      <c r="H15" s="348"/>
-      <c r="I15" s="348"/>
-      <c r="J15" s="348"/>
-      <c r="K15" s="348"/>
-      <c r="L15" s="348"/>
-      <c r="M15" s="348"/>
-      <c r="N15" s="348"/>
-      <c r="O15" s="348"/>
-      <c r="P15" s="341"/>
-      <c r="Q15" s="342" t="s">
+      <c r="T14" s="403"/>
+      <c r="U14" s="404"/>
+    </row>
+    <row r="15" spans="1:21" s="325" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="347"/>
+      <c r="B15" s="347"/>
+      <c r="C15" s="347"/>
+      <c r="D15" s="347"/>
+      <c r="E15" s="347"/>
+      <c r="F15" s="347"/>
+      <c r="G15" s="347"/>
+      <c r="H15" s="347"/>
+      <c r="I15" s="347"/>
+      <c r="J15" s="347"/>
+      <c r="K15" s="347"/>
+      <c r="L15" s="347"/>
+      <c r="M15" s="347"/>
+      <c r="N15" s="347"/>
+      <c r="O15" s="347"/>
+      <c r="P15" s="340"/>
+      <c r="Q15" s="341" t="s">
         <v>140</v>
       </c>
-      <c r="R15" s="336">
+      <c r="R15" s="335">
         <v>2</v>
       </c>
-      <c r="T15" s="401" t="s">
+      <c r="T15" s="400" t="s">
         <v>10</v>
       </c>
-      <c r="U15" s="407"/>
-    </row>
-    <row r="16" spans="1:21" s="326" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="348"/>
-      <c r="B16" s="474" t="s">
+      <c r="U15" s="406"/>
+    </row>
+    <row r="16" spans="1:21" s="325" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="347"/>
+      <c r="B16" s="411" t="s">
         <v>198</v>
       </c>
-      <c r="C16" s="475"/>
-      <c r="D16" s="475"/>
-      <c r="E16" s="475"/>
-      <c r="F16" s="476"/>
-      <c r="G16" s="348"/>
-      <c r="H16" s="477" t="s">
+      <c r="C16" s="412"/>
+      <c r="D16" s="412"/>
+      <c r="E16" s="412"/>
+      <c r="F16" s="413"/>
+      <c r="G16" s="347"/>
+      <c r="H16" s="414" t="s">
         <v>199</v>
       </c>
-      <c r="I16" s="478"/>
-      <c r="J16" s="479"/>
-      <c r="K16" s="486" t="s">
+      <c r="I16" s="415"/>
+      <c r="J16" s="416"/>
+      <c r="K16" s="424" t="s">
         <v>200</v>
       </c>
-      <c r="L16" s="486"/>
-      <c r="M16" s="348"/>
-      <c r="N16" s="348"/>
-      <c r="O16" s="348"/>
-      <c r="P16" s="341"/>
-      <c r="Q16" s="349" t="s">
+      <c r="L16" s="424"/>
+      <c r="M16" s="347"/>
+      <c r="N16" s="347"/>
+      <c r="O16" s="347"/>
+      <c r="P16" s="340"/>
+      <c r="Q16" s="348" t="s">
         <v>201</v>
       </c>
-      <c r="T16" s="401" t="s">
+      <c r="T16" s="400" t="s">
         <v>12</v>
       </c>
-      <c r="U16" s="407"/>
-    </row>
-    <row r="17" spans="1:22" s="326" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="348"/>
-      <c r="B17" s="443" t="s">
+      <c r="U16" s="406"/>
+    </row>
+    <row r="17" spans="1:22" s="325" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="347"/>
+      <c r="B17" s="430" t="s">
         <v>202</v>
       </c>
-      <c r="C17" s="444"/>
-      <c r="D17" s="445"/>
-      <c r="E17" s="394"/>
-      <c r="F17" s="395"/>
-      <c r="G17" s="348"/>
-      <c r="H17" s="448" t="s">
+      <c r="C17" s="431"/>
+      <c r="D17" s="432"/>
+      <c r="E17" s="393"/>
+      <c r="F17" s="394"/>
+      <c r="G17" s="347"/>
+      <c r="H17" s="435" t="s">
         <v>203</v>
       </c>
-      <c r="I17" s="449"/>
-      <c r="J17" s="450"/>
-      <c r="K17" s="424"/>
-      <c r="L17" s="426"/>
-      <c r="M17" s="348"/>
-      <c r="N17" s="348"/>
-      <c r="O17" s="348"/>
-      <c r="P17" s="350"/>
-      <c r="Q17" s="341"/>
-      <c r="T17" s="401" t="s">
+      <c r="I17" s="436"/>
+      <c r="J17" s="437"/>
+      <c r="K17" s="438"/>
+      <c r="L17" s="439"/>
+      <c r="M17" s="347"/>
+      <c r="N17" s="347"/>
+      <c r="O17" s="347"/>
+      <c r="P17" s="349"/>
+      <c r="Q17" s="340"/>
+      <c r="T17" s="400" t="s">
         <v>236</v>
       </c>
-      <c r="U17" s="408"/>
-    </row>
-    <row r="18" spans="1:22" s="326" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="348"/>
-      <c r="B18" s="443" t="s">
+      <c r="U17" s="407"/>
+    </row>
+    <row r="18" spans="1:22" s="325" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="347"/>
+      <c r="B18" s="430" t="s">
         <v>204</v>
       </c>
-      <c r="C18" s="444"/>
-      <c r="D18" s="445"/>
-      <c r="E18" s="446" t="s">
+      <c r="C18" s="431"/>
+      <c r="D18" s="432"/>
+      <c r="E18" s="433" t="s">
         <v>237</v>
       </c>
-      <c r="F18" s="447"/>
-      <c r="G18" s="348"/>
-      <c r="H18" s="448" t="s">
+      <c r="F18" s="434"/>
+      <c r="G18" s="347"/>
+      <c r="H18" s="435" t="s">
         <v>205</v>
       </c>
-      <c r="I18" s="449"/>
-      <c r="J18" s="450"/>
-      <c r="K18" s="424"/>
-      <c r="L18" s="426"/>
-      <c r="M18" s="348"/>
-      <c r="N18" s="348"/>
-      <c r="O18" s="348"/>
-      <c r="P18" s="341"/>
-      <c r="Q18" s="341"/>
-    </row>
-    <row r="19" spans="1:22" s="326" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="348"/>
-      <c r="B19" s="443" t="s">
+      <c r="I18" s="436"/>
+      <c r="J18" s="437"/>
+      <c r="K18" s="438"/>
+      <c r="L18" s="439"/>
+      <c r="M18" s="347"/>
+      <c r="N18" s="347"/>
+      <c r="O18" s="347"/>
+      <c r="P18" s="340"/>
+      <c r="Q18" s="340"/>
+    </row>
+    <row r="19" spans="1:22" s="325" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="347"/>
+      <c r="B19" s="430" t="s">
         <v>206</v>
       </c>
-      <c r="C19" s="444"/>
-      <c r="D19" s="445"/>
-      <c r="E19" s="446" t="s">
+      <c r="C19" s="431"/>
+      <c r="D19" s="432"/>
+      <c r="E19" s="433" t="s">
         <v>237</v>
       </c>
-      <c r="F19" s="447"/>
-      <c r="G19" s="348"/>
-      <c r="H19" s="448" t="s">
+      <c r="F19" s="434"/>
+      <c r="G19" s="347"/>
+      <c r="H19" s="435" t="s">
         <v>207</v>
       </c>
-      <c r="I19" s="449"/>
-      <c r="J19" s="450"/>
-      <c r="K19" s="424"/>
-      <c r="L19" s="426"/>
-      <c r="M19" s="348"/>
-      <c r="N19" s="348"/>
-      <c r="O19" s="348"/>
-      <c r="P19" s="341"/>
-      <c r="Q19" s="341"/>
-    </row>
-    <row r="20" spans="1:22" s="326" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="348"/>
-      <c r="B20" s="443" t="s">
+      <c r="I19" s="436"/>
+      <c r="J19" s="437"/>
+      <c r="K19" s="438"/>
+      <c r="L19" s="439"/>
+      <c r="M19" s="347"/>
+      <c r="N19" s="347"/>
+      <c r="O19" s="347"/>
+      <c r="P19" s="340"/>
+      <c r="Q19" s="340"/>
+    </row>
+    <row r="20" spans="1:22" s="325" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="347"/>
+      <c r="B20" s="430" t="s">
         <v>208</v>
       </c>
-      <c r="C20" s="444"/>
-      <c r="D20" s="445"/>
-      <c r="E20" s="446" t="s">
+      <c r="C20" s="431"/>
+      <c r="D20" s="432"/>
+      <c r="E20" s="433" t="s">
         <v>237</v>
       </c>
-      <c r="F20" s="447"/>
-      <c r="G20" s="348"/>
-      <c r="H20" s="453" t="s">
+      <c r="F20" s="434"/>
+      <c r="G20" s="347"/>
+      <c r="H20" s="442" t="s">
         <v>209</v>
       </c>
-      <c r="I20" s="454"/>
-      <c r="J20" s="455"/>
-      <c r="K20" s="459"/>
-      <c r="L20" s="460"/>
-      <c r="M20" s="348"/>
-      <c r="N20" s="348"/>
-      <c r="O20" s="348"/>
-      <c r="P20" s="341"/>
-      <c r="Q20" s="341"/>
-    </row>
-    <row r="21" spans="1:22" s="326" customFormat="1" ht="7.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="348"/>
-      <c r="B21" s="348"/>
-      <c r="C21" s="348"/>
-      <c r="D21" s="348"/>
-      <c r="E21" s="348"/>
-      <c r="F21" s="348"/>
-      <c r="G21" s="348"/>
-      <c r="H21" s="456"/>
-      <c r="I21" s="457"/>
-      <c r="J21" s="458"/>
-      <c r="K21" s="461"/>
-      <c r="L21" s="462"/>
-      <c r="M21" s="348"/>
-      <c r="N21" s="348"/>
-      <c r="O21" s="348"/>
-      <c r="P21" s="341"/>
-      <c r="Q21" s="341"/>
-    </row>
-    <row r="22" spans="1:22" s="326" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="348"/>
-      <c r="B22" s="443" t="s">
+      <c r="I20" s="443"/>
+      <c r="J20" s="444"/>
+      <c r="K20" s="448"/>
+      <c r="L20" s="449"/>
+      <c r="M20" s="347"/>
+      <c r="N20" s="347"/>
+      <c r="O20" s="347"/>
+      <c r="P20" s="340"/>
+      <c r="Q20" s="340"/>
+    </row>
+    <row r="21" spans="1:22" s="325" customFormat="1" ht="7.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="347"/>
+      <c r="B21" s="347"/>
+      <c r="C21" s="347"/>
+      <c r="D21" s="347"/>
+      <c r="E21" s="347"/>
+      <c r="F21" s="347"/>
+      <c r="G21" s="347"/>
+      <c r="H21" s="445"/>
+      <c r="I21" s="446"/>
+      <c r="J21" s="447"/>
+      <c r="K21" s="450"/>
+      <c r="L21" s="451"/>
+      <c r="M21" s="347"/>
+      <c r="N21" s="347"/>
+      <c r="O21" s="347"/>
+      <c r="P21" s="340"/>
+      <c r="Q21" s="340"/>
+    </row>
+    <row r="22" spans="1:22" s="325" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="347"/>
+      <c r="B22" s="430" t="s">
         <v>210</v>
       </c>
-      <c r="C22" s="444"/>
-      <c r="D22" s="445"/>
-      <c r="E22" s="463"/>
-      <c r="F22" s="464"/>
-      <c r="G22" s="348"/>
-      <c r="H22" s="448" t="s">
+      <c r="C22" s="431"/>
+      <c r="D22" s="432"/>
+      <c r="E22" s="452"/>
+      <c r="F22" s="453"/>
+      <c r="G22" s="347"/>
+      <c r="H22" s="435" t="s">
         <v>211</v>
       </c>
-      <c r="I22" s="449"/>
-      <c r="J22" s="450"/>
-      <c r="K22" s="448"/>
-      <c r="L22" s="450"/>
-      <c r="M22" s="348"/>
-      <c r="N22" s="348"/>
-      <c r="O22" s="348"/>
-      <c r="P22" s="341"/>
-      <c r="Q22" s="341"/>
-    </row>
-    <row r="23" spans="1:22" s="326" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="348"/>
-      <c r="B23" s="443" t="s">
+      <c r="I22" s="436"/>
+      <c r="J22" s="437"/>
+      <c r="K22" s="435"/>
+      <c r="L22" s="437"/>
+      <c r="M22" s="347"/>
+      <c r="N22" s="347"/>
+      <c r="O22" s="347"/>
+      <c r="P22" s="340"/>
+      <c r="Q22" s="340"/>
+    </row>
+    <row r="23" spans="1:22" s="325" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="347"/>
+      <c r="B23" s="430" t="s">
         <v>212</v>
       </c>
-      <c r="C23" s="444"/>
-      <c r="D23" s="445"/>
-      <c r="E23" s="463"/>
-      <c r="F23" s="464"/>
-      <c r="G23" s="348"/>
-      <c r="H23" s="431" t="s">
+      <c r="C23" s="431"/>
+      <c r="D23" s="432"/>
+      <c r="E23" s="452"/>
+      <c r="F23" s="453"/>
+      <c r="G23" s="347"/>
+      <c r="H23" s="454" t="s">
         <v>213</v>
       </c>
-      <c r="I23" s="432"/>
-      <c r="J23" s="433"/>
-      <c r="K23" s="431"/>
-      <c r="L23" s="433"/>
-      <c r="M23" s="348"/>
-      <c r="N23" s="348"/>
-      <c r="O23" s="348"/>
-      <c r="P23" s="341"/>
-      <c r="Q23" s="341"/>
-    </row>
-    <row r="24" spans="1:22" s="326" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="348"/>
-      <c r="B24" s="351" t="s">
+      <c r="I23" s="455"/>
+      <c r="J23" s="456"/>
+      <c r="K23" s="454"/>
+      <c r="L23" s="456"/>
+      <c r="M23" s="347"/>
+      <c r="N23" s="347"/>
+      <c r="O23" s="347"/>
+      <c r="P23" s="340"/>
+      <c r="Q23" s="340"/>
+    </row>
+    <row r="24" spans="1:22" s="325" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="347"/>
+      <c r="B24" s="350" t="s">
         <v>214</v>
       </c>
-      <c r="C24" s="352"/>
-      <c r="D24" s="352"/>
-      <c r="E24" s="352"/>
-      <c r="F24" s="352"/>
-      <c r="G24" s="348"/>
-      <c r="H24" s="348"/>
-      <c r="I24" s="348"/>
-      <c r="J24" s="348"/>
-      <c r="K24" s="348"/>
-      <c r="L24" s="348"/>
-      <c r="M24" s="348"/>
-      <c r="N24" s="434"/>
-      <c r="O24" s="434"/>
-      <c r="P24" s="341"/>
-      <c r="Q24" s="341"/>
-    </row>
-    <row r="25" spans="1:22" s="326" customFormat="1" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="348"/>
-      <c r="B25" s="353"/>
-      <c r="C25" s="353"/>
-      <c r="D25" s="353"/>
-      <c r="E25" s="353"/>
-      <c r="F25" s="353"/>
-      <c r="G25" s="348"/>
-      <c r="H25" s="348"/>
-      <c r="I25" s="348"/>
-      <c r="J25" s="348"/>
-      <c r="K25" s="348"/>
-      <c r="L25" s="348"/>
-      <c r="M25" s="348"/>
-      <c r="N25" s="348"/>
-      <c r="O25" s="348"/>
-      <c r="P25" s="341"/>
-      <c r="Q25" s="341"/>
-    </row>
-    <row r="26" spans="1:22" s="326" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="348"/>
-      <c r="B26" s="451" t="s">
+      <c r="C24" s="351"/>
+      <c r="D24" s="351"/>
+      <c r="E24" s="351"/>
+      <c r="F24" s="351"/>
+      <c r="G24" s="347"/>
+      <c r="H24" s="347"/>
+      <c r="I24" s="347"/>
+      <c r="J24" s="347"/>
+      <c r="K24" s="347"/>
+      <c r="L24" s="347"/>
+      <c r="M24" s="347"/>
+      <c r="N24" s="457"/>
+      <c r="O24" s="457"/>
+      <c r="P24" s="340"/>
+      <c r="Q24" s="340"/>
+    </row>
+    <row r="25" spans="1:22" s="325" customFormat="1" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="347"/>
+      <c r="B25" s="352"/>
+      <c r="C25" s="352"/>
+      <c r="D25" s="352"/>
+      <c r="E25" s="352"/>
+      <c r="F25" s="352"/>
+      <c r="G25" s="347"/>
+      <c r="H25" s="347"/>
+      <c r="I25" s="347"/>
+      <c r="J25" s="347"/>
+      <c r="K25" s="347"/>
+      <c r="L25" s="347"/>
+      <c r="M25" s="347"/>
+      <c r="N25" s="347"/>
+      <c r="O25" s="347"/>
+      <c r="P25" s="340"/>
+      <c r="Q25" s="340"/>
+    </row>
+    <row r="26" spans="1:22" s="325" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="347"/>
+      <c r="B26" s="440" t="s">
         <v>25</v>
       </c>
-      <c r="C26" s="451"/>
-      <c r="D26" s="451"/>
-      <c r="E26" s="451"/>
-      <c r="F26" s="451"/>
-      <c r="G26" s="451"/>
-      <c r="H26" s="451"/>
-      <c r="I26" s="451"/>
-      <c r="J26" s="348"/>
-      <c r="K26" s="452" t="s">
+      <c r="C26" s="440"/>
+      <c r="D26" s="440"/>
+      <c r="E26" s="440"/>
+      <c r="F26" s="440"/>
+      <c r="G26" s="440"/>
+      <c r="H26" s="440"/>
+      <c r="I26" s="440"/>
+      <c r="J26" s="347"/>
+      <c r="K26" s="441" t="s">
         <v>215</v>
       </c>
-      <c r="L26" s="452"/>
-      <c r="M26" s="452"/>
-      <c r="N26" s="452"/>
-      <c r="O26" s="354"/>
-      <c r="P26" s="341"/>
-      <c r="Q26" s="341"/>
-    </row>
-    <row r="27" spans="1:22" s="326" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="348"/>
-      <c r="B27" s="436" t="s">
+      <c r="L26" s="441"/>
+      <c r="M26" s="441"/>
+      <c r="N26" s="441"/>
+      <c r="O26" s="353"/>
+      <c r="P26" s="340"/>
+      <c r="Q26" s="340"/>
+    </row>
+    <row r="27" spans="1:22" s="325" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="347"/>
+      <c r="B27" s="463" t="s">
         <v>216</v>
       </c>
-      <c r="C27" s="437"/>
-      <c r="D27" s="437"/>
-      <c r="E27" s="437"/>
-      <c r="F27" s="437"/>
-      <c r="G27" s="438"/>
-      <c r="H27" s="439"/>
-      <c r="I27" s="440"/>
-      <c r="J27" s="348"/>
-      <c r="K27" s="420" t="s">
+      <c r="C27" s="464"/>
+      <c r="D27" s="464"/>
+      <c r="E27" s="464"/>
+      <c r="F27" s="464"/>
+      <c r="G27" s="465"/>
+      <c r="H27" s="466"/>
+      <c r="I27" s="467"/>
+      <c r="J27" s="347"/>
+      <c r="K27" s="468" t="s">
         <v>217</v>
       </c>
-      <c r="L27" s="420"/>
-      <c r="M27" s="420"/>
-      <c r="N27" s="420"/>
-      <c r="O27" s="354"/>
-      <c r="P27" s="341"/>
-      <c r="Q27" s="341"/>
-    </row>
-    <row r="28" spans="1:22" s="326" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="348"/>
-      <c r="B28" s="355" t="s">
+      <c r="L27" s="468"/>
+      <c r="M27" s="468"/>
+      <c r="N27" s="468"/>
+      <c r="O27" s="353"/>
+      <c r="P27" s="340"/>
+      <c r="Q27" s="340"/>
+    </row>
+    <row r="28" spans="1:22" s="325" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="347"/>
+      <c r="B28" s="354" t="s">
         <v>218</v>
       </c>
-      <c r="C28" s="356"/>
-      <c r="D28" s="356"/>
-      <c r="E28" s="356"/>
-      <c r="F28" s="356"/>
-      <c r="G28" s="356"/>
-      <c r="H28" s="441"/>
-      <c r="I28" s="442"/>
-      <c r="J28" s="348"/>
-      <c r="K28" s="420" t="s">
+      <c r="C28" s="355"/>
+      <c r="D28" s="355"/>
+      <c r="E28" s="355"/>
+      <c r="F28" s="355"/>
+      <c r="G28" s="355"/>
+      <c r="H28" s="469"/>
+      <c r="I28" s="470"/>
+      <c r="J28" s="347"/>
+      <c r="K28" s="468" t="s">
         <v>219</v>
       </c>
-      <c r="L28" s="420"/>
-      <c r="M28" s="420"/>
-      <c r="N28" s="420"/>
-      <c r="O28" s="354"/>
-      <c r="P28" s="341"/>
-      <c r="Q28" s="341"/>
-    </row>
-    <row r="29" spans="1:22" s="326" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="348"/>
-      <c r="B29" s="355" t="s">
+      <c r="L28" s="468"/>
+      <c r="M28" s="468"/>
+      <c r="N28" s="468"/>
+      <c r="O28" s="353"/>
+      <c r="P28" s="340"/>
+      <c r="Q28" s="340"/>
+    </row>
+    <row r="29" spans="1:22" s="325" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="347"/>
+      <c r="B29" s="354" t="s">
         <v>220</v>
       </c>
-      <c r="C29" s="356"/>
-      <c r="D29" s="356"/>
-      <c r="E29" s="356"/>
-      <c r="F29" s="356"/>
-      <c r="G29" s="356"/>
-      <c r="H29" s="441"/>
-      <c r="I29" s="442"/>
-      <c r="J29" s="348"/>
-      <c r="K29" s="420" t="s">
+      <c r="C29" s="355"/>
+      <c r="D29" s="355"/>
+      <c r="E29" s="355"/>
+      <c r="F29" s="355"/>
+      <c r="G29" s="355"/>
+      <c r="H29" s="469"/>
+      <c r="I29" s="470"/>
+      <c r="J29" s="347"/>
+      <c r="K29" s="468" t="s">
         <v>221</v>
       </c>
-      <c r="L29" s="420"/>
-      <c r="M29" s="420"/>
-      <c r="N29" s="420"/>
-      <c r="O29" s="354"/>
-      <c r="P29" s="341"/>
-      <c r="Q29" s="341"/>
-    </row>
-    <row r="30" spans="1:22" s="326" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="348"/>
-      <c r="B30" s="348"/>
-      <c r="C30" s="348"/>
-      <c r="D30" s="348"/>
-      <c r="E30" s="348"/>
-      <c r="F30" s="348"/>
-      <c r="G30" s="348"/>
-      <c r="H30" s="348"/>
-      <c r="I30" s="348"/>
-      <c r="J30" s="348"/>
-      <c r="K30" s="357"/>
-      <c r="L30" s="348"/>
-      <c r="M30" s="348"/>
-      <c r="N30" s="348"/>
-      <c r="O30" s="348"/>
-      <c r="P30" s="341"/>
-      <c r="Q30" s="341"/>
-    </row>
-    <row r="31" spans="1:22" s="326" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="348"/>
-      <c r="B31" s="435" t="s">
+      <c r="L29" s="468"/>
+      <c r="M29" s="468"/>
+      <c r="N29" s="468"/>
+      <c r="O29" s="353"/>
+      <c r="P29" s="340"/>
+      <c r="Q29" s="340"/>
+    </row>
+    <row r="30" spans="1:22" s="325" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="347"/>
+      <c r="B30" s="347"/>
+      <c r="C30" s="347"/>
+      <c r="D30" s="347"/>
+      <c r="E30" s="347"/>
+      <c r="F30" s="347"/>
+      <c r="G30" s="347"/>
+      <c r="H30" s="347"/>
+      <c r="I30" s="347"/>
+      <c r="J30" s="347"/>
+      <c r="K30" s="356"/>
+      <c r="L30" s="347"/>
+      <c r="M30" s="347"/>
+      <c r="N30" s="347"/>
+      <c r="O30" s="347"/>
+      <c r="P30" s="340"/>
+      <c r="Q30" s="340"/>
+    </row>
+    <row r="31" spans="1:22" s="325" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="347"/>
+      <c r="B31" s="458" t="s">
         <v>222</v>
       </c>
-      <c r="C31" s="435"/>
-      <c r="D31" s="435"/>
-      <c r="E31" s="435"/>
-      <c r="F31" s="435"/>
-      <c r="G31" s="435"/>
-      <c r="H31" s="435"/>
-      <c r="I31" s="435"/>
-      <c r="J31" s="435"/>
-      <c r="K31" s="435"/>
-      <c r="L31" s="435"/>
-      <c r="M31" s="435"/>
-      <c r="N31" s="435"/>
-      <c r="O31" s="435"/>
-      <c r="P31" s="341"/>
-      <c r="Q31" s="341"/>
-    </row>
-    <row r="32" spans="1:22" s="326" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B32" s="358"/>
-      <c r="C32" s="349"/>
-      <c r="D32" s="349"/>
-      <c r="E32" s="349"/>
-      <c r="F32" s="349"/>
-      <c r="G32" s="349"/>
-      <c r="H32" s="349"/>
-      <c r="I32" s="349"/>
-      <c r="J32" s="349"/>
-      <c r="K32" s="349"/>
-      <c r="L32" s="349"/>
-      <c r="M32" s="349"/>
-      <c r="N32" s="349"/>
-      <c r="O32" s="349"/>
-      <c r="Q32" s="341"/>
-      <c r="T32" s="359"/>
-      <c r="U32" s="359"/>
-      <c r="V32" s="359"/>
-    </row>
-    <row r="33" spans="1:28" s="326" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B33" s="427" t="s">
+      <c r="C31" s="458"/>
+      <c r="D31" s="458"/>
+      <c r="E31" s="458"/>
+      <c r="F31" s="458"/>
+      <c r="G31" s="458"/>
+      <c r="H31" s="458"/>
+      <c r="I31" s="458"/>
+      <c r="J31" s="458"/>
+      <c r="K31" s="458"/>
+      <c r="L31" s="458"/>
+      <c r="M31" s="458"/>
+      <c r="N31" s="458"/>
+      <c r="O31" s="458"/>
+      <c r="P31" s="340"/>
+      <c r="Q31" s="340"/>
+    </row>
+    <row r="32" spans="1:22" s="325" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B32" s="357"/>
+      <c r="C32" s="348"/>
+      <c r="D32" s="348"/>
+      <c r="E32" s="348"/>
+      <c r="F32" s="348"/>
+      <c r="G32" s="348"/>
+      <c r="H32" s="348"/>
+      <c r="I32" s="348"/>
+      <c r="J32" s="348"/>
+      <c r="K32" s="348"/>
+      <c r="L32" s="348"/>
+      <c r="M32" s="348"/>
+      <c r="N32" s="348"/>
+      <c r="O32" s="348"/>
+      <c r="Q32" s="340"/>
+      <c r="T32" s="358"/>
+      <c r="U32" s="358"/>
+      <c r="V32" s="358"/>
+    </row>
+    <row r="33" spans="1:28" s="325" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B33" s="459" t="s">
         <v>41</v>
       </c>
-      <c r="C33" s="428"/>
-      <c r="D33" s="428"/>
-      <c r="E33" s="428"/>
-      <c r="F33" s="428"/>
-      <c r="G33" s="428"/>
-      <c r="H33" s="428"/>
-      <c r="I33" s="428"/>
-      <c r="J33" s="428"/>
-      <c r="K33" s="429"/>
-      <c r="L33" s="360" t="s">
+      <c r="C33" s="460"/>
+      <c r="D33" s="460"/>
+      <c r="E33" s="460"/>
+      <c r="F33" s="460"/>
+      <c r="G33" s="460"/>
+      <c r="H33" s="460"/>
+      <c r="I33" s="460"/>
+      <c r="J33" s="460"/>
+      <c r="K33" s="461"/>
+      <c r="L33" s="359" t="s">
         <v>223</v>
       </c>
-      <c r="M33" s="430" t="s">
+      <c r="M33" s="462" t="s">
         <v>18</v>
       </c>
-      <c r="N33" s="430"/>
-      <c r="O33" s="430"/>
-      <c r="Q33" s="341"/>
-      <c r="R33" s="361"/>
-      <c r="T33" s="359"/>
-      <c r="U33" s="359"/>
-      <c r="V33" s="359"/>
-    </row>
-    <row r="34" spans="1:28" s="326" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B34" s="362" t="s">
+      <c r="N33" s="462"/>
+      <c r="O33" s="462"/>
+      <c r="Q33" s="340"/>
+      <c r="R33" s="360"/>
+      <c r="T33" s="358"/>
+      <c r="U33" s="358"/>
+      <c r="V33" s="358"/>
+    </row>
+    <row r="34" spans="1:28" s="325" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B34" s="361" t="s">
         <v>45</v>
       </c>
-      <c r="C34" s="363" t="s">
+      <c r="C34" s="362" t="s">
         <v>46</v>
       </c>
       <c r="D34" s="69"/>
@@ -9216,23 +9345,23 @@
       <c r="H34" s="69"/>
       <c r="I34" s="69"/>
       <c r="J34" s="69"/>
-      <c r="K34" s="364"/>
+      <c r="K34" s="363"/>
       <c r="L34" s="61" t="s">
         <v>47</v>
       </c>
-      <c r="M34" s="391"/>
-      <c r="N34" s="393"/>
-      <c r="O34" s="392"/>
-      <c r="R34" s="365"/>
-      <c r="T34" s="365"/>
-      <c r="U34" s="359"/>
-      <c r="V34" s="359"/>
-    </row>
-    <row r="35" spans="1:28" s="326" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B35" s="362" t="s">
+      <c r="M34" s="390"/>
+      <c r="N34" s="392"/>
+      <c r="O34" s="391"/>
+      <c r="R34" s="364"/>
+      <c r="T34" s="364"/>
+      <c r="U34" s="358"/>
+      <c r="V34" s="358"/>
+    </row>
+    <row r="35" spans="1:28" s="325" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B35" s="361" t="s">
         <v>48</v>
       </c>
-      <c r="C35" s="363" t="s">
+      <c r="C35" s="362" t="s">
         <v>49</v>
       </c>
       <c r="D35" s="69"/>
@@ -9242,23 +9371,23 @@
       <c r="H35" s="69"/>
       <c r="I35" s="69"/>
       <c r="J35" s="69"/>
-      <c r="K35" s="364"/>
+      <c r="K35" s="363"/>
       <c r="L35" s="61" t="s">
         <v>47</v>
       </c>
-      <c r="M35" s="391"/>
-      <c r="N35" s="393"/>
-      <c r="O35" s="392"/>
-      <c r="R35" s="366"/>
-      <c r="T35" s="367"/>
-      <c r="U35" s="359"/>
-      <c r="V35" s="359"/>
-    </row>
-    <row r="36" spans="1:28" s="326" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B36" s="362" t="s">
+      <c r="M35" s="390"/>
+      <c r="N35" s="392"/>
+      <c r="O35" s="391"/>
+      <c r="R35" s="365"/>
+      <c r="T35" s="366"/>
+      <c r="U35" s="358"/>
+      <c r="V35" s="358"/>
+    </row>
+    <row r="36" spans="1:28" s="325" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B36" s="361" t="s">
         <v>50</v>
       </c>
-      <c r="C36" s="363" t="s">
+      <c r="C36" s="362" t="s">
         <v>224</v>
       </c>
       <c r="D36" s="69"/>
@@ -9268,415 +9397,415 @@
       <c r="H36" s="69"/>
       <c r="I36" s="69"/>
       <c r="J36" s="69"/>
-      <c r="K36" s="364"/>
-      <c r="L36" s="368" t="s">
+      <c r="K36" s="363"/>
+      <c r="L36" s="367" t="s">
         <v>47</v>
       </c>
-      <c r="M36" s="391"/>
-      <c r="N36" s="393"/>
-      <c r="O36" s="392"/>
-      <c r="R36" s="366"/>
-      <c r="T36" s="367"/>
-      <c r="U36" s="359"/>
-      <c r="V36" s="359"/>
-    </row>
-    <row r="37" spans="1:28" s="326" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B37" s="416" t="s">
+      <c r="M36" s="390"/>
+      <c r="N36" s="392"/>
+      <c r="O36" s="391"/>
+      <c r="R36" s="365"/>
+      <c r="T36" s="366"/>
+      <c r="U36" s="358"/>
+      <c r="V36" s="358"/>
+    </row>
+    <row r="37" spans="1:28" s="325" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B37" s="471" t="s">
         <v>52</v>
       </c>
-      <c r="C37" s="417" t="s">
+      <c r="C37" s="472" t="s">
         <v>53</v>
       </c>
-      <c r="D37" s="417"/>
-      <c r="E37" s="417"/>
-      <c r="F37" s="417"/>
-      <c r="G37" s="417"/>
-      <c r="H37" s="417"/>
-      <c r="I37" s="417"/>
-      <c r="J37" s="417"/>
-      <c r="K37" s="417"/>
-      <c r="L37" s="418" t="s">
+      <c r="D37" s="472"/>
+      <c r="E37" s="472"/>
+      <c r="F37" s="472"/>
+      <c r="G37" s="472"/>
+      <c r="H37" s="472"/>
+      <c r="I37" s="472"/>
+      <c r="J37" s="472"/>
+      <c r="K37" s="472"/>
+      <c r="L37" s="473" t="s">
         <v>47</v>
       </c>
-      <c r="M37" s="419"/>
-      <c r="N37" s="419"/>
-      <c r="O37" s="369"/>
-      <c r="R37" s="366"/>
-      <c r="T37" s="367"/>
-      <c r="U37" s="359"/>
-      <c r="V37" s="359"/>
-    </row>
-    <row r="38" spans="1:28" s="326" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B38" s="416"/>
-      <c r="C38" s="417"/>
-      <c r="D38" s="417"/>
-      <c r="E38" s="417"/>
-      <c r="F38" s="417"/>
-      <c r="G38" s="417"/>
-      <c r="H38" s="417"/>
-      <c r="I38" s="417"/>
-      <c r="J38" s="417"/>
-      <c r="K38" s="417"/>
-      <c r="L38" s="418"/>
-      <c r="M38" s="390" t="s">
+      <c r="M37" s="474"/>
+      <c r="N37" s="474"/>
+      <c r="O37" s="368"/>
+      <c r="R37" s="365"/>
+      <c r="T37" s="366"/>
+      <c r="U37" s="358"/>
+      <c r="V37" s="358"/>
+    </row>
+    <row r="38" spans="1:28" s="325" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B38" s="471"/>
+      <c r="C38" s="472"/>
+      <c r="D38" s="472"/>
+      <c r="E38" s="472"/>
+      <c r="F38" s="472"/>
+      <c r="G38" s="472"/>
+      <c r="H38" s="472"/>
+      <c r="I38" s="472"/>
+      <c r="J38" s="472"/>
+      <c r="K38" s="472"/>
+      <c r="L38" s="473"/>
+      <c r="M38" s="389" t="s">
         <v>225</v>
       </c>
-      <c r="N38" s="390"/>
-      <c r="O38" s="390"/>
-      <c r="R38" s="366"/>
-      <c r="T38" s="367"/>
-      <c r="U38" s="359"/>
-      <c r="V38" s="359"/>
-    </row>
-    <row r="39" spans="1:28" s="326" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B39" s="370" t="s">
+      <c r="N38" s="389"/>
+      <c r="O38" s="389"/>
+      <c r="R38" s="365"/>
+      <c r="T38" s="366"/>
+      <c r="U38" s="358"/>
+      <c r="V38" s="358"/>
+    </row>
+    <row r="39" spans="1:28" s="325" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B39" s="369" t="s">
         <v>226</v>
       </c>
-      <c r="R39" s="366"/>
-      <c r="T39" s="367"/>
-      <c r="U39" s="359"/>
-      <c r="V39" s="359"/>
-    </row>
-    <row r="40" spans="1:28" s="326" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B40" s="427" t="s">
+      <c r="R39" s="365"/>
+      <c r="T39" s="366"/>
+      <c r="U39" s="358"/>
+      <c r="V39" s="358"/>
+    </row>
+    <row r="40" spans="1:28" s="325" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B40" s="459" t="s">
         <v>41</v>
       </c>
-      <c r="C40" s="428"/>
-      <c r="D40" s="428"/>
-      <c r="E40" s="428"/>
-      <c r="F40" s="428"/>
-      <c r="G40" s="428"/>
-      <c r="H40" s="428"/>
-      <c r="I40" s="428"/>
-      <c r="J40" s="428"/>
-      <c r="K40" s="429"/>
-      <c r="L40" s="360" t="s">
+      <c r="C40" s="460"/>
+      <c r="D40" s="460"/>
+      <c r="E40" s="460"/>
+      <c r="F40" s="460"/>
+      <c r="G40" s="460"/>
+      <c r="H40" s="460"/>
+      <c r="I40" s="460"/>
+      <c r="J40" s="460"/>
+      <c r="K40" s="461"/>
+      <c r="L40" s="359" t="s">
         <v>223</v>
       </c>
-      <c r="M40" s="430" t="s">
+      <c r="M40" s="462" t="s">
         <v>18</v>
       </c>
-      <c r="N40" s="430"/>
-      <c r="O40" s="430"/>
-      <c r="Q40" s="341"/>
-      <c r="R40" s="361"/>
-      <c r="S40" s="359"/>
-      <c r="T40" s="359"/>
-      <c r="U40" s="359"/>
-      <c r="V40" s="359"/>
-    </row>
-    <row r="41" spans="1:28" s="326" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B41" s="362" t="s">
+      <c r="N40" s="462"/>
+      <c r="O40" s="462"/>
+      <c r="Q40" s="340"/>
+      <c r="R40" s="360"/>
+      <c r="S40" s="358"/>
+      <c r="T40" s="358"/>
+      <c r="U40" s="358"/>
+      <c r="V40" s="358"/>
+    </row>
+    <row r="41" spans="1:28" s="325" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B41" s="361" t="s">
         <v>45</v>
       </c>
-      <c r="C41" s="421" t="s">
+      <c r="C41" s="475" t="s">
         <v>46</v>
       </c>
-      <c r="D41" s="422"/>
-      <c r="E41" s="422"/>
-      <c r="F41" s="422"/>
-      <c r="G41" s="422"/>
-      <c r="H41" s="422"/>
-      <c r="I41" s="422"/>
-      <c r="J41" s="422"/>
-      <c r="K41" s="423"/>
+      <c r="D41" s="476"/>
+      <c r="E41" s="476"/>
+      <c r="F41" s="476"/>
+      <c r="G41" s="476"/>
+      <c r="H41" s="476"/>
+      <c r="I41" s="476"/>
+      <c r="J41" s="476"/>
+      <c r="K41" s="477"/>
       <c r="L41" s="61" t="s">
         <v>47</v>
       </c>
-      <c r="M41" s="419"/>
-      <c r="N41" s="419"/>
-      <c r="O41" s="419"/>
-      <c r="Q41" s="341"/>
-      <c r="R41" s="361"/>
-      <c r="S41" s="359"/>
-      <c r="T41" s="359"/>
-      <c r="U41" s="359"/>
-      <c r="V41" s="359"/>
-    </row>
-    <row r="42" spans="1:28" s="326" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B42" s="362" t="s">
+      <c r="M41" s="474"/>
+      <c r="N41" s="474"/>
+      <c r="O41" s="474"/>
+      <c r="Q41" s="340"/>
+      <c r="R41" s="360"/>
+      <c r="S41" s="358"/>
+      <c r="T41" s="358"/>
+      <c r="U41" s="358"/>
+      <c r="V41" s="358"/>
+    </row>
+    <row r="42" spans="1:28" s="325" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B42" s="361" t="s">
         <v>48</v>
       </c>
-      <c r="C42" s="421" t="s">
+      <c r="C42" s="475" t="s">
         <v>49</v>
       </c>
-      <c r="D42" s="422"/>
-      <c r="E42" s="422"/>
-      <c r="F42" s="422"/>
-      <c r="G42" s="422"/>
-      <c r="H42" s="422"/>
-      <c r="I42" s="422"/>
-      <c r="J42" s="422"/>
-      <c r="K42" s="423"/>
+      <c r="D42" s="476"/>
+      <c r="E42" s="476"/>
+      <c r="F42" s="476"/>
+      <c r="G42" s="476"/>
+      <c r="H42" s="476"/>
+      <c r="I42" s="476"/>
+      <c r="J42" s="476"/>
+      <c r="K42" s="477"/>
       <c r="L42" s="61" t="s">
         <v>47</v>
       </c>
-      <c r="M42" s="419"/>
-      <c r="N42" s="419"/>
-      <c r="O42" s="419"/>
-      <c r="Q42" s="341"/>
-      <c r="R42" s="361"/>
-      <c r="S42" s="359"/>
-      <c r="T42" s="359"/>
-      <c r="U42" s="359"/>
-      <c r="V42" s="359"/>
-    </row>
-    <row r="43" spans="1:28" s="326" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B43" s="362" t="s">
+      <c r="M42" s="474"/>
+      <c r="N42" s="474"/>
+      <c r="O42" s="474"/>
+      <c r="Q42" s="340"/>
+      <c r="R42" s="360"/>
+      <c r="S42" s="358"/>
+      <c r="T42" s="358"/>
+      <c r="U42" s="358"/>
+      <c r="V42" s="358"/>
+    </row>
+    <row r="43" spans="1:28" s="325" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B43" s="361" t="s">
         <v>50</v>
       </c>
-      <c r="C43" s="421" t="s">
+      <c r="C43" s="475" t="s">
         <v>224</v>
       </c>
-      <c r="D43" s="422"/>
-      <c r="E43" s="422"/>
-      <c r="F43" s="422"/>
-      <c r="G43" s="422"/>
-      <c r="H43" s="422"/>
-      <c r="I43" s="422"/>
-      <c r="J43" s="422"/>
-      <c r="K43" s="423"/>
-      <c r="L43" s="368" t="s">
+      <c r="D43" s="476"/>
+      <c r="E43" s="476"/>
+      <c r="F43" s="476"/>
+      <c r="G43" s="476"/>
+      <c r="H43" s="476"/>
+      <c r="I43" s="476"/>
+      <c r="J43" s="476"/>
+      <c r="K43" s="477"/>
+      <c r="L43" s="367" t="s">
         <v>47</v>
       </c>
-      <c r="M43" s="424"/>
-      <c r="N43" s="425"/>
-      <c r="O43" s="426"/>
-      <c r="Q43" s="341"/>
-      <c r="R43" s="361"/>
-      <c r="S43" s="359"/>
-      <c r="T43" s="359"/>
-      <c r="U43" s="359"/>
-      <c r="V43" s="359"/>
-    </row>
-    <row r="44" spans="1:28" s="326" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B44" s="416" t="s">
+      <c r="M43" s="438"/>
+      <c r="N43" s="478"/>
+      <c r="O43" s="439"/>
+      <c r="Q43" s="340"/>
+      <c r="R43" s="360"/>
+      <c r="S43" s="358"/>
+      <c r="T43" s="358"/>
+      <c r="U43" s="358"/>
+      <c r="V43" s="358"/>
+    </row>
+    <row r="44" spans="1:28" s="325" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B44" s="471" t="s">
         <v>52</v>
       </c>
-      <c r="C44" s="417" t="s">
+      <c r="C44" s="472" t="s">
         <v>53</v>
       </c>
-      <c r="D44" s="417"/>
-      <c r="E44" s="417"/>
-      <c r="F44" s="417"/>
-      <c r="G44" s="417"/>
-      <c r="H44" s="417"/>
-      <c r="I44" s="417"/>
-      <c r="J44" s="417"/>
-      <c r="K44" s="417"/>
-      <c r="L44" s="418" t="s">
+      <c r="D44" s="472"/>
+      <c r="E44" s="472"/>
+      <c r="F44" s="472"/>
+      <c r="G44" s="472"/>
+      <c r="H44" s="472"/>
+      <c r="I44" s="472"/>
+      <c r="J44" s="472"/>
+      <c r="K44" s="472"/>
+      <c r="L44" s="473" t="s">
         <v>47</v>
       </c>
-      <c r="M44" s="419"/>
-      <c r="N44" s="419"/>
-      <c r="O44" s="369"/>
-      <c r="R44" s="361"/>
-      <c r="S44" s="359"/>
-      <c r="T44" s="359"/>
-      <c r="U44" s="359"/>
-      <c r="V44" s="359"/>
-    </row>
-    <row r="45" spans="1:28" s="326" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B45" s="416"/>
-      <c r="C45" s="417"/>
-      <c r="D45" s="417"/>
-      <c r="E45" s="417"/>
-      <c r="F45" s="417"/>
-      <c r="G45" s="417"/>
-      <c r="H45" s="417"/>
-      <c r="I45" s="417"/>
-      <c r="J45" s="417"/>
-      <c r="K45" s="417"/>
-      <c r="L45" s="418"/>
-      <c r="M45" s="420" t="s">
+      <c r="M44" s="474"/>
+      <c r="N44" s="474"/>
+      <c r="O44" s="368"/>
+      <c r="R44" s="360"/>
+      <c r="S44" s="358"/>
+      <c r="T44" s="358"/>
+      <c r="U44" s="358"/>
+      <c r="V44" s="358"/>
+    </row>
+    <row r="45" spans="1:28" s="325" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B45" s="471"/>
+      <c r="C45" s="472"/>
+      <c r="D45" s="472"/>
+      <c r="E45" s="472"/>
+      <c r="F45" s="472"/>
+      <c r="G45" s="472"/>
+      <c r="H45" s="472"/>
+      <c r="I45" s="472"/>
+      <c r="J45" s="472"/>
+      <c r="K45" s="472"/>
+      <c r="L45" s="473"/>
+      <c r="M45" s="468" t="s">
         <v>225</v>
       </c>
-      <c r="N45" s="420"/>
-      <c r="O45" s="420"/>
-      <c r="Q45" s="341"/>
-      <c r="S45" s="414"/>
-      <c r="T45" s="414"/>
-      <c r="U45" s="414"/>
-      <c r="V45" s="414"/>
-      <c r="W45" s="414"/>
-      <c r="X45" s="372"/>
-      <c r="Y45" s="409"/>
-      <c r="Z45" s="409"/>
-      <c r="AA45" s="409"/>
-      <c r="AB45" s="409"/>
-    </row>
-    <row r="46" spans="1:28" s="326" customFormat="1" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K46" s="374"/>
-      <c r="L46" s="375"/>
-      <c r="M46" s="376"/>
-      <c r="N46" s="376"/>
-      <c r="O46" s="376"/>
-      <c r="Q46" s="341"/>
-      <c r="S46" s="371"/>
-      <c r="T46" s="371"/>
-      <c r="U46" s="371"/>
-      <c r="V46" s="371"/>
-      <c r="W46" s="371"/>
-      <c r="X46" s="372"/>
-      <c r="Y46" s="373"/>
-      <c r="Z46" s="373"/>
-      <c r="AA46" s="373"/>
-      <c r="AB46" s="373"/>
-    </row>
-    <row r="47" spans="1:28" s="326" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N45" s="468"/>
+      <c r="O45" s="468"/>
+      <c r="Q45" s="340"/>
+      <c r="S45" s="485"/>
+      <c r="T45" s="485"/>
+      <c r="U45" s="485"/>
+      <c r="V45" s="485"/>
+      <c r="W45" s="485"/>
+      <c r="X45" s="371"/>
+      <c r="Y45" s="480"/>
+      <c r="Z45" s="480"/>
+      <c r="AA45" s="480"/>
+      <c r="AB45" s="480"/>
+    </row>
+    <row r="46" spans="1:28" s="325" customFormat="1" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K46" s="373"/>
+      <c r="L46" s="374"/>
+      <c r="M46" s="375"/>
+      <c r="N46" s="375"/>
+      <c r="O46" s="375"/>
+      <c r="Q46" s="340"/>
+      <c r="S46" s="370"/>
+      <c r="T46" s="370"/>
+      <c r="U46" s="370"/>
+      <c r="V46" s="370"/>
+      <c r="W46" s="370"/>
+      <c r="X46" s="371"/>
+      <c r="Y46" s="372"/>
+      <c r="Z46" s="372"/>
+      <c r="AA46" s="372"/>
+      <c r="AB46" s="372"/>
+    </row>
+    <row r="47" spans="1:28" s="325" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="53"/>
-      <c r="B47" s="410" t="s">
+      <c r="B47" s="481" t="s">
         <v>227</v>
       </c>
-      <c r="C47" s="410"/>
-      <c r="D47" s="410"/>
-      <c r="E47" s="410"/>
-      <c r="F47" s="410"/>
-      <c r="G47" s="410"/>
-      <c r="H47" s="410"/>
-      <c r="I47" s="410"/>
-      <c r="J47" s="410"/>
-      <c r="K47" s="410"/>
-      <c r="L47" s="410"/>
-      <c r="M47" s="410"/>
-      <c r="N47" s="410"/>
-      <c r="O47" s="410"/>
-      <c r="Q47" s="341"/>
-      <c r="S47" s="411"/>
-      <c r="T47" s="412"/>
-      <c r="U47" s="412"/>
-      <c r="V47" s="412"/>
-      <c r="W47" s="375"/>
-      <c r="X47" s="372"/>
-      <c r="Y47" s="413"/>
-      <c r="Z47" s="413"/>
-      <c r="AA47" s="377"/>
-      <c r="AB47" s="377"/>
-    </row>
-    <row r="48" spans="1:28" s="326" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="378" t="s">
+      <c r="C47" s="481"/>
+      <c r="D47" s="481"/>
+      <c r="E47" s="481"/>
+      <c r="F47" s="481"/>
+      <c r="G47" s="481"/>
+      <c r="H47" s="481"/>
+      <c r="I47" s="481"/>
+      <c r="J47" s="481"/>
+      <c r="K47" s="481"/>
+      <c r="L47" s="481"/>
+      <c r="M47" s="481"/>
+      <c r="N47" s="481"/>
+      <c r="O47" s="481"/>
+      <c r="Q47" s="340"/>
+      <c r="S47" s="482"/>
+      <c r="T47" s="483"/>
+      <c r="U47" s="483"/>
+      <c r="V47" s="483"/>
+      <c r="W47" s="374"/>
+      <c r="X47" s="371"/>
+      <c r="Y47" s="484"/>
+      <c r="Z47" s="484"/>
+      <c r="AA47" s="376"/>
+      <c r="AB47" s="376"/>
+    </row>
+    <row r="48" spans="1:28" s="325" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="377" t="s">
         <v>33</v>
       </c>
-      <c r="B48" s="379"/>
-      <c r="C48" s="380"/>
-      <c r="D48" s="381"/>
-      <c r="E48" s="381"/>
-      <c r="F48" s="381"/>
-      <c r="G48" s="382"/>
-      <c r="H48" s="382"/>
-      <c r="I48" s="382"/>
-      <c r="J48" s="382"/>
-      <c r="K48" s="382"/>
-      <c r="L48" s="382"/>
-      <c r="M48" s="382"/>
-      <c r="N48" s="382"/>
-      <c r="O48" s="382"/>
-      <c r="P48" s="341"/>
-      <c r="Q48" s="341"/>
-    </row>
-    <row r="49" spans="1:17" s="326" customFormat="1" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B49" s="379"/>
-      <c r="C49" s="380"/>
-      <c r="D49" s="380"/>
-      <c r="E49" s="380"/>
-      <c r="F49" s="380"/>
-      <c r="P49" s="341"/>
-      <c r="Q49" s="341"/>
-    </row>
-    <row r="50" spans="1:17" s="326" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="383"/>
-      <c r="B50" s="379"/>
-      <c r="C50" s="380"/>
-      <c r="D50" s="380"/>
-      <c r="E50" s="380"/>
-      <c r="F50" s="380"/>
-      <c r="G50" s="384"/>
-      <c r="H50" s="384"/>
-      <c r="I50" s="384"/>
-      <c r="J50" s="384"/>
-      <c r="K50" s="384"/>
-      <c r="L50" s="384"/>
-      <c r="M50" s="385"/>
-      <c r="N50" s="385"/>
-      <c r="O50" s="386"/>
-      <c r="P50" s="341"/>
-      <c r="Q50" s="341"/>
-    </row>
-    <row r="51" spans="1:17" s="326" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="383"/>
-      <c r="G51" s="384"/>
-      <c r="H51" s="384"/>
-      <c r="I51" s="384"/>
-      <c r="J51" s="384"/>
-      <c r="K51" s="384"/>
-      <c r="L51" s="384"/>
-      <c r="M51" s="385"/>
-      <c r="N51" s="385"/>
-      <c r="O51" s="386"/>
-      <c r="P51" s="341"/>
-      <c r="Q51" s="341"/>
-    </row>
-    <row r="52" spans="1:17" s="326" customFormat="1" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="387" t="s">
+      <c r="B48" s="378"/>
+      <c r="C48" s="379"/>
+      <c r="D48" s="380"/>
+      <c r="E48" s="380"/>
+      <c r="F48" s="380"/>
+      <c r="G48" s="381"/>
+      <c r="H48" s="381"/>
+      <c r="I48" s="381"/>
+      <c r="J48" s="381"/>
+      <c r="K48" s="381"/>
+      <c r="L48" s="381"/>
+      <c r="M48" s="381"/>
+      <c r="N48" s="381"/>
+      <c r="O48" s="381"/>
+      <c r="P48" s="340"/>
+      <c r="Q48" s="340"/>
+    </row>
+    <row r="49" spans="1:17" s="325" customFormat="1" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B49" s="378"/>
+      <c r="C49" s="379"/>
+      <c r="D49" s="379"/>
+      <c r="E49" s="379"/>
+      <c r="F49" s="379"/>
+      <c r="P49" s="340"/>
+      <c r="Q49" s="340"/>
+    </row>
+    <row r="50" spans="1:17" s="325" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A50" s="382"/>
+      <c r="B50" s="378"/>
+      <c r="C50" s="379"/>
+      <c r="D50" s="379"/>
+      <c r="E50" s="379"/>
+      <c r="F50" s="379"/>
+      <c r="G50" s="383"/>
+      <c r="H50" s="383"/>
+      <c r="I50" s="383"/>
+      <c r="J50" s="383"/>
+      <c r="K50" s="383"/>
+      <c r="L50" s="383"/>
+      <c r="M50" s="384"/>
+      <c r="N50" s="384"/>
+      <c r="O50" s="385"/>
+      <c r="P50" s="340"/>
+      <c r="Q50" s="340"/>
+    </row>
+    <row r="51" spans="1:17" s="325" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A51" s="382"/>
+      <c r="G51" s="383"/>
+      <c r="H51" s="383"/>
+      <c r="I51" s="383"/>
+      <c r="J51" s="383"/>
+      <c r="K51" s="383"/>
+      <c r="L51" s="383"/>
+      <c r="M51" s="384"/>
+      <c r="N51" s="384"/>
+      <c r="O51" s="385"/>
+      <c r="P51" s="340"/>
+      <c r="Q51" s="340"/>
+    </row>
+    <row r="52" spans="1:17" s="325" customFormat="1" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A52" s="386" t="s">
         <v>34</v>
       </c>
-      <c r="B52" s="380"/>
-      <c r="C52" s="380"/>
-      <c r="D52" s="380"/>
-      <c r="E52" s="380"/>
-      <c r="F52" s="380"/>
-      <c r="G52" s="380"/>
-      <c r="H52" s="380"/>
-      <c r="I52" s="380"/>
-      <c r="J52" s="380"/>
-      <c r="K52" s="380"/>
-      <c r="L52" s="380"/>
-      <c r="M52" s="380"/>
-      <c r="N52" s="380"/>
-      <c r="O52" s="380"/>
-      <c r="P52" s="341"/>
-      <c r="Q52" s="341"/>
-    </row>
-    <row r="53" spans="1:17" s="326" customFormat="1" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="349" t="s">
+      <c r="B52" s="379"/>
+      <c r="C52" s="379"/>
+      <c r="D52" s="379"/>
+      <c r="E52" s="379"/>
+      <c r="F52" s="379"/>
+      <c r="G52" s="379"/>
+      <c r="H52" s="379"/>
+      <c r="I52" s="379"/>
+      <c r="J52" s="379"/>
+      <c r="K52" s="379"/>
+      <c r="L52" s="379"/>
+      <c r="M52" s="379"/>
+      <c r="N52" s="379"/>
+      <c r="O52" s="379"/>
+      <c r="P52" s="340"/>
+      <c r="Q52" s="340"/>
+    </row>
+    <row r="53" spans="1:17" s="325" customFormat="1" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A53" s="348" t="s">
         <v>228</v>
       </c>
-      <c r="B53" s="380"/>
-      <c r="C53" s="380"/>
-      <c r="D53" s="380"/>
-      <c r="F53" s="380"/>
-      <c r="G53" s="380"/>
-      <c r="H53" s="388" t="s">
+      <c r="B53" s="379"/>
+      <c r="C53" s="379"/>
+      <c r="D53" s="379"/>
+      <c r="F53" s="379"/>
+      <c r="G53" s="379"/>
+      <c r="H53" s="387" t="s">
         <v>229</v>
       </c>
-      <c r="J53" s="380"/>
-      <c r="K53" s="380"/>
-      <c r="L53" s="380"/>
-      <c r="M53" s="380"/>
-      <c r="N53" s="380"/>
-      <c r="O53" s="380"/>
-      <c r="P53" s="341"/>
-      <c r="Q53" s="341"/>
-    </row>
-    <row r="54" spans="1:17" s="326" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="55" spans="1:17" s="326" customFormat="1" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="415" t="s">
+      <c r="J53" s="379"/>
+      <c r="K53" s="379"/>
+      <c r="L53" s="379"/>
+      <c r="M53" s="379"/>
+      <c r="N53" s="379"/>
+      <c r="O53" s="379"/>
+      <c r="P53" s="340"/>
+      <c r="Q53" s="340"/>
+    </row>
+    <row r="54" spans="1:17" s="325" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="55" spans="1:17" s="325" customFormat="1" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A55" s="479" t="s">
         <v>230</v>
       </c>
-      <c r="B55" s="415"/>
-      <c r="C55" s="415"/>
-      <c r="D55" s="415"/>
-      <c r="E55" s="415"/>
-      <c r="F55" s="415"/>
-      <c r="G55" s="415"/>
-      <c r="H55" s="415"/>
-      <c r="I55" s="415"/>
-      <c r="J55" s="415"/>
-      <c r="K55" s="415"/>
-      <c r="L55" s="415"/>
-      <c r="M55" s="415"/>
-      <c r="N55" s="415"/>
-      <c r="O55" s="415"/>
+      <c r="B55" s="479"/>
+      <c r="C55" s="479"/>
+      <c r="D55" s="479"/>
+      <c r="E55" s="479"/>
+      <c r="F55" s="479"/>
+      <c r="G55" s="479"/>
+      <c r="H55" s="479"/>
+      <c r="I55" s="479"/>
+      <c r="J55" s="479"/>
+      <c r="K55" s="479"/>
+      <c r="L55" s="479"/>
+      <c r="M55" s="479"/>
+      <c r="N55" s="479"/>
+      <c r="O55" s="479"/>
     </row>
   </sheetData>
   <protectedRanges>
@@ -9684,27 +9813,43 @@
     <protectedRange sqref="C10:C11 D11" name="Rango3_3_1_1_1_1_1_2_1"/>
   </protectedRanges>
   <mergeCells count="74">
-    <mergeCell ref="A14:O14"/>
-    <mergeCell ref="B16:F16"/>
-    <mergeCell ref="H16:J16"/>
-    <mergeCell ref="B11:D11"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="I11:K11"/>
-    <mergeCell ref="M11:O11"/>
-    <mergeCell ref="A13:O13"/>
-    <mergeCell ref="K16:L16"/>
-    <mergeCell ref="A7:O7"/>
-    <mergeCell ref="A8:O8"/>
-    <mergeCell ref="F10:G10"/>
-    <mergeCell ref="I10:K10"/>
-    <mergeCell ref="M10:O10"/>
-    <mergeCell ref="B18:D18"/>
-    <mergeCell ref="E18:F18"/>
-    <mergeCell ref="H18:J18"/>
-    <mergeCell ref="K18:L18"/>
-    <mergeCell ref="B17:D17"/>
-    <mergeCell ref="H17:J17"/>
-    <mergeCell ref="K17:L17"/>
+    <mergeCell ref="Y45:Z45"/>
+    <mergeCell ref="AA45:AB45"/>
+    <mergeCell ref="B47:O47"/>
+    <mergeCell ref="S47:V47"/>
+    <mergeCell ref="Y47:Z47"/>
+    <mergeCell ref="S45:W45"/>
+    <mergeCell ref="A55:O55"/>
+    <mergeCell ref="B44:B45"/>
+    <mergeCell ref="C44:K45"/>
+    <mergeCell ref="L44:L45"/>
+    <mergeCell ref="M44:N44"/>
+    <mergeCell ref="M45:O45"/>
+    <mergeCell ref="C41:K41"/>
+    <mergeCell ref="M41:O41"/>
+    <mergeCell ref="C42:K42"/>
+    <mergeCell ref="M42:O42"/>
+    <mergeCell ref="C43:K43"/>
+    <mergeCell ref="M43:O43"/>
+    <mergeCell ref="B37:B38"/>
+    <mergeCell ref="C37:K38"/>
+    <mergeCell ref="L37:L38"/>
+    <mergeCell ref="M37:N37"/>
+    <mergeCell ref="B40:K40"/>
+    <mergeCell ref="M40:O40"/>
+    <mergeCell ref="H23:J23"/>
+    <mergeCell ref="K23:L23"/>
+    <mergeCell ref="N24:O24"/>
+    <mergeCell ref="B31:O31"/>
+    <mergeCell ref="B33:K33"/>
+    <mergeCell ref="M33:O33"/>
+    <mergeCell ref="B27:G27"/>
+    <mergeCell ref="H27:I27"/>
+    <mergeCell ref="K27:N27"/>
+    <mergeCell ref="H28:I28"/>
+    <mergeCell ref="K28:N28"/>
+    <mergeCell ref="H29:I29"/>
+    <mergeCell ref="K29:N29"/>
     <mergeCell ref="B19:D19"/>
     <mergeCell ref="E19:F19"/>
     <mergeCell ref="H19:J19"/>
@@ -9721,43 +9866,27 @@
     <mergeCell ref="K22:L22"/>
     <mergeCell ref="B23:D23"/>
     <mergeCell ref="E23:F23"/>
-    <mergeCell ref="H23:J23"/>
-    <mergeCell ref="K23:L23"/>
-    <mergeCell ref="N24:O24"/>
-    <mergeCell ref="B31:O31"/>
-    <mergeCell ref="B33:K33"/>
-    <mergeCell ref="M33:O33"/>
-    <mergeCell ref="B27:G27"/>
-    <mergeCell ref="H27:I27"/>
-    <mergeCell ref="K27:N27"/>
-    <mergeCell ref="H28:I28"/>
-    <mergeCell ref="K28:N28"/>
-    <mergeCell ref="H29:I29"/>
-    <mergeCell ref="K29:N29"/>
-    <mergeCell ref="B37:B38"/>
-    <mergeCell ref="C37:K38"/>
-    <mergeCell ref="L37:L38"/>
-    <mergeCell ref="M37:N37"/>
-    <mergeCell ref="B40:K40"/>
-    <mergeCell ref="M40:O40"/>
-    <mergeCell ref="C41:K41"/>
-    <mergeCell ref="M41:O41"/>
-    <mergeCell ref="C42:K42"/>
-    <mergeCell ref="M42:O42"/>
-    <mergeCell ref="C43:K43"/>
-    <mergeCell ref="M43:O43"/>
-    <mergeCell ref="A55:O55"/>
-    <mergeCell ref="B44:B45"/>
-    <mergeCell ref="C44:K45"/>
-    <mergeCell ref="L44:L45"/>
-    <mergeCell ref="M44:N44"/>
-    <mergeCell ref="M45:O45"/>
-    <mergeCell ref="Y45:Z45"/>
-    <mergeCell ref="AA45:AB45"/>
-    <mergeCell ref="B47:O47"/>
-    <mergeCell ref="S47:V47"/>
-    <mergeCell ref="Y47:Z47"/>
-    <mergeCell ref="S45:W45"/>
+    <mergeCell ref="B18:D18"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="H18:J18"/>
+    <mergeCell ref="K18:L18"/>
+    <mergeCell ref="B17:D17"/>
+    <mergeCell ref="H17:J17"/>
+    <mergeCell ref="K17:L17"/>
+    <mergeCell ref="A7:O7"/>
+    <mergeCell ref="A8:O8"/>
+    <mergeCell ref="F10:G10"/>
+    <mergeCell ref="I10:K10"/>
+    <mergeCell ref="M10:O10"/>
+    <mergeCell ref="A14:O14"/>
+    <mergeCell ref="B16:F16"/>
+    <mergeCell ref="H16:J16"/>
+    <mergeCell ref="B11:D11"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="I11:K11"/>
+    <mergeCell ref="M11:O11"/>
+    <mergeCell ref="A13:O13"/>
+    <mergeCell ref="K16:L16"/>
   </mergeCells>
   <conditionalFormatting sqref="B36">
     <cfRule type="cellIs" priority="2" stopIfTrue="1" operator="between">
@@ -9797,36 +9926,36 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="491" t="s">
+      <c r="A2" s="490" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="491"/>
-      <c r="C2" s="491"/>
-      <c r="D2" s="491"/>
-      <c r="E2" s="491"/>
-      <c r="F2" s="491"/>
-      <c r="G2" s="491"/>
-      <c r="H2" s="491"/>
-      <c r="I2" s="491"/>
-      <c r="J2" s="491"/>
-      <c r="K2" s="491"/>
-      <c r="L2" s="491"/>
+      <c r="B2" s="490"/>
+      <c r="C2" s="490"/>
+      <c r="D2" s="490"/>
+      <c r="E2" s="490"/>
+      <c r="F2" s="490"/>
+      <c r="G2" s="490"/>
+      <c r="H2" s="490"/>
+      <c r="I2" s="490"/>
+      <c r="J2" s="490"/>
+      <c r="K2" s="490"/>
+      <c r="L2" s="490"/>
     </row>
     <row r="3" spans="1:12" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="498">
+      <c r="A3" s="497">
         <v>0</v>
       </c>
-      <c r="B3" s="498"/>
-      <c r="C3" s="498"/>
-      <c r="D3" s="498"/>
-      <c r="E3" s="498"/>
-      <c r="F3" s="498"/>
-      <c r="G3" s="498"/>
-      <c r="H3" s="498"/>
-      <c r="I3" s="498"/>
-      <c r="J3" s="498"/>
-      <c r="K3" s="498"/>
-      <c r="L3" s="498"/>
+      <c r="B3" s="497"/>
+      <c r="C3" s="497"/>
+      <c r="D3" s="497"/>
+      <c r="E3" s="497"/>
+      <c r="F3" s="497"/>
+      <c r="G3" s="497"/>
+      <c r="H3" s="497"/>
+      <c r="I3" s="497"/>
+      <c r="J3" s="497"/>
+      <c r="K3" s="497"/>
+      <c r="L3" s="497"/>
     </row>
     <row r="4" spans="1:12" ht="15.9" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="5" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -9836,16 +9965,16 @@
       <c r="B5" s="23" t="s">
         <v>2</v>
       </c>
-      <c r="C5" s="501">
+      <c r="C5" s="500">
         <f>+'FORMATO PEG'!U2</f>
         <v>0</v>
       </c>
-      <c r="D5" s="501"/>
-      <c r="E5" s="501"/>
-      <c r="F5" s="501"/>
-      <c r="G5" s="501"/>
-      <c r="H5" s="501"/>
-      <c r="I5" s="501"/>
+      <c r="D5" s="500"/>
+      <c r="E5" s="500"/>
+      <c r="F5" s="500"/>
+      <c r="G5" s="500"/>
+      <c r="H5" s="500"/>
+      <c r="I5" s="500"/>
       <c r="J5" s="25" t="s">
         <v>3</v>
       </c>
@@ -9863,23 +9992,23 @@
       <c r="B6" s="23" t="s">
         <v>2</v>
       </c>
-      <c r="C6" s="501">
+      <c r="C6" s="500">
         <f>+'FORMATO PEG'!U3</f>
         <v>0</v>
       </c>
-      <c r="D6" s="501"/>
-      <c r="E6" s="501"/>
-      <c r="F6" s="501"/>
-      <c r="G6" s="501"/>
-      <c r="H6" s="501"/>
-      <c r="I6" s="501"/>
+      <c r="D6" s="500"/>
+      <c r="E6" s="500"/>
+      <c r="F6" s="500"/>
+      <c r="G6" s="500"/>
+      <c r="H6" s="500"/>
+      <c r="I6" s="500"/>
       <c r="J6" s="25" t="s">
         <v>155</v>
       </c>
       <c r="K6" s="23" t="s">
         <v>2</v>
       </c>
-      <c r="L6" s="320">
+      <c r="L6" s="319">
         <f>+'FORMATO PEG'!U7</f>
         <v>0</v>
       </c>
@@ -9891,23 +10020,23 @@
       <c r="B7" s="23" t="s">
         <v>2</v>
       </c>
-      <c r="C7" s="501">
+      <c r="C7" s="500">
         <f>+'FORMATO PEG'!U4</f>
         <v>0</v>
       </c>
-      <c r="D7" s="501"/>
-      <c r="E7" s="501"/>
-      <c r="F7" s="501"/>
-      <c r="G7" s="501"/>
-      <c r="H7" s="501"/>
-      <c r="I7" s="501"/>
+      <c r="D7" s="500"/>
+      <c r="E7" s="500"/>
+      <c r="F7" s="500"/>
+      <c r="G7" s="500"/>
+      <c r="H7" s="500"/>
+      <c r="I7" s="500"/>
       <c r="J7" s="25" t="s">
         <v>156</v>
       </c>
       <c r="K7" s="23" t="s">
         <v>2</v>
       </c>
-      <c r="L7" s="320">
+      <c r="L7" s="319">
         <f>+'FORMATO PEG'!U9</f>
         <v>0</v>
       </c>
@@ -9919,23 +10048,23 @@
       <c r="B8" s="23" t="s">
         <v>2</v>
       </c>
-      <c r="C8" s="501">
+      <c r="C8" s="500">
         <f>+'FORMATO PEG'!U5</f>
         <v>0</v>
       </c>
-      <c r="D8" s="501"/>
-      <c r="E8" s="501"/>
-      <c r="F8" s="501"/>
-      <c r="G8" s="501"/>
-      <c r="H8" s="501"/>
-      <c r="I8" s="501"/>
+      <c r="D8" s="500"/>
+      <c r="E8" s="500"/>
+      <c r="F8" s="500"/>
+      <c r="G8" s="500"/>
+      <c r="H8" s="500"/>
+      <c r="I8" s="500"/>
       <c r="J8" s="25" t="s">
         <v>6</v>
       </c>
       <c r="K8" s="23" t="s">
         <v>2</v>
       </c>
-      <c r="L8" s="309">
+      <c r="L8" s="308">
         <f>+'FORMATO PEG'!U8</f>
         <v>0</v>
       </c>
@@ -9971,36 +10100,36 @@
       <c r="L10" s="18"/>
     </row>
     <row r="11" spans="1:12" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="492" t="s">
+      <c r="A11" s="491" t="s">
         <v>177</v>
       </c>
-      <c r="B11" s="493"/>
-      <c r="C11" s="493"/>
-      <c r="D11" s="493"/>
-      <c r="E11" s="493"/>
-      <c r="F11" s="493"/>
-      <c r="G11" s="493"/>
-      <c r="H11" s="493"/>
-      <c r="I11" s="493"/>
-      <c r="J11" s="493"/>
-      <c r="K11" s="493"/>
-      <c r="L11" s="494"/>
+      <c r="B11" s="492"/>
+      <c r="C11" s="492"/>
+      <c r="D11" s="492"/>
+      <c r="E11" s="492"/>
+      <c r="F11" s="492"/>
+      <c r="G11" s="492"/>
+      <c r="H11" s="492"/>
+      <c r="I11" s="492"/>
+      <c r="J11" s="492"/>
+      <c r="K11" s="492"/>
+      <c r="L11" s="493"/>
     </row>
     <row r="12" spans="1:12" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="495" t="s">
+      <c r="A12" s="494" t="s">
         <v>188</v>
       </c>
-      <c r="B12" s="496"/>
-      <c r="C12" s="496"/>
-      <c r="D12" s="496"/>
-      <c r="E12" s="496"/>
-      <c r="F12" s="496"/>
-      <c r="G12" s="496"/>
-      <c r="H12" s="496"/>
-      <c r="I12" s="496"/>
-      <c r="J12" s="496"/>
-      <c r="K12" s="496"/>
-      <c r="L12" s="497"/>
+      <c r="B12" s="495"/>
+      <c r="C12" s="495"/>
+      <c r="D12" s="495"/>
+      <c r="E12" s="495"/>
+      <c r="F12" s="495"/>
+      <c r="G12" s="495"/>
+      <c r="H12" s="495"/>
+      <c r="I12" s="495"/>
+      <c r="J12" s="495"/>
+      <c r="K12" s="495"/>
+      <c r="L12" s="496"/>
     </row>
     <row r="13" spans="1:12" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="28"/>
@@ -10055,7 +10184,7 @@
       <c r="K15" s="160" t="s">
         <v>2</v>
       </c>
-      <c r="L15" s="321">
+      <c r="L15" s="320">
         <f>+'FORMATO PEG'!U11</f>
         <v>0</v>
       </c>
@@ -10083,7 +10212,7 @@
       <c r="K16" s="160" t="s">
         <v>2</v>
       </c>
-      <c r="L16" s="310">
+      <c r="L16" s="309">
         <f>+'FORMATO PEG'!U12</f>
         <v>0</v>
       </c>
@@ -10097,7 +10226,7 @@
       <c r="D17" s="155" t="s">
         <v>2</v>
       </c>
-      <c r="E17" s="313">
+      <c r="E17" s="312">
         <f>+'FORMATO PEG'!U17</f>
         <v>0</v>
       </c>
@@ -10111,7 +10240,7 @@
       <c r="K17" s="160" t="s">
         <v>2</v>
       </c>
-      <c r="L17" s="310">
+      <c r="L17" s="309">
         <f>+'FORMATO PEG'!U13</f>
         <v>0</v>
       </c>
@@ -10156,10 +10285,10 @@
       <c r="B20" s="42"/>
       <c r="C20" s="42"/>
       <c r="D20" s="68"/>
-      <c r="E20" s="490"/>
-      <c r="F20" s="490"/>
-      <c r="G20" s="490"/>
-      <c r="H20" s="490"/>
+      <c r="E20" s="489"/>
+      <c r="F20" s="489"/>
+      <c r="G20" s="489"/>
+      <c r="H20" s="489"/>
       <c r="I20" s="22"/>
       <c r="J20" s="42"/>
       <c r="K20" s="42"/>
@@ -10167,15 +10296,15 @@
     </row>
     <row r="21" spans="1:13" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="41"/>
-      <c r="B21" s="499" t="s">
+      <c r="B21" s="498" t="s">
         <v>16</v>
       </c>
-      <c r="C21" s="500"/>
-      <c r="D21" s="500"/>
-      <c r="E21" s="500"/>
-      <c r="F21" s="500"/>
-      <c r="G21" s="500"/>
-      <c r="H21" s="500"/>
+      <c r="C21" s="499"/>
+      <c r="D21" s="499"/>
+      <c r="E21" s="499"/>
+      <c r="F21" s="499"/>
+      <c r="G21" s="499"/>
+      <c r="H21" s="499"/>
       <c r="I21" s="111" t="s">
         <v>17</v>
       </c>
@@ -10187,7 +10316,7 @@
     </row>
     <row r="22" spans="1:13" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="41"/>
-      <c r="B22" s="304" t="s">
+      <c r="B22" s="303" t="s">
         <v>19</v>
       </c>
       <c r="C22" s="40"/>
@@ -10250,7 +10379,7 @@
     </row>
     <row r="25" spans="1:13" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="41"/>
-      <c r="B25" s="305" t="s">
+      <c r="B25" s="304" t="s">
         <v>23</v>
       </c>
       <c r="C25" s="122"/>
@@ -10338,11 +10467,11 @@
       <c r="F30" s="21"/>
       <c r="G30" s="21"/>
       <c r="H30" s="21"/>
-      <c r="J30" s="132" cm="1">
+      <c r="J30" s="561" cm="1">
         <f t="array" ref="J30:K30">+'FORMATO PEG'!H27:I27</f>
         <v>0</v>
       </c>
-      <c r="K30" s="49">
+      <c r="K30" s="562">
         <v>0</v>
       </c>
       <c r="L30" s="49"/>
@@ -10376,11 +10505,11 @@
       <c r="F32" s="21"/>
       <c r="G32" s="21"/>
       <c r="H32" s="21"/>
-      <c r="J32" s="132" cm="1">
+      <c r="J32" s="561" cm="1">
         <f t="array" ref="J32:K32">+'FORMATO PEG'!H28:I28</f>
         <v>0</v>
       </c>
-      <c r="K32" s="49">
+      <c r="K32" s="562">
         <v>0</v>
       </c>
       <c r="L32" s="49"/>
@@ -10445,20 +10574,20 @@
       <c r="L36" s="27"/>
     </row>
     <row r="37" spans="1:14" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="488" t="s">
+      <c r="A37" s="487" t="s">
         <v>172</v>
       </c>
-      <c r="B37" s="489"/>
-      <c r="C37" s="489"/>
-      <c r="D37" s="489"/>
-      <c r="E37" s="489"/>
-      <c r="F37" s="489"/>
-      <c r="G37" s="489"/>
-      <c r="H37" s="489"/>
-      <c r="I37" s="489"/>
-      <c r="J37" s="489"/>
-      <c r="K37" s="489"/>
-      <c r="L37" s="489"/>
+      <c r="B37" s="488"/>
+      <c r="C37" s="488"/>
+      <c r="D37" s="488"/>
+      <c r="E37" s="488"/>
+      <c r="F37" s="488"/>
+      <c r="G37" s="488"/>
+      <c r="H37" s="488"/>
+      <c r="I37" s="488"/>
+      <c r="J37" s="488"/>
+      <c r="K37" s="488"/>
+      <c r="L37" s="488"/>
     </row>
     <row r="38" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="59" t="s">
@@ -10477,22 +10606,22 @@
       <c r="L38" s="27"/>
     </row>
     <row r="39" spans="1:14" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="487" t="s">
+      <c r="A39" s="486" t="s">
         <v>185</v>
       </c>
-      <c r="B39" s="487"/>
-      <c r="C39" s="487"/>
-      <c r="D39" s="487"/>
-      <c r="E39" s="487"/>
-      <c r="F39" s="487"/>
-      <c r="G39" s="487"/>
-      <c r="H39" s="487"/>
-      <c r="I39" s="487"/>
-      <c r="J39" s="487"/>
-      <c r="K39" s="487"/>
-      <c r="L39" s="487"/>
-      <c r="M39" s="317"/>
-      <c r="N39" s="317"/>
+      <c r="B39" s="486"/>
+      <c r="C39" s="486"/>
+      <c r="D39" s="486"/>
+      <c r="E39" s="486"/>
+      <c r="F39" s="486"/>
+      <c r="G39" s="486"/>
+      <c r="H39" s="486"/>
+      <c r="I39" s="486"/>
+      <c r="J39" s="486"/>
+      <c r="K39" s="486"/>
+      <c r="L39" s="486"/>
+      <c r="M39" s="316"/>
+      <c r="N39" s="316"/>
     </row>
     <row r="40" spans="1:14" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="59"/>
@@ -10611,11 +10740,6 @@
     </row>
     <row r="48" spans="1:14" ht="15.9" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="x1m06SVvBAjr8MSBI7Z3A0MIDn2cA6c3VxZcptcD/cT5bqSBjZHRE2O26jBBsQA6Zj8Fbw8guF8ZLwwMgwR9sA==" saltValue="Q5hVu0avY3QO9ps6QcyxVA==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
-  <protectedRanges>
-    <protectedRange sqref="E9:E10 E13" name="Rango3_3_1_1_1_1_1_1_1_1"/>
-    <protectedRange sqref="E8:I8" name="Rango3_3_1_1_1_1_1_1_1_1_1_1_1_2_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1"/>
-  </protectedRanges>
   <mergeCells count="12">
     <mergeCell ref="A39:L39"/>
     <mergeCell ref="A37:L37"/>
@@ -10668,22 +10792,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="502" t="s">
+      <c r="A1" s="513" t="s">
         <v>189</v>
       </c>
-      <c r="B1" s="503"/>
-      <c r="C1" s="503"/>
-      <c r="D1" s="503"/>
-      <c r="E1" s="503"/>
-      <c r="F1" s="503"/>
-      <c r="G1" s="503"/>
-      <c r="H1" s="503"/>
-      <c r="I1" s="503"/>
-      <c r="J1" s="503"/>
-      <c r="K1" s="503"/>
-      <c r="L1" s="503"/>
-      <c r="M1" s="503"/>
-      <c r="N1" s="504"/>
+      <c r="B1" s="514"/>
+      <c r="C1" s="514"/>
+      <c r="D1" s="514"/>
+      <c r="E1" s="514"/>
+      <c r="F1" s="514"/>
+      <c r="G1" s="514"/>
+      <c r="H1" s="514"/>
+      <c r="I1" s="514"/>
+      <c r="J1" s="514"/>
+      <c r="K1" s="514"/>
+      <c r="L1" s="514"/>
+      <c r="M1" s="514"/>
+      <c r="N1" s="515"/>
       <c r="O1" s="64"/>
     </row>
     <row r="2" spans="1:20" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
@@ -10708,8 +10832,8 @@
       <c r="A3" s="170" t="s">
         <v>37</v>
       </c>
-      <c r="B3" s="299"/>
-      <c r="C3" s="299"/>
+      <c r="B3" s="298"/>
+      <c r="C3" s="298"/>
       <c r="D3" s="65"/>
       <c r="E3" s="65"/>
       <c r="F3" s="174"/>
@@ -10723,7 +10847,7 @@
       <c r="A4" s="170" t="s">
         <v>38</v>
       </c>
-      <c r="B4" s="299"/>
+      <c r="B4" s="298"/>
       <c r="C4" s="68">
         <f>+Balanza!C7</f>
         <v>-4.6299999999999997E-6</v>
@@ -10732,11 +10856,11 @@
       <c r="E4" s="65"/>
       <c r="F4" s="174"/>
       <c r="G4" s="65"/>
-      <c r="H4" s="302" t="s">
+      <c r="H4" s="301" t="s">
         <v>40</v>
       </c>
-      <c r="I4" s="299"/>
-      <c r="J4" s="303">
+      <c r="I4" s="298"/>
+      <c r="J4" s="302">
         <f>+Balanza!D12</f>
         <v>46132</v>
       </c>
@@ -10754,9 +10878,9 @@
         <f>+Balanza!C11</f>
         <v>EQP-0050</v>
       </c>
-      <c r="D5" s="300"/>
-      <c r="E5" s="300"/>
-      <c r="F5" s="301"/>
+      <c r="D5" s="299"/>
+      <c r="E5" s="299"/>
+      <c r="F5" s="300"/>
       <c r="G5" s="74"/>
       <c r="H5" s="74"/>
       <c r="I5" s="74"/>
@@ -10788,20 +10912,20 @@
       </c>
       <c r="C7" s="179"/>
       <c r="D7" s="180"/>
-      <c r="E7" s="513" t="s">
+      <c r="E7" s="524" t="s">
         <v>20</v>
       </c>
-      <c r="F7" s="514"/>
+      <c r="F7" s="525"/>
       <c r="G7" s="65"/>
       <c r="H7" s="178" t="s">
         <v>162</v>
       </c>
       <c r="I7" s="179"/>
       <c r="J7" s="181"/>
-      <c r="K7" s="518" t="s">
+      <c r="K7" s="504" t="s">
         <v>20</v>
       </c>
-      <c r="L7" s="519"/>
+      <c r="L7" s="505"/>
       <c r="M7" s="65"/>
       <c r="N7" s="65"/>
     </row>
@@ -10822,25 +10946,25 @@
     </row>
     <row r="9" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="107"/>
-      <c r="B9" s="509" t="s">
+      <c r="B9" s="520" t="s">
         <v>152</v>
       </c>
-      <c r="C9" s="509"/>
-      <c r="D9" s="508" t="e">
+      <c r="C9" s="520"/>
+      <c r="D9" s="519" t="e">
         <f>+INDEX(P13:Q23,MATCH(E7,P13:P23,0),2)</f>
         <v>#N/A</v>
       </c>
-      <c r="E9" s="508"/>
-      <c r="F9" s="510" t="e">
+      <c r="E9" s="519"/>
+      <c r="F9" s="521" t="e">
         <f>+IF(I13/1000&gt;D9,"Cumple","No Cumple")</f>
         <v>#N/A</v>
       </c>
-      <c r="G9" s="510"/>
+      <c r="G9" s="521"/>
       <c r="H9" s="65"/>
       <c r="J9" s="194" t="s">
         <v>168</v>
       </c>
-      <c r="K9" s="311" t="s">
+      <c r="K9" s="310" t="s">
         <v>20</v>
       </c>
       <c r="O9" s="147"/>
@@ -10857,30 +10981,30 @@
       <c r="O10" s="147"/>
     </row>
     <row r="11" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="512" t="s">
+      <c r="A11" s="523" t="s">
         <v>41</v>
       </c>
-      <c r="B11" s="512"/>
-      <c r="C11" s="512"/>
-      <c r="D11" s="512"/>
-      <c r="E11" s="512"/>
-      <c r="F11" s="512"/>
-      <c r="G11" s="512"/>
-      <c r="H11" s="512" t="s">
+      <c r="B11" s="523"/>
+      <c r="C11" s="523"/>
+      <c r="D11" s="523"/>
+      <c r="E11" s="523"/>
+      <c r="F11" s="523"/>
+      <c r="G11" s="523"/>
+      <c r="H11" s="523" t="s">
         <v>42</v>
       </c>
-      <c r="I11" s="511" t="s">
+      <c r="I11" s="522" t="s">
         <v>134</v>
       </c>
-      <c r="J11" s="511"/>
-      <c r="K11" s="511" t="s">
+      <c r="J11" s="522"/>
+      <c r="K11" s="522" t="s">
         <v>135</v>
       </c>
-      <c r="L11" s="511"/>
-      <c r="M11" s="511" t="s">
+      <c r="L11" s="522"/>
+      <c r="M11" s="522" t="s">
         <v>136</v>
       </c>
-      <c r="N11" s="511"/>
+      <c r="N11" s="522"/>
       <c r="O11" s="148"/>
       <c r="P11" s="177" t="s">
         <v>159</v>
@@ -10890,14 +11014,14 @@
       </c>
     </row>
     <row r="12" spans="1:20" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="512"/>
-      <c r="B12" s="512"/>
-      <c r="C12" s="512"/>
-      <c r="D12" s="512"/>
-      <c r="E12" s="512"/>
-      <c r="F12" s="512"/>
-      <c r="G12" s="512"/>
-      <c r="H12" s="512"/>
+      <c r="A12" s="523"/>
+      <c r="B12" s="523"/>
+      <c r="C12" s="523"/>
+      <c r="D12" s="523"/>
+      <c r="E12" s="523"/>
+      <c r="F12" s="523"/>
+      <c r="G12" s="523"/>
+      <c r="H12" s="523"/>
       <c r="I12" s="111" t="s">
         <v>43</v>
       </c>
@@ -10935,15 +11059,15 @@
       <c r="F13" s="186"/>
       <c r="G13" s="187"/>
       <c r="H13" s="184"/>
-      <c r="I13" s="507">
+      <c r="I13" s="518">
         <f>+'FORMATO PEG'!O27</f>
         <v>0</v>
       </c>
-      <c r="J13" s="507"/>
-      <c r="K13" s="507"/>
-      <c r="L13" s="507"/>
-      <c r="M13" s="507"/>
-      <c r="N13" s="507"/>
+      <c r="J13" s="518"/>
+      <c r="K13" s="518"/>
+      <c r="L13" s="518"/>
+      <c r="M13" s="518"/>
+      <c r="N13" s="518"/>
       <c r="O13" s="149"/>
       <c r="P13" s="164" t="s">
         <v>144</v>
@@ -10965,7 +11089,7 @@
       <c r="H14" s="184" t="s">
         <v>47</v>
       </c>
-      <c r="I14" s="312">
+      <c r="I14" s="311">
         <f>+'FORMATO PEG'!O28</f>
         <v>0</v>
       </c>
@@ -11000,15 +11124,15 @@
         <v>154</v>
       </c>
       <c r="C15" s="186"/>
-      <c r="D15" s="520" t="s">
+      <c r="D15" s="506" t="s">
         <v>147</v>
       </c>
-      <c r="E15" s="520"/>
-      <c r="F15" s="505" t="e">
+      <c r="E15" s="506"/>
+      <c r="F15" s="516" t="e">
         <f>+SUM(J15,L15,N15)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="G15" s="506"/>
+      <c r="G15" s="517"/>
       <c r="H15" s="184" t="s">
         <v>24</v>
       </c>
@@ -11034,7 +11158,7 @@
       <c r="Q15" s="164">
         <v>18</v>
       </c>
-      <c r="T15" s="306"/>
+      <c r="T15" s="305"/>
     </row>
     <row r="16" spans="1:20" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="61" t="s">
@@ -11081,14 +11205,14 @@
       <c r="A17" s="61" t="s">
         <v>48</v>
       </c>
-      <c r="B17" s="421" t="s">
+      <c r="B17" s="475" t="s">
         <v>49</v>
       </c>
-      <c r="C17" s="422"/>
-      <c r="D17" s="422"/>
-      <c r="E17" s="422"/>
-      <c r="F17" s="422"/>
-      <c r="G17" s="423"/>
+      <c r="C17" s="476"/>
+      <c r="D17" s="476"/>
+      <c r="E17" s="476"/>
+      <c r="F17" s="476"/>
+      <c r="G17" s="477"/>
       <c r="H17" s="143" t="s">
         <v>47</v>
       </c>
@@ -11122,14 +11246,14 @@
       <c r="A18" s="61" t="s">
         <v>50</v>
       </c>
-      <c r="B18" s="515" t="s">
+      <c r="B18" s="501" t="s">
         <v>51</v>
       </c>
-      <c r="C18" s="516"/>
-      <c r="D18" s="516"/>
-      <c r="E18" s="516"/>
-      <c r="F18" s="516"/>
-      <c r="G18" s="517"/>
+      <c r="C18" s="502"/>
+      <c r="D18" s="502"/>
+      <c r="E18" s="502"/>
+      <c r="F18" s="502"/>
+      <c r="G18" s="503"/>
       <c r="H18" s="143" t="s">
         <v>47</v>
       </c>
@@ -11214,7 +11338,7 @@
       <c r="G20" s="135"/>
       <c r="H20" s="145"/>
       <c r="I20" s="62"/>
-      <c r="J20" s="308" t="e">
+      <c r="J20" s="307" t="e">
         <f>J17/(J18-J19)</f>
         <v>#DIV/0!</v>
       </c>
@@ -11250,7 +11374,7 @@
       <c r="G21" s="135"/>
       <c r="H21" s="145"/>
       <c r="I21" s="62"/>
-      <c r="J21" s="308" t="e">
+      <c r="J21" s="307" t="e">
         <f>J18/(J18-J19)</f>
         <v>#DIV/0!</v>
       </c>
@@ -11286,7 +11410,7 @@
       <c r="G22" s="135"/>
       <c r="H22" s="145"/>
       <c r="I22" s="62"/>
-      <c r="J22" s="308" t="e">
+      <c r="J22" s="307" t="e">
         <f t="shared" ref="J22" si="0">J17/(J17-J19)</f>
         <v>#DIV/0!</v>
       </c>
@@ -11324,7 +11448,7 @@
         <v>24</v>
       </c>
       <c r="I23" s="63"/>
-      <c r="J23" s="307" t="e">
+      <c r="J23" s="306" t="e">
         <f>(J18-J17)/J17*100</f>
         <v>#DIV/0!</v>
       </c>
@@ -11354,24 +11478,24 @@
     </row>
     <row r="25" spans="1:17" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="68"/>
-      <c r="B25" s="421" t="s">
+      <c r="B25" s="475" t="s">
         <v>63</v>
       </c>
-      <c r="C25" s="422"/>
-      <c r="D25" s="422"/>
-      <c r="E25" s="422"/>
-      <c r="F25" s="422"/>
-      <c r="G25" s="423"/>
+      <c r="C25" s="476"/>
+      <c r="D25" s="476"/>
+      <c r="E25" s="476"/>
+      <c r="F25" s="476"/>
+      <c r="G25" s="477"/>
       <c r="H25" s="55"/>
-      <c r="I25" s="524" t="b">
+      <c r="I25" s="510" t="b">
         <f>IF(K7=1,J20,IF(K7=2,1/(($J$15/100)/J20+($L$15/100)/L20),IF(K7=3,1/(($J$15/100)/J20+($L$15/100)/L20+(N15/100)/N20))))</f>
         <v>0</v>
       </c>
-      <c r="J25" s="525"/>
-      <c r="K25" s="525"/>
-      <c r="L25" s="525"/>
-      <c r="M25" s="525"/>
-      <c r="N25" s="526"/>
+      <c r="J25" s="511"/>
+      <c r="K25" s="511"/>
+      <c r="L25" s="511"/>
+      <c r="M25" s="511"/>
+      <c r="N25" s="512"/>
       <c r="O25" s="173"/>
       <c r="P25" s="164" t="s">
         <v>20</v>
@@ -11383,75 +11507,87 @@
     </row>
     <row r="26" spans="1:17" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="68"/>
-      <c r="B26" s="421" t="s">
+      <c r="B26" s="475" t="s">
         <v>64</v>
       </c>
-      <c r="C26" s="422"/>
-      <c r="D26" s="422"/>
-      <c r="E26" s="422"/>
-      <c r="F26" s="422"/>
-      <c r="G26" s="423"/>
+      <c r="C26" s="476"/>
+      <c r="D26" s="476"/>
+      <c r="E26" s="476"/>
+      <c r="F26" s="476"/>
+      <c r="G26" s="477"/>
       <c r="H26" s="55"/>
-      <c r="I26" s="524" t="b">
+      <c r="I26" s="510" t="b">
         <f>IF(K7=1,J21,IF(K7=2,1/(($J$15/100)/J21+($L$15/100)/L21),IF(K7=3,1/(($J$15/100)/J21+($L$15/100)/L21+(N15/100)/N21))))</f>
         <v>0</v>
       </c>
-      <c r="J26" s="525"/>
-      <c r="K26" s="525"/>
-      <c r="L26" s="525"/>
-      <c r="M26" s="525"/>
-      <c r="N26" s="526"/>
+      <c r="J26" s="511"/>
+      <c r="K26" s="511"/>
+      <c r="L26" s="511"/>
+      <c r="M26" s="511"/>
+      <c r="N26" s="512"/>
       <c r="O26" s="173"/>
     </row>
     <row r="27" spans="1:17" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="68"/>
-      <c r="B27" s="421" t="s">
+      <c r="B27" s="475" t="s">
         <v>65</v>
       </c>
-      <c r="C27" s="422"/>
-      <c r="D27" s="422"/>
-      <c r="E27" s="422"/>
-      <c r="F27" s="422"/>
-      <c r="G27" s="423"/>
+      <c r="C27" s="476"/>
+      <c r="D27" s="476"/>
+      <c r="E27" s="476"/>
+      <c r="F27" s="476"/>
+      <c r="G27" s="477"/>
       <c r="H27" s="55"/>
-      <c r="I27" s="524" t="b">
+      <c r="I27" s="510" t="b">
         <f>IF(K7=1,J22,IF(K7=2,1/(($J$15/100)/J22+($L$15/100)/L22),IF(K7=3,1/(($J$15/100)/J22+($L$15/100)/L22+(N15/100)/N22))))</f>
         <v>0</v>
       </c>
-      <c r="J27" s="525"/>
-      <c r="K27" s="525"/>
-      <c r="L27" s="525"/>
-      <c r="M27" s="525"/>
-      <c r="N27" s="526"/>
+      <c r="J27" s="511"/>
+      <c r="K27" s="511"/>
+      <c r="L27" s="511"/>
+      <c r="M27" s="511"/>
+      <c r="N27" s="512"/>
       <c r="O27" s="173"/>
     </row>
     <row r="28" spans="1:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="68"/>
-      <c r="B28" s="421" t="s">
+      <c r="B28" s="475" t="s">
         <v>66</v>
       </c>
-      <c r="C28" s="422"/>
-      <c r="D28" s="422"/>
-      <c r="E28" s="422"/>
-      <c r="F28" s="422"/>
-      <c r="G28" s="423"/>
+      <c r="C28" s="476"/>
+      <c r="D28" s="476"/>
+      <c r="E28" s="476"/>
+      <c r="F28" s="476"/>
+      <c r="G28" s="477"/>
       <c r="H28" s="56" t="s">
         <v>24</v>
       </c>
-      <c r="I28" s="521" t="b">
+      <c r="I28" s="507" t="b">
         <f>IF(K7=1,J23,IF(K7=2,1/(($J$15/100)/J23+($L$15/100)/L23),IF(K7=3,1/(($J$15/100)/J23+($L$15/100)/L23+(N15/100)/N23))))</f>
         <v>0</v>
       </c>
-      <c r="J28" s="522"/>
-      <c r="K28" s="522"/>
-      <c r="L28" s="522"/>
-      <c r="M28" s="522"/>
-      <c r="N28" s="523"/>
+      <c r="J28" s="508"/>
+      <c r="K28" s="508"/>
+      <c r="L28" s="508"/>
+      <c r="M28" s="508"/>
+      <c r="N28" s="509"/>
       <c r="O28" s="153"/>
     </row>
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="W+ehWvk1+G4fxMwMlFFe24eUcB7dTRS6CSN4hdQEHiO/u8gs+lAQOb/9/FmIcet9iZVIOf5wG+i5LTmEs2xhcA==" saltValue="AwzUmQKx7HBfx5Grx49ElQ==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="24">
+    <mergeCell ref="A1:N1"/>
+    <mergeCell ref="F15:G15"/>
+    <mergeCell ref="I13:N13"/>
+    <mergeCell ref="D9:E9"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="F9:G9"/>
+    <mergeCell ref="I11:J11"/>
+    <mergeCell ref="K11:L11"/>
+    <mergeCell ref="M11:N11"/>
+    <mergeCell ref="A11:G12"/>
+    <mergeCell ref="H11:H12"/>
+    <mergeCell ref="E7:F7"/>
     <mergeCell ref="B17:G17"/>
     <mergeCell ref="B18:G18"/>
     <mergeCell ref="K7:L7"/>
@@ -11464,18 +11600,6 @@
     <mergeCell ref="B25:G25"/>
     <mergeCell ref="B26:G26"/>
     <mergeCell ref="B27:G27"/>
-    <mergeCell ref="A1:N1"/>
-    <mergeCell ref="F15:G15"/>
-    <mergeCell ref="I13:N13"/>
-    <mergeCell ref="D9:E9"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="F9:G9"/>
-    <mergeCell ref="I11:J11"/>
-    <mergeCell ref="K11:L11"/>
-    <mergeCell ref="M11:N11"/>
-    <mergeCell ref="A11:G12"/>
-    <mergeCell ref="H11:H12"/>
-    <mergeCell ref="E7:F7"/>
   </mergeCells>
   <conditionalFormatting sqref="F9:G10 O9:O10">
     <cfRule type="containsText" dxfId="0" priority="2" operator="containsText" text="no">
@@ -11505,7 +11629,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3AB8A787-28AE-4F29-9790-1AE86195FD78}">
-  <dimension ref="A1:T93"/>
+  <dimension ref="A1:T100"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="26" style="1" customWidth="1"/>
@@ -11522,16 +11646,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="528"/>
-      <c r="B1" s="531" t="s">
+      <c r="A1" s="527"/>
+      <c r="B1" s="530" t="s">
         <v>77</v>
       </c>
-      <c r="C1" s="532"/>
-      <c r="D1" s="532"/>
-      <c r="E1" s="532"/>
-      <c r="F1" s="532"/>
-      <c r="G1" s="532"/>
-      <c r="H1" s="533"/>
+      <c r="C1" s="531"/>
+      <c r="D1" s="531"/>
+      <c r="E1" s="531"/>
+      <c r="F1" s="531"/>
+      <c r="G1" s="531"/>
+      <c r="H1" s="532"/>
       <c r="I1" s="84" t="s">
         <v>78</v>
       </c>
@@ -11540,14 +11664,14 @@
       </c>
     </row>
     <row r="2" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="529"/>
-      <c r="B2" s="534"/>
-      <c r="C2" s="535"/>
-      <c r="D2" s="535"/>
-      <c r="E2" s="535"/>
-      <c r="F2" s="535"/>
-      <c r="G2" s="535"/>
-      <c r="H2" s="536"/>
+      <c r="A2" s="528"/>
+      <c r="B2" s="533"/>
+      <c r="C2" s="534"/>
+      <c r="D2" s="534"/>
+      <c r="E2" s="534"/>
+      <c r="F2" s="534"/>
+      <c r="G2" s="534"/>
+      <c r="H2" s="535"/>
       <c r="I2" s="84" t="s">
         <v>80</v>
       </c>
@@ -11556,14 +11680,14 @@
       </c>
     </row>
     <row r="3" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="529"/>
-      <c r="B3" s="534"/>
-      <c r="C3" s="535"/>
-      <c r="D3" s="535"/>
-      <c r="E3" s="535"/>
-      <c r="F3" s="535"/>
-      <c r="G3" s="535"/>
-      <c r="H3" s="536"/>
+      <c r="A3" s="528"/>
+      <c r="B3" s="533"/>
+      <c r="C3" s="534"/>
+      <c r="D3" s="534"/>
+      <c r="E3" s="534"/>
+      <c r="F3" s="534"/>
+      <c r="G3" s="534"/>
+      <c r="H3" s="535"/>
       <c r="I3" s="84" t="s">
         <v>81</v>
       </c>
@@ -11572,14 +11696,14 @@
       </c>
     </row>
     <row r="4" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="530"/>
-      <c r="B4" s="537"/>
-      <c r="C4" s="538"/>
-      <c r="D4" s="538"/>
-      <c r="E4" s="538"/>
-      <c r="F4" s="538"/>
-      <c r="G4" s="538"/>
-      <c r="H4" s="539"/>
+      <c r="A4" s="529"/>
+      <c r="B4" s="536"/>
+      <c r="C4" s="537"/>
+      <c r="D4" s="537"/>
+      <c r="E4" s="537"/>
+      <c r="F4" s="537"/>
+      <c r="G4" s="537"/>
+      <c r="H4" s="538"/>
       <c r="I4" s="84" t="s">
         <v>82</v>
       </c>
@@ -11731,11 +11855,11 @@
       <c r="M18" s="112"/>
     </row>
     <row r="19" spans="1:13" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="540"/>
-      <c r="B19" s="540"/>
-      <c r="C19" s="540"/>
-      <c r="D19" s="540"/>
-      <c r="E19" s="540"/>
+      <c r="A19" s="539"/>
+      <c r="B19" s="539"/>
+      <c r="C19" s="539"/>
+      <c r="D19" s="539"/>
+      <c r="E19" s="539"/>
     </row>
     <row r="20" spans="1:13" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="K20" s="112"/>
@@ -11758,16 +11882,16 @@
     <row r="29" spans="1:13" ht="12" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="30" spans="1:13" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="31" spans="1:13" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="541" t="s">
+      <c r="A31" s="540" t="s">
         <v>93</v>
       </c>
-      <c r="B31" s="542"/>
-      <c r="C31" s="542"/>
-      <c r="D31" s="542"/>
-      <c r="E31" s="542"/>
-      <c r="F31" s="542"/>
-      <c r="G31" s="542"/>
-      <c r="H31" s="543"/>
+      <c r="B31" s="541"/>
+      <c r="C31" s="541"/>
+      <c r="D31" s="541"/>
+      <c r="E31" s="541"/>
+      <c r="F31" s="541"/>
+      <c r="G31" s="541"/>
+      <c r="H31" s="542"/>
       <c r="I31" s="89"/>
       <c r="J31" s="89"/>
     </row>
@@ -12918,10 +13042,10 @@
       <c r="I68" s="89"/>
       <c r="J68" s="87"/>
       <c r="K68" s="227"/>
-      <c r="L68" s="527" t="s">
+      <c r="L68" s="526" t="s">
         <v>112</v>
       </c>
-      <c r="M68" s="527"/>
+      <c r="M68" s="526"/>
       <c r="N68" s="231" t="s">
         <v>101</v>
       </c>
@@ -13263,10 +13387,10 @@
       <c r="H79" s="93"/>
       <c r="J79" s="87"/>
       <c r="K79" s="227"/>
-      <c r="L79" s="527" t="s">
+      <c r="L79" s="526" t="s">
         <v>112</v>
       </c>
-      <c r="M79" s="527"/>
+      <c r="M79" s="526"/>
       <c r="N79" s="231" t="s">
         <v>101</v>
       </c>
@@ -13697,8 +13821,23 @@
       <c r="Q92" s="89"/>
       <c r="R92" s="89"/>
     </row>
-    <row r="93" spans="1:18" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A93" s="298"/>
+    <row r="93" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A93" s="549" t="s">
+        <v>238</v>
+      </c>
+      <c r="B93" s="550" t="s">
+        <v>239</v>
+      </c>
+      <c r="C93" s="551"/>
+      <c r="D93" s="552"/>
+      <c r="E93" s="553" t="s">
+        <v>240</v>
+      </c>
+      <c r="F93" s="553"/>
+      <c r="G93" s="554" t="s">
+        <v>241</v>
+      </c>
+      <c r="H93" s="555"/>
       <c r="K93" s="89"/>
       <c r="L93" s="89"/>
       <c r="M93" s="89"/>
@@ -13708,8 +13847,45 @@
       <c r="Q93" s="89"/>
       <c r="R93" s="89"/>
     </row>
+    <row r="94" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A94" s="556"/>
+      <c r="B94" s="556"/>
+      <c r="C94" s="556"/>
+      <c r="D94" s="556"/>
+      <c r="E94" s="556"/>
+      <c r="F94" s="556"/>
+      <c r="G94" s="556"/>
+      <c r="H94" s="556"/>
+    </row>
+    <row r="95" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A95" s="557" t="s">
+        <v>242</v>
+      </c>
+      <c r="B95" s="558">
+        <v>44869</v>
+      </c>
+      <c r="C95" s="559"/>
+      <c r="D95" s="556"/>
+      <c r="E95" s="560" t="s">
+        <v>243</v>
+      </c>
+      <c r="F95" s="560"/>
+      <c r="G95" s="558">
+        <v>44870</v>
+      </c>
+      <c r="H95" s="559"/>
+    </row>
+    <row r="100" spans="8:8" x14ac:dyDescent="0.25">
+      <c r="H100" s="100"/>
+    </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="12">
+    <mergeCell ref="B93:C93"/>
+    <mergeCell ref="E93:F93"/>
+    <mergeCell ref="G93:H93"/>
+    <mergeCell ref="B95:C95"/>
+    <mergeCell ref="E95:F95"/>
+    <mergeCell ref="G95:H95"/>
     <mergeCell ref="L68:M68"/>
     <mergeCell ref="L79:M79"/>
     <mergeCell ref="A1:A4"/>
@@ -13799,7 +13975,7 @@
         <v>187</v>
       </c>
       <c r="C12" s="78"/>
-      <c r="D12" s="318">
+      <c r="D12" s="317">
         <v>46132</v>
       </c>
     </row>
@@ -13810,34 +13986,34 @@
       <c r="C13" s="197" t="s">
         <v>74</v>
       </c>
-      <c r="D13" s="315">
+      <c r="D13" s="314">
         <v>500</v>
       </c>
-      <c r="E13" s="315">
+      <c r="E13" s="314">
         <v>1000</v>
       </c>
-      <c r="F13" s="315">
+      <c r="F13" s="314">
         <v>5000</v>
       </c>
-      <c r="G13" s="315">
+      <c r="G13" s="314">
         <v>10000</v>
       </c>
-      <c r="H13" s="315">
+      <c r="H13" s="314">
         <v>15000</v>
       </c>
     </row>
     <row r="14" spans="2:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="319"/>
-      <c r="C14" s="314"/>
-      <c r="D14" s="316"/>
-      <c r="E14" s="316"/>
-      <c r="F14" s="316"/>
-      <c r="G14" s="316"/>
-      <c r="H14" s="316"/>
+      <c r="B14" s="318"/>
+      <c r="C14" s="313"/>
+      <c r="D14" s="315"/>
+      <c r="E14" s="315"/>
+      <c r="F14" s="315"/>
+      <c r="G14" s="315"/>
+      <c r="H14" s="315"/>
     </row>
     <row r="15" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B15" s="396"/>
-      <c r="C15" s="397"/>
+      <c r="B15" s="395"/>
+      <c r="C15" s="396"/>
     </row>
     <row r="16" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B16" s="80"/>
@@ -13915,13 +14091,13 @@
       <c r="I22" s="83"/>
     </row>
     <row r="23" spans="2:9" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B23" s="545" t="str">
+      <c r="B23" s="544" t="str">
         <f>+DATOS!B17</f>
         <v>Masa de la muestra secada al horno constante</v>
       </c>
-      <c r="C23" s="545"/>
-      <c r="D23" s="545"/>
-      <c r="E23" s="545"/>
+      <c r="C23" s="544"/>
+      <c r="D23" s="544"/>
+      <c r="E23" s="544"/>
       <c r="F23" s="214">
         <f>+DATOS!I17</f>
         <v>0</v>
@@ -13935,13 +14111,13 @@
       </c>
     </row>
     <row r="24" spans="2:9" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B24" s="544" t="str">
+      <c r="B24" s="543" t="str">
         <f>+DATOS!B18</f>
         <v>Masa de la muestra de ensayo de superficie seca saturada en el aire</v>
       </c>
-      <c r="C24" s="544"/>
-      <c r="D24" s="544"/>
-      <c r="E24" s="544"/>
+      <c r="C24" s="543"/>
+      <c r="D24" s="543"/>
+      <c r="E24" s="543"/>
       <c r="F24" s="214">
         <f>+DATOS!I18</f>
         <v>0</v>
@@ -13955,13 +14131,13 @@
       </c>
     </row>
     <row r="25" spans="2:9" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B25" s="546" t="str">
+      <c r="B25" s="545" t="str">
         <f>+DATOS!B19</f>
         <v>Masa aparente de la muestra de prueba sumergida en agua</v>
       </c>
-      <c r="C25" s="546"/>
-      <c r="D25" s="546"/>
-      <c r="E25" s="546"/>
+      <c r="C25" s="545"/>
+      <c r="D25" s="545"/>
+      <c r="E25" s="545"/>
       <c r="F25" s="214">
         <f>+DATOS!I19</f>
         <v>0</v>
@@ -15163,112 +15339,112 @@
       <c r="A5" s="125" t="s">
         <v>129</v>
       </c>
-      <c r="B5" s="400"/>
+      <c r="B5" s="399"/>
     </row>
     <row r="6" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="7" spans="1:25" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="549" t="s">
+      <c r="A7" s="548" t="s">
         <v>130</v>
       </c>
-      <c r="B7" s="549"/>
-      <c r="C7" s="549"/>
-      <c r="D7" s="549"/>
-      <c r="F7" s="549" t="s">
+      <c r="B7" s="548"/>
+      <c r="C7" s="548"/>
+      <c r="D7" s="548"/>
+      <c r="F7" s="548" t="s">
         <v>131</v>
       </c>
-      <c r="G7" s="549"/>
-      <c r="H7" s="549"/>
-      <c r="I7" s="549"/>
-      <c r="K7" s="549" t="s">
+      <c r="G7" s="548"/>
+      <c r="H7" s="548"/>
+      <c r="I7" s="548"/>
+      <c r="K7" s="548" t="s">
         <v>132</v>
       </c>
-      <c r="L7" s="549"/>
-      <c r="M7" s="549"/>
-      <c r="N7" s="549"/>
-      <c r="P7" s="549" t="s">
+      <c r="L7" s="548"/>
+      <c r="M7" s="548"/>
+      <c r="N7" s="548"/>
+      <c r="P7" s="548" t="s">
         <v>133</v>
       </c>
-      <c r="Q7" s="549"/>
-      <c r="R7" s="549"/>
-      <c r="S7" s="549"/>
+      <c r="Q7" s="548"/>
+      <c r="R7" s="548"/>
+      <c r="S7" s="548"/>
     </row>
     <row r="8" spans="1:25" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="399" t="s">
+      <c r="A8" s="398" t="s">
         <v>232</v>
       </c>
-      <c r="B8" s="547">
+      <c r="B8" s="546">
         <v>4.1539806879132444E-3</v>
       </c>
-      <c r="C8" s="547"/>
-      <c r="D8" s="547"/>
-      <c r="F8" s="399" t="s">
+      <c r="C8" s="546"/>
+      <c r="D8" s="546"/>
+      <c r="F8" s="398" t="s">
         <v>232</v>
       </c>
-      <c r="G8" s="547">
+      <c r="G8" s="546">
         <v>4.2163702135577961E-3</v>
       </c>
-      <c r="H8" s="547"/>
-      <c r="I8" s="547"/>
-      <c r="K8" s="399" t="s">
+      <c r="H8" s="546"/>
+      <c r="I8" s="546"/>
+      <c r="K8" s="398" t="s">
         <v>232</v>
       </c>
-      <c r="L8" s="547">
+      <c r="L8" s="546">
         <v>4.4397197108725995E-3</v>
       </c>
-      <c r="M8" s="547"/>
-      <c r="N8" s="547"/>
-      <c r="P8" s="399" t="s">
+      <c r="M8" s="546"/>
+      <c r="N8" s="546"/>
+      <c r="P8" s="398" t="s">
         <v>232</v>
       </c>
-      <c r="Q8" s="547">
+      <c r="Q8" s="546">
         <v>2.923088169119166E-2</v>
       </c>
-      <c r="R8" s="547"/>
-      <c r="S8" s="547"/>
-      <c r="U8" s="398"/>
-      <c r="V8" s="398"/>
-      <c r="W8" s="398"/>
-      <c r="X8" s="398"/>
-      <c r="Y8" s="398"/>
+      <c r="R8" s="546"/>
+      <c r="S8" s="546"/>
+      <c r="U8" s="397"/>
+      <c r="V8" s="397"/>
+      <c r="W8" s="397"/>
+      <c r="X8" s="397"/>
+      <c r="Y8" s="397"/>
     </row>
     <row r="9" spans="1:25" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="399" t="s">
+      <c r="A9" s="398" t="s">
         <v>233</v>
       </c>
-      <c r="B9" s="547">
+      <c r="B9" s="546">
         <v>4.5030853616677231E-3</v>
       </c>
-      <c r="C9" s="547"/>
-      <c r="D9" s="547"/>
-      <c r="F9" s="399" t="s">
+      <c r="C9" s="546"/>
+      <c r="D9" s="546"/>
+      <c r="F9" s="398" t="s">
         <v>233</v>
       </c>
-      <c r="G9" s="547">
+      <c r="G9" s="546">
         <v>4.4762749065281162E-3</v>
       </c>
-      <c r="H9" s="547"/>
-      <c r="I9" s="547"/>
-      <c r="K9" s="399" t="s">
+      <c r="H9" s="546"/>
+      <c r="I9" s="546"/>
+      <c r="K9" s="398" t="s">
         <v>233</v>
       </c>
-      <c r="L9" s="547">
+      <c r="L9" s="546">
         <v>4.4855735834586023E-3</v>
       </c>
-      <c r="M9" s="547"/>
-      <c r="N9" s="547"/>
-      <c r="P9" s="399" t="s">
+      <c r="M9" s="546"/>
+      <c r="N9" s="546"/>
+      <c r="P9" s="398" t="s">
         <v>233</v>
       </c>
-      <c r="Q9" s="547">
+      <c r="Q9" s="546">
         <v>6.1433493096797555E-2</v>
       </c>
-      <c r="R9" s="547"/>
-      <c r="S9" s="547"/>
-      <c r="U9" s="398"/>
-      <c r="V9" s="398"/>
-      <c r="W9" s="398"/>
-      <c r="X9" s="398"/>
-      <c r="Y9" s="398"/>
+      <c r="R9" s="546"/>
+      <c r="S9" s="546"/>
+      <c r="U9" s="397"/>
+      <c r="V9" s="397"/>
+      <c r="W9" s="397"/>
+      <c r="X9" s="397"/>
+      <c r="Y9" s="397"/>
     </row>
     <row r="10" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="128"/>
@@ -15287,11 +15463,11 @@
       <c r="Q10" s="128"/>
       <c r="R10" s="128"/>
       <c r="S10" s="126"/>
-      <c r="U10" s="398"/>
-      <c r="V10" s="398"/>
-      <c r="W10" s="398"/>
-      <c r="X10" s="398"/>
-      <c r="Y10" s="398"/>
+      <c r="U10" s="397"/>
+      <c r="V10" s="397"/>
+      <c r="W10" s="397"/>
+      <c r="X10" s="397"/>
+      <c r="Y10" s="397"/>
     </row>
     <row r="11" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="128"/>
@@ -15310,41 +15486,41 @@
       <c r="Q11" s="128"/>
       <c r="R11" s="128"/>
       <c r="S11" s="126"/>
-      <c r="U11" s="398"/>
-      <c r="V11" s="398"/>
-      <c r="W11" s="398"/>
-      <c r="X11" s="398"/>
-      <c r="Y11" s="398"/>
+      <c r="U11" s="397"/>
+      <c r="V11" s="397"/>
+      <c r="W11" s="397"/>
+      <c r="X11" s="397"/>
+      <c r="Y11" s="397"/>
     </row>
     <row r="12" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="V12" s="548"/>
-      <c r="W12" s="548"/>
-      <c r="X12" s="548"/>
-      <c r="Y12" s="548"/>
+      <c r="V12" s="547"/>
+      <c r="W12" s="547"/>
+      <c r="X12" s="547"/>
+      <c r="Y12" s="547"/>
     </row>
     <row r="13" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="V13" s="548"/>
-      <c r="W13" s="548"/>
-      <c r="X13" s="548"/>
-      <c r="Y13" s="548"/>
+      <c r="V13" s="547"/>
+      <c r="W13" s="547"/>
+      <c r="X13" s="547"/>
+      <c r="Y13" s="547"/>
     </row>
     <row r="14" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="V14" s="548"/>
-      <c r="W14" s="548"/>
-      <c r="X14" s="548"/>
-      <c r="Y14" s="548"/>
+      <c r="V14" s="547"/>
+      <c r="W14" s="547"/>
+      <c r="X14" s="547"/>
+      <c r="Y14" s="547"/>
     </row>
     <row r="15" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="V15" s="548"/>
-      <c r="W15" s="548"/>
-      <c r="X15" s="548"/>
-      <c r="Y15" s="548"/>
+      <c r="V15" s="547"/>
+      <c r="W15" s="547"/>
+      <c r="X15" s="547"/>
+      <c r="Y15" s="547"/>
     </row>
     <row r="16" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="V16" s="548"/>
-      <c r="W16" s="548"/>
-      <c r="X16" s="548"/>
-      <c r="Y16" s="548"/>
+      <c r="V16" s="547"/>
+      <c r="W16" s="547"/>
+      <c r="X16" s="547"/>
+      <c r="Y16" s="547"/>
     </row>
   </sheetData>
   <mergeCells count="13">

--- a/app/templates/Template_GE_GRUESO.xlsx
+++ b/app/templates/Template_GE_GRUESO.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo\Documents\crmnew\api-geofal-crm\app\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89D688AF-C396-4282-9C66-1488F868A017}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C695498-F91C-4C5D-8FA2-E3EAA80BE809}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="723" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="723" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="FORMATO PEG" sheetId="97" r:id="rId1"/>
@@ -100,7 +100,7 @@
     <definedName name="W" localSheetId="3">#REF!</definedName>
     <definedName name="W">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="191029" calcMode="auto" fullCalcOnLoad="1" forceFullCalc="1"/>
+  <calcPr calcId="191029" forceFullCalc="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -112,6 +112,8 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -1603,8 +1605,9 @@
     </font>
     <font>
       <sz val="10"/>
+      <color theme="0"/>
       <name val="Arial"/>
-      <color theme="0"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="7">
@@ -2240,7 +2243,7 @@
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="563">
+  <cellXfs count="562">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="3" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="10" xfId="3" applyFill="1" applyBorder="1"/>
@@ -2634,10 +2637,6 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="1" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3551,6 +3550,243 @@
     <xf numFmtId="0" fontId="7" fillId="2" borderId="13" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="50" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="3" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="2" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="6" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="11" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="11" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="12" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="11" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="11" xfId="2" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="2" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="2" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="11" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="11" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="12" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="10" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="4" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="5" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="8" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="2" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="9" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="0" borderId="11" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="0" borderId="10" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="0" xfId="6" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="13" fillId="0" borderId="0" xfId="6" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="11" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="10" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="1" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection hidden="1"/>
@@ -3587,9 +3823,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="6" borderId="11" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3615,225 +3848,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="0" xfId="6" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="13" fillId="0" borderId="0" xfId="6" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="11" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="10" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="1" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="11" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="11" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="12" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="10" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="4" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="5" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="8" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="2" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="9" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="44" fillId="0" borderId="11" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="44" fillId="0" borderId="10" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="11" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="11" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="12" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="11" xfId="2" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="2" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="2" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="11" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="2" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="6" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="4" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -3879,6 +3893,53 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="9" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="1" fontId="9" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="3" fontId="33" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="175" fontId="9" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="33" fillId="4" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="33" fillId="4" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="11" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -3919,52 +3980,29 @@
     <xf numFmtId="165" fontId="9" fillId="0" borderId="10" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="9" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="1" fontId="9" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="3" fontId="33" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="175" fontId="9" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="33" fillId="4" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="33" fillId="4" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="20" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="20" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="3" fillId="2" borderId="11" xfId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="3" fillId="2" borderId="10" xfId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -4036,48 +4074,9 @@
     <xf numFmtId="0" fontId="30" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="50" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="20" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="20" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="3" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="3" fillId="2" borderId="11" xfId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="3" fillId="2" borderId="10" xfId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="52" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="52" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="8">
@@ -6003,6 +6002,65 @@
         </a:extLst>
       </xdr:spPr>
     </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>11370</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>8339</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>18990</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>12930</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="3" name="Rectángulo 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{58FA883E-9068-4939-B972-3CFD0A8749BF}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="5823352" y="5335412"/>
+          <a:ext cx="114993" cy="648827"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg1"/>
+        </a:solidFill>
+        <a:ln w="28575" cap="flat" cmpd="sng" algn="ctr">
+          <a:noFill/>
+          <a:prstDash val="solid"/>
+          <a:round/>
+          <a:headEnd type="none" w="med" len="med"/>
+          <a:tailEnd type="none" w="med" len="med"/>
+        </a:ln>
+        <a:effectLst/>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" wrap="square" lIns="18288" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="ctr" upright="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="es-PE" sz="1100">
+            <a:solidFill>
+              <a:schemeClr val="bg1"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
@@ -8496,846 +8554,846 @@
   <dimension ref="A1:AB55"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="1" style="388" customWidth="1"/>
-    <col min="2" max="2" width="6.33203125" style="388" customWidth="1"/>
-    <col min="3" max="3" width="9.44140625" style="388" customWidth="1"/>
-    <col min="4" max="4" width="12.88671875" style="388" customWidth="1"/>
-    <col min="5" max="5" width="10.33203125" style="388" customWidth="1"/>
-    <col min="6" max="6" width="10.6640625" style="388" customWidth="1"/>
-    <col min="7" max="7" width="0.6640625" style="388" customWidth="1"/>
-    <col min="8" max="8" width="10" style="388" customWidth="1"/>
-    <col min="9" max="9" width="4.109375" style="388" customWidth="1"/>
-    <col min="10" max="10" width="0.88671875" style="388" customWidth="1"/>
-    <col min="11" max="11" width="7" style="388" customWidth="1"/>
-    <col min="12" max="12" width="7.109375" style="388" customWidth="1"/>
-    <col min="13" max="13" width="0.6640625" style="388" customWidth="1"/>
-    <col min="14" max="14" width="13.44140625" style="388" customWidth="1"/>
-    <col min="15" max="15" width="15.5546875" style="388" customWidth="1"/>
-    <col min="16" max="16" width="8.88671875" style="388"/>
-    <col min="17" max="17" width="9.6640625" style="388" customWidth="1"/>
-    <col min="18" max="18" width="11.6640625" style="388" customWidth="1"/>
-    <col min="19" max="20" width="8.88671875" style="388"/>
-    <col min="21" max="21" width="10.5546875" style="388" customWidth="1"/>
-    <col min="22" max="16384" width="8.88671875" style="388"/>
+    <col min="1" max="1" width="1" style="387" customWidth="1"/>
+    <col min="2" max="2" width="6.33203125" style="387" customWidth="1"/>
+    <col min="3" max="3" width="9.44140625" style="387" customWidth="1"/>
+    <col min="4" max="4" width="12.88671875" style="387" customWidth="1"/>
+    <col min="5" max="5" width="10.33203125" style="387" customWidth="1"/>
+    <col min="6" max="6" width="10.6640625" style="387" customWidth="1"/>
+    <col min="7" max="7" width="0.6640625" style="387" customWidth="1"/>
+    <col min="8" max="8" width="10" style="387" customWidth="1"/>
+    <col min="9" max="9" width="4.109375" style="387" customWidth="1"/>
+    <col min="10" max="10" width="0.88671875" style="387" customWidth="1"/>
+    <col min="11" max="11" width="7" style="387" customWidth="1"/>
+    <col min="12" max="12" width="7.109375" style="387" customWidth="1"/>
+    <col min="13" max="13" width="0.6640625" style="387" customWidth="1"/>
+    <col min="14" max="14" width="13.44140625" style="387" customWidth="1"/>
+    <col min="15" max="15" width="15.5546875" style="387" customWidth="1"/>
+    <col min="16" max="16" width="8.88671875" style="387"/>
+    <col min="17" max="17" width="9.6640625" style="387" customWidth="1"/>
+    <col min="18" max="18" width="11.6640625" style="387" customWidth="1"/>
+    <col min="19" max="20" width="8.88671875" style="387"/>
+    <col min="21" max="21" width="10.5546875" style="387" customWidth="1"/>
+    <col min="22" max="16384" width="8.88671875" style="387"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" s="325" customFormat="1" ht="15" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="321"/>
-      <c r="B1" s="322"/>
-      <c r="C1" s="322"/>
-      <c r="D1" s="322"/>
-      <c r="E1" s="323"/>
-      <c r="F1" s="323"/>
-      <c r="G1" s="323"/>
-      <c r="H1" s="323"/>
-      <c r="I1" s="323"/>
-      <c r="J1" s="323"/>
-      <c r="K1" s="323"/>
-      <c r="L1" s="323"/>
-      <c r="M1" s="323"/>
-      <c r="N1" s="323"/>
-      <c r="O1" s="324"/>
-    </row>
-    <row r="2" spans="1:21" s="325" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="326"/>
-      <c r="B2" s="327"/>
-      <c r="C2" s="327"/>
-      <c r="D2" s="327"/>
-      <c r="E2" s="328"/>
-      <c r="F2" s="328"/>
-      <c r="G2" s="328"/>
-      <c r="H2" s="328"/>
-      <c r="I2" s="328"/>
-      <c r="J2" s="328"/>
-      <c r="K2" s="328"/>
-      <c r="L2" s="328"/>
-      <c r="M2" s="328"/>
-      <c r="N2" s="328"/>
-      <c r="O2" s="329"/>
-      <c r="T2" s="400" t="s">
+    <row r="1" spans="1:21" s="324" customFormat="1" ht="15" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="320"/>
+      <c r="B1" s="321"/>
+      <c r="C1" s="321"/>
+      <c r="D1" s="321"/>
+      <c r="E1" s="322"/>
+      <c r="F1" s="322"/>
+      <c r="G1" s="322"/>
+      <c r="H1" s="322"/>
+      <c r="I1" s="322"/>
+      <c r="J1" s="322"/>
+      <c r="K1" s="322"/>
+      <c r="L1" s="322"/>
+      <c r="M1" s="322"/>
+      <c r="N1" s="322"/>
+      <c r="O1" s="323"/>
+    </row>
+    <row r="2" spans="1:21" s="324" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="325"/>
+      <c r="B2" s="326"/>
+      <c r="C2" s="326"/>
+      <c r="D2" s="326"/>
+      <c r="E2" s="327"/>
+      <c r="F2" s="327"/>
+      <c r="G2" s="327"/>
+      <c r="H2" s="327"/>
+      <c r="I2" s="327"/>
+      <c r="J2" s="327"/>
+      <c r="K2" s="327"/>
+      <c r="L2" s="327"/>
+      <c r="M2" s="327"/>
+      <c r="N2" s="327"/>
+      <c r="O2" s="328"/>
+      <c r="T2" s="399" t="s">
         <v>1</v>
       </c>
-      <c r="U2" s="401"/>
-    </row>
-    <row r="3" spans="1:21" s="325" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="326"/>
-      <c r="B3" s="327"/>
-      <c r="C3" s="327"/>
-      <c r="D3" s="327"/>
-      <c r="E3" s="328"/>
-      <c r="F3" s="328"/>
-      <c r="G3" s="328"/>
-      <c r="H3" s="328"/>
-      <c r="I3" s="328"/>
-      <c r="J3" s="328"/>
-      <c r="K3" s="328"/>
-      <c r="L3" s="328"/>
-      <c r="M3" s="328"/>
-      <c r="N3" s="328"/>
-      <c r="O3" s="329"/>
-      <c r="T3" s="400" t="s">
+      <c r="U2" s="400"/>
+    </row>
+    <row r="3" spans="1:21" s="324" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="325"/>
+      <c r="B3" s="326"/>
+      <c r="C3" s="326"/>
+      <c r="D3" s="326"/>
+      <c r="E3" s="327"/>
+      <c r="F3" s="327"/>
+      <c r="G3" s="327"/>
+      <c r="H3" s="327"/>
+      <c r="I3" s="327"/>
+      <c r="J3" s="327"/>
+      <c r="K3" s="327"/>
+      <c r="L3" s="327"/>
+      <c r="M3" s="327"/>
+      <c r="N3" s="327"/>
+      <c r="O3" s="328"/>
+      <c r="T3" s="399" t="s">
         <v>4</v>
       </c>
-      <c r="U3" s="402"/>
-    </row>
-    <row r="4" spans="1:21" s="325" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="326"/>
-      <c r="B4" s="327"/>
-      <c r="C4" s="327"/>
-      <c r="D4" s="327"/>
-      <c r="E4" s="328"/>
-      <c r="F4" s="328"/>
-      <c r="G4" s="328"/>
-      <c r="H4" s="328"/>
-      <c r="I4" s="328"/>
-      <c r="J4" s="328"/>
-      <c r="K4" s="328"/>
-      <c r="L4" s="328"/>
-      <c r="M4" s="328"/>
-      <c r="N4" s="328"/>
-      <c r="O4" s="329"/>
-      <c r="Q4" s="330" t="s">
+      <c r="U3" s="401"/>
+    </row>
+    <row r="4" spans="1:21" s="324" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="325"/>
+      <c r="B4" s="326"/>
+      <c r="C4" s="326"/>
+      <c r="D4" s="326"/>
+      <c r="E4" s="327"/>
+      <c r="F4" s="327"/>
+      <c r="G4" s="327"/>
+      <c r="H4" s="327"/>
+      <c r="I4" s="327"/>
+      <c r="J4" s="327"/>
+      <c r="K4" s="327"/>
+      <c r="L4" s="327"/>
+      <c r="M4" s="327"/>
+      <c r="N4" s="327"/>
+      <c r="O4" s="328"/>
+      <c r="Q4" s="329" t="s">
         <v>159</v>
       </c>
-      <c r="R4" s="330" t="s">
+      <c r="R4" s="329" t="s">
         <v>158</v>
       </c>
-      <c r="T4" s="400" t="s">
+      <c r="T4" s="399" t="s">
         <v>5</v>
       </c>
-      <c r="U4" s="402"/>
-    </row>
-    <row r="5" spans="1:21" s="325" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="331"/>
-      <c r="B5" s="332"/>
-      <c r="C5" s="332"/>
-      <c r="D5" s="332"/>
-      <c r="E5" s="332"/>
-      <c r="F5" s="332"/>
-      <c r="G5" s="332"/>
-      <c r="H5" s="332"/>
-      <c r="I5" s="332"/>
-      <c r="J5" s="332"/>
-      <c r="K5" s="332"/>
-      <c r="L5" s="332"/>
-      <c r="M5" s="332"/>
-      <c r="N5" s="332"/>
-      <c r="O5" s="333"/>
-      <c r="Q5" s="330" t="s">
+      <c r="U4" s="401"/>
+    </row>
+    <row r="5" spans="1:21" s="324" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="330"/>
+      <c r="B5" s="331"/>
+      <c r="C5" s="331"/>
+      <c r="D5" s="331"/>
+      <c r="E5" s="331"/>
+      <c r="F5" s="331"/>
+      <c r="G5" s="331"/>
+      <c r="H5" s="331"/>
+      <c r="I5" s="331"/>
+      <c r="J5" s="331"/>
+      <c r="K5" s="331"/>
+      <c r="L5" s="331"/>
+      <c r="M5" s="331"/>
+      <c r="N5" s="331"/>
+      <c r="O5" s="332"/>
+      <c r="Q5" s="329" t="s">
         <v>161</v>
       </c>
-      <c r="R5" s="330" t="s">
+      <c r="R5" s="329" t="s">
         <v>160</v>
       </c>
-      <c r="T5" s="400" t="s">
+      <c r="T5" s="399" t="s">
         <v>7</v>
       </c>
-      <c r="U5" s="402"/>
-    </row>
-    <row r="6" spans="1:21" s="325" customFormat="1" ht="12" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="334"/>
-      <c r="B6" s="334"/>
-      <c r="C6" s="334"/>
-      <c r="D6" s="334"/>
-      <c r="E6" s="334"/>
-      <c r="F6" s="334"/>
-      <c r="G6" s="334"/>
-      <c r="H6" s="334"/>
-      <c r="I6" s="334"/>
-      <c r="J6" s="334"/>
-      <c r="K6" s="334"/>
-      <c r="L6" s="334"/>
-      <c r="M6" s="334"/>
-      <c r="N6" s="334"/>
-      <c r="O6" s="334"/>
-      <c r="Q6" s="335" t="s">
+      <c r="U5" s="401"/>
+    </row>
+    <row r="6" spans="1:21" s="324" customFormat="1" ht="12" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="333"/>
+      <c r="B6" s="333"/>
+      <c r="C6" s="333"/>
+      <c r="D6" s="333"/>
+      <c r="E6" s="333"/>
+      <c r="F6" s="333"/>
+      <c r="G6" s="333"/>
+      <c r="H6" s="333"/>
+      <c r="I6" s="333"/>
+      <c r="J6" s="333"/>
+      <c r="K6" s="333"/>
+      <c r="L6" s="333"/>
+      <c r="M6" s="333"/>
+      <c r="N6" s="333"/>
+      <c r="O6" s="333"/>
+      <c r="Q6" s="334" t="s">
         <v>144</v>
       </c>
-      <c r="R6" s="335">
+      <c r="R6" s="334">
         <v>40</v>
       </c>
-      <c r="T6" s="403"/>
-      <c r="U6" s="404"/>
-    </row>
-    <row r="7" spans="1:21" s="325" customFormat="1" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="425" t="s">
+      <c r="T6" s="402"/>
+      <c r="U6" s="403"/>
+    </row>
+    <row r="7" spans="1:21" s="324" customFormat="1" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="468" t="s">
         <v>0</v>
       </c>
-      <c r="B7" s="425"/>
-      <c r="C7" s="425"/>
-      <c r="D7" s="425"/>
-      <c r="E7" s="425"/>
-      <c r="F7" s="425"/>
-      <c r="G7" s="425"/>
-      <c r="H7" s="425"/>
-      <c r="I7" s="425"/>
-      <c r="J7" s="425"/>
-      <c r="K7" s="425"/>
-      <c r="L7" s="425"/>
-      <c r="M7" s="425"/>
-      <c r="N7" s="425"/>
-      <c r="O7" s="425"/>
-      <c r="Q7" s="335" t="s">
+      <c r="B7" s="468"/>
+      <c r="C7" s="468"/>
+      <c r="D7" s="468"/>
+      <c r="E7" s="468"/>
+      <c r="F7" s="468"/>
+      <c r="G7" s="468"/>
+      <c r="H7" s="468"/>
+      <c r="I7" s="468"/>
+      <c r="J7" s="468"/>
+      <c r="K7" s="468"/>
+      <c r="L7" s="468"/>
+      <c r="M7" s="468"/>
+      <c r="N7" s="468"/>
+      <c r="O7" s="468"/>
+      <c r="Q7" s="334" t="s">
         <v>143</v>
       </c>
-      <c r="R7" s="335">
+      <c r="R7" s="334">
         <v>25</v>
       </c>
-      <c r="T7" s="400" t="s">
+      <c r="T7" s="399" t="s">
         <v>155</v>
       </c>
-      <c r="U7" s="404"/>
-    </row>
-    <row r="8" spans="1:21" s="325" customFormat="1" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="426" t="s">
+      <c r="U7" s="403"/>
+    </row>
+    <row r="8" spans="1:21" s="324" customFormat="1" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="469" t="s">
         <v>191</v>
       </c>
-      <c r="B8" s="426"/>
-      <c r="C8" s="426"/>
-      <c r="D8" s="426"/>
-      <c r="E8" s="426"/>
-      <c r="F8" s="426"/>
-      <c r="G8" s="426"/>
-      <c r="H8" s="426"/>
-      <c r="I8" s="426"/>
-      <c r="J8" s="426"/>
-      <c r="K8" s="426"/>
-      <c r="L8" s="426"/>
-      <c r="M8" s="426"/>
-      <c r="N8" s="426"/>
-      <c r="O8" s="426"/>
-      <c r="Q8" s="335" t="s">
+      <c r="B8" s="469"/>
+      <c r="C8" s="469"/>
+      <c r="D8" s="469"/>
+      <c r="E8" s="469"/>
+      <c r="F8" s="469"/>
+      <c r="G8" s="469"/>
+      <c r="H8" s="469"/>
+      <c r="I8" s="469"/>
+      <c r="J8" s="469"/>
+      <c r="K8" s="469"/>
+      <c r="L8" s="469"/>
+      <c r="M8" s="469"/>
+      <c r="N8" s="469"/>
+      <c r="O8" s="469"/>
+      <c r="Q8" s="334" t="s">
         <v>142</v>
       </c>
-      <c r="R8" s="335">
+      <c r="R8" s="334">
         <v>18</v>
       </c>
-      <c r="T8" s="400" t="s">
+      <c r="T8" s="399" t="s">
         <v>235</v>
       </c>
-      <c r="U8" s="405"/>
-    </row>
-    <row r="9" spans="1:21" s="325" customFormat="1" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="336"/>
-      <c r="B9" s="336"/>
-      <c r="C9" s="336"/>
-      <c r="E9" s="336"/>
-      <c r="F9" s="336"/>
-      <c r="G9" s="336"/>
-      <c r="H9" s="336"/>
-      <c r="I9" s="336"/>
-      <c r="J9" s="336"/>
-      <c r="K9" s="336"/>
-      <c r="L9" s="336"/>
-      <c r="M9" s="336"/>
-      <c r="N9" s="336"/>
-      <c r="O9" s="336"/>
-      <c r="Q9" s="337">
+      <c r="U8" s="404"/>
+    </row>
+    <row r="9" spans="1:21" s="324" customFormat="1" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="335"/>
+      <c r="B9" s="335"/>
+      <c r="C9" s="335"/>
+      <c r="E9" s="335"/>
+      <c r="F9" s="335"/>
+      <c r="G9" s="335"/>
+      <c r="H9" s="335"/>
+      <c r="I9" s="335"/>
+      <c r="J9" s="335"/>
+      <c r="K9" s="335"/>
+      <c r="L9" s="335"/>
+      <c r="M9" s="335"/>
+      <c r="N9" s="335"/>
+      <c r="O9" s="335"/>
+      <c r="Q9" s="336">
         <v>2.5</v>
       </c>
-      <c r="R9" s="335">
+      <c r="R9" s="334">
         <v>12</v>
       </c>
-      <c r="T9" s="400" t="s">
+      <c r="T9" s="399" t="s">
         <v>156</v>
       </c>
-      <c r="U9" s="404"/>
-    </row>
-    <row r="10" spans="1:21" s="325" customFormat="1" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C10" s="338"/>
-      <c r="E10" s="339" t="s">
+      <c r="U9" s="403"/>
+    </row>
+    <row r="10" spans="1:21" s="324" customFormat="1" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C10" s="337"/>
+      <c r="E10" s="338" t="s">
         <v>192</v>
       </c>
-      <c r="F10" s="427" t="s">
+      <c r="F10" s="470" t="s">
         <v>193</v>
       </c>
-      <c r="G10" s="428"/>
-      <c r="H10" s="339" t="s">
+      <c r="G10" s="471"/>
+      <c r="H10" s="338" t="s">
         <v>194</v>
       </c>
-      <c r="I10" s="429" t="s">
+      <c r="I10" s="472" t="s">
         <v>195</v>
       </c>
-      <c r="J10" s="429"/>
-      <c r="K10" s="429"/>
-      <c r="L10" s="338"/>
-      <c r="M10" s="417"/>
-      <c r="N10" s="417"/>
-      <c r="O10" s="417"/>
-      <c r="P10" s="340"/>
-      <c r="Q10" s="341" t="s">
+      <c r="J10" s="472"/>
+      <c r="K10" s="472"/>
+      <c r="L10" s="337"/>
+      <c r="M10" s="473"/>
+      <c r="N10" s="473"/>
+      <c r="O10" s="473"/>
+      <c r="P10" s="339"/>
+      <c r="Q10" s="340" t="s">
         <v>138</v>
       </c>
-      <c r="R10" s="335">
+      <c r="R10" s="334">
         <v>8</v>
       </c>
-      <c r="T10" s="403"/>
-      <c r="U10" s="404"/>
-    </row>
-    <row r="11" spans="1:21" s="325" customFormat="1" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="342"/>
-      <c r="B11" s="417"/>
-      <c r="C11" s="417"/>
-      <c r="D11" s="417"/>
-      <c r="E11" s="343"/>
-      <c r="F11" s="418"/>
-      <c r="G11" s="419"/>
-      <c r="H11" s="344"/>
-      <c r="I11" s="418"/>
-      <c r="J11" s="420"/>
-      <c r="K11" s="419"/>
-      <c r="L11" s="338"/>
-      <c r="M11" s="417"/>
-      <c r="N11" s="417"/>
-      <c r="O11" s="417"/>
-      <c r="P11" s="340"/>
-      <c r="Q11" s="341" t="s">
+      <c r="T10" s="402"/>
+      <c r="U10" s="403"/>
+    </row>
+    <row r="11" spans="1:21" s="324" customFormat="1" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="341"/>
+      <c r="B11" s="473"/>
+      <c r="C11" s="473"/>
+      <c r="D11" s="473"/>
+      <c r="E11" s="342"/>
+      <c r="F11" s="483"/>
+      <c r="G11" s="484"/>
+      <c r="H11" s="343"/>
+      <c r="I11" s="483"/>
+      <c r="J11" s="485"/>
+      <c r="K11" s="484"/>
+      <c r="L11" s="337"/>
+      <c r="M11" s="473"/>
+      <c r="N11" s="473"/>
+      <c r="O11" s="473"/>
+      <c r="P11" s="339"/>
+      <c r="Q11" s="340" t="s">
         <v>62</v>
       </c>
-      <c r="R11" s="335">
+      <c r="R11" s="334">
         <v>5</v>
       </c>
-      <c r="T11" s="400" t="s">
+      <c r="T11" s="399" t="s">
         <v>11</v>
       </c>
-      <c r="U11" s="404"/>
-    </row>
-    <row r="12" spans="1:21" s="325" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="342"/>
-      <c r="B12" s="338"/>
-      <c r="C12" s="345"/>
-      <c r="D12" s="345"/>
-      <c r="E12" s="345"/>
-      <c r="F12" s="345"/>
-      <c r="G12" s="345"/>
-      <c r="H12" s="345"/>
-      <c r="I12" s="345"/>
-      <c r="J12" s="345"/>
-      <c r="K12" s="345"/>
-      <c r="L12" s="345"/>
-      <c r="M12" s="345"/>
-      <c r="N12" s="345"/>
-      <c r="O12" s="346"/>
-      <c r="P12" s="340"/>
-      <c r="Q12" s="341" t="s">
+      <c r="U11" s="403"/>
+    </row>
+    <row r="12" spans="1:21" s="324" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="341"/>
+      <c r="B12" s="337"/>
+      <c r="C12" s="344"/>
+      <c r="D12" s="344"/>
+      <c r="E12" s="344"/>
+      <c r="F12" s="344"/>
+      <c r="G12" s="344"/>
+      <c r="H12" s="344"/>
+      <c r="I12" s="344"/>
+      <c r="J12" s="344"/>
+      <c r="K12" s="344"/>
+      <c r="L12" s="344"/>
+      <c r="M12" s="344"/>
+      <c r="N12" s="344"/>
+      <c r="O12" s="345"/>
+      <c r="P12" s="339"/>
+      <c r="Q12" s="340" t="s">
         <v>139</v>
       </c>
-      <c r="R12" s="335">
+      <c r="R12" s="334">
         <v>4</v>
       </c>
-      <c r="T12" s="400" t="s">
+      <c r="T12" s="399" t="s">
         <v>13</v>
       </c>
-      <c r="U12" s="405"/>
-    </row>
-    <row r="13" spans="1:21" s="325" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="421" t="s">
+      <c r="U12" s="404"/>
+    </row>
+    <row r="13" spans="1:21" s="324" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="486" t="s">
         <v>196</v>
       </c>
-      <c r="B13" s="422"/>
-      <c r="C13" s="422"/>
-      <c r="D13" s="422"/>
-      <c r="E13" s="422"/>
-      <c r="F13" s="422"/>
-      <c r="G13" s="422"/>
-      <c r="H13" s="422"/>
-      <c r="I13" s="422"/>
-      <c r="J13" s="422"/>
-      <c r="K13" s="422"/>
-      <c r="L13" s="422"/>
-      <c r="M13" s="422"/>
-      <c r="N13" s="422"/>
-      <c r="O13" s="423"/>
-      <c r="P13" s="340"/>
-      <c r="Q13" s="341" t="s">
+      <c r="B13" s="487"/>
+      <c r="C13" s="487"/>
+      <c r="D13" s="487"/>
+      <c r="E13" s="487"/>
+      <c r="F13" s="487"/>
+      <c r="G13" s="487"/>
+      <c r="H13" s="487"/>
+      <c r="I13" s="487"/>
+      <c r="J13" s="487"/>
+      <c r="K13" s="487"/>
+      <c r="L13" s="487"/>
+      <c r="M13" s="487"/>
+      <c r="N13" s="487"/>
+      <c r="O13" s="488"/>
+      <c r="P13" s="339"/>
+      <c r="Q13" s="340" t="s">
         <v>137</v>
       </c>
-      <c r="R13" s="335">
+      <c r="R13" s="334">
         <v>3</v>
       </c>
-      <c r="T13" s="400" t="s">
+      <c r="T13" s="399" t="s">
         <v>14</v>
       </c>
-      <c r="U13" s="405"/>
-    </row>
-    <row r="14" spans="1:21" s="325" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="408" t="s">
+      <c r="U13" s="404"/>
+    </row>
+    <row r="14" spans="1:21" s="324" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="474" t="s">
         <v>197</v>
       </c>
-      <c r="B14" s="409"/>
-      <c r="C14" s="409"/>
-      <c r="D14" s="409"/>
-      <c r="E14" s="409"/>
-      <c r="F14" s="409"/>
-      <c r="G14" s="409"/>
-      <c r="H14" s="409"/>
-      <c r="I14" s="409"/>
-      <c r="J14" s="409"/>
-      <c r="K14" s="409"/>
-      <c r="L14" s="409"/>
-      <c r="M14" s="409"/>
-      <c r="N14" s="409"/>
-      <c r="O14" s="410"/>
-      <c r="P14" s="340"/>
-      <c r="Q14" s="341" t="s">
+      <c r="B14" s="475"/>
+      <c r="C14" s="475"/>
+      <c r="D14" s="475"/>
+      <c r="E14" s="475"/>
+      <c r="F14" s="475"/>
+      <c r="G14" s="475"/>
+      <c r="H14" s="475"/>
+      <c r="I14" s="475"/>
+      <c r="J14" s="475"/>
+      <c r="K14" s="475"/>
+      <c r="L14" s="475"/>
+      <c r="M14" s="475"/>
+      <c r="N14" s="475"/>
+      <c r="O14" s="476"/>
+      <c r="P14" s="339"/>
+      <c r="Q14" s="340" t="s">
         <v>183</v>
       </c>
-      <c r="R14" s="335">
+      <c r="R14" s="334">
         <v>2</v>
       </c>
-      <c r="T14" s="403"/>
-      <c r="U14" s="404"/>
-    </row>
-    <row r="15" spans="1:21" s="325" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="347"/>
-      <c r="B15" s="347"/>
-      <c r="C15" s="347"/>
-      <c r="D15" s="347"/>
-      <c r="E15" s="347"/>
-      <c r="F15" s="347"/>
-      <c r="G15" s="347"/>
-      <c r="H15" s="347"/>
-      <c r="I15" s="347"/>
-      <c r="J15" s="347"/>
-      <c r="K15" s="347"/>
-      <c r="L15" s="347"/>
-      <c r="M15" s="347"/>
-      <c r="N15" s="347"/>
-      <c r="O15" s="347"/>
-      <c r="P15" s="340"/>
-      <c r="Q15" s="341" t="s">
+      <c r="T14" s="402"/>
+      <c r="U14" s="403"/>
+    </row>
+    <row r="15" spans="1:21" s="324" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="346"/>
+      <c r="B15" s="346"/>
+      <c r="C15" s="346"/>
+      <c r="D15" s="346"/>
+      <c r="E15" s="346"/>
+      <c r="F15" s="346"/>
+      <c r="G15" s="346"/>
+      <c r="H15" s="346"/>
+      <c r="I15" s="346"/>
+      <c r="J15" s="346"/>
+      <c r="K15" s="346"/>
+      <c r="L15" s="346"/>
+      <c r="M15" s="346"/>
+      <c r="N15" s="346"/>
+      <c r="O15" s="346"/>
+      <c r="P15" s="339"/>
+      <c r="Q15" s="340" t="s">
         <v>140</v>
       </c>
-      <c r="R15" s="335">
+      <c r="R15" s="334">
         <v>2</v>
       </c>
-      <c r="T15" s="400" t="s">
+      <c r="T15" s="399" t="s">
         <v>10</v>
       </c>
-      <c r="U15" s="406"/>
-    </row>
-    <row r="16" spans="1:21" s="325" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="347"/>
-      <c r="B16" s="411" t="s">
+      <c r="U15" s="405"/>
+    </row>
+    <row r="16" spans="1:21" s="324" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="346"/>
+      <c r="B16" s="477" t="s">
         <v>198</v>
       </c>
-      <c r="C16" s="412"/>
-      <c r="D16" s="412"/>
-      <c r="E16" s="412"/>
-      <c r="F16" s="413"/>
-      <c r="G16" s="347"/>
-      <c r="H16" s="414" t="s">
+      <c r="C16" s="478"/>
+      <c r="D16" s="478"/>
+      <c r="E16" s="478"/>
+      <c r="F16" s="479"/>
+      <c r="G16" s="346"/>
+      <c r="H16" s="480" t="s">
         <v>199</v>
       </c>
-      <c r="I16" s="415"/>
-      <c r="J16" s="416"/>
-      <c r="K16" s="424" t="s">
+      <c r="I16" s="481"/>
+      <c r="J16" s="482"/>
+      <c r="K16" s="489" t="s">
         <v>200</v>
       </c>
-      <c r="L16" s="424"/>
-      <c r="M16" s="347"/>
-      <c r="N16" s="347"/>
-      <c r="O16" s="347"/>
-      <c r="P16" s="340"/>
-      <c r="Q16" s="348" t="s">
+      <c r="L16" s="489"/>
+      <c r="M16" s="346"/>
+      <c r="N16" s="346"/>
+      <c r="O16" s="346"/>
+      <c r="P16" s="339"/>
+      <c r="Q16" s="347" t="s">
         <v>201</v>
       </c>
-      <c r="T16" s="400" t="s">
+      <c r="T16" s="399" t="s">
         <v>12</v>
       </c>
-      <c r="U16" s="406"/>
-    </row>
-    <row r="17" spans="1:22" s="325" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="347"/>
-      <c r="B17" s="430" t="s">
+      <c r="U16" s="405"/>
+    </row>
+    <row r="17" spans="1:22" s="324" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="346"/>
+      <c r="B17" s="446" t="s">
         <v>202</v>
       </c>
-      <c r="C17" s="431"/>
-      <c r="D17" s="432"/>
-      <c r="E17" s="393"/>
-      <c r="F17" s="394"/>
-      <c r="G17" s="347"/>
-      <c r="H17" s="435" t="s">
+      <c r="C17" s="447"/>
+      <c r="D17" s="448"/>
+      <c r="E17" s="392"/>
+      <c r="F17" s="393"/>
+      <c r="G17" s="346"/>
+      <c r="H17" s="451" t="s">
         <v>203</v>
       </c>
-      <c r="I17" s="436"/>
-      <c r="J17" s="437"/>
-      <c r="K17" s="438"/>
-      <c r="L17" s="439"/>
-      <c r="M17" s="347"/>
-      <c r="N17" s="347"/>
-      <c r="O17" s="347"/>
-      <c r="P17" s="349"/>
-      <c r="Q17" s="340"/>
-      <c r="T17" s="400" t="s">
+      <c r="I17" s="452"/>
+      <c r="J17" s="453"/>
+      <c r="K17" s="427"/>
+      <c r="L17" s="429"/>
+      <c r="M17" s="346"/>
+      <c r="N17" s="346"/>
+      <c r="O17" s="346"/>
+      <c r="P17" s="348"/>
+      <c r="Q17" s="339"/>
+      <c r="T17" s="399" t="s">
         <v>236</v>
       </c>
-      <c r="U17" s="407"/>
-    </row>
-    <row r="18" spans="1:22" s="325" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="347"/>
-      <c r="B18" s="430" t="s">
+      <c r="U17" s="406"/>
+    </row>
+    <row r="18" spans="1:22" s="324" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="346"/>
+      <c r="B18" s="446" t="s">
         <v>204</v>
       </c>
-      <c r="C18" s="431"/>
-      <c r="D18" s="432"/>
-      <c r="E18" s="433" t="s">
+      <c r="C18" s="447"/>
+      <c r="D18" s="448"/>
+      <c r="E18" s="449" t="s">
         <v>237</v>
       </c>
-      <c r="F18" s="434"/>
-      <c r="G18" s="347"/>
-      <c r="H18" s="435" t="s">
+      <c r="F18" s="450"/>
+      <c r="G18" s="346"/>
+      <c r="H18" s="451" t="s">
         <v>205</v>
       </c>
-      <c r="I18" s="436"/>
-      <c r="J18" s="437"/>
-      <c r="K18" s="438"/>
-      <c r="L18" s="439"/>
-      <c r="M18" s="347"/>
-      <c r="N18" s="347"/>
-      <c r="O18" s="347"/>
-      <c r="P18" s="340"/>
-      <c r="Q18" s="340"/>
-    </row>
-    <row r="19" spans="1:22" s="325" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="347"/>
-      <c r="B19" s="430" t="s">
+      <c r="I18" s="452"/>
+      <c r="J18" s="453"/>
+      <c r="K18" s="427"/>
+      <c r="L18" s="429"/>
+      <c r="M18" s="346"/>
+      <c r="N18" s="346"/>
+      <c r="O18" s="346"/>
+      <c r="P18" s="339"/>
+      <c r="Q18" s="339"/>
+    </row>
+    <row r="19" spans="1:22" s="324" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="346"/>
+      <c r="B19" s="446" t="s">
         <v>206</v>
       </c>
-      <c r="C19" s="431"/>
-      <c r="D19" s="432"/>
-      <c r="E19" s="433" t="s">
+      <c r="C19" s="447"/>
+      <c r="D19" s="448"/>
+      <c r="E19" s="449" t="s">
         <v>237</v>
       </c>
-      <c r="F19" s="434"/>
-      <c r="G19" s="347"/>
-      <c r="H19" s="435" t="s">
+      <c r="F19" s="450"/>
+      <c r="G19" s="346"/>
+      <c r="H19" s="451" t="s">
         <v>207</v>
       </c>
-      <c r="I19" s="436"/>
-      <c r="J19" s="437"/>
-      <c r="K19" s="438"/>
-      <c r="L19" s="439"/>
-      <c r="M19" s="347"/>
-      <c r="N19" s="347"/>
-      <c r="O19" s="347"/>
-      <c r="P19" s="340"/>
-      <c r="Q19" s="340"/>
-    </row>
-    <row r="20" spans="1:22" s="325" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="347"/>
-      <c r="B20" s="430" t="s">
+      <c r="I19" s="452"/>
+      <c r="J19" s="453"/>
+      <c r="K19" s="427"/>
+      <c r="L19" s="429"/>
+      <c r="M19" s="346"/>
+      <c r="N19" s="346"/>
+      <c r="O19" s="346"/>
+      <c r="P19" s="339"/>
+      <c r="Q19" s="339"/>
+    </row>
+    <row r="20" spans="1:22" s="324" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="346"/>
+      <c r="B20" s="446" t="s">
         <v>208</v>
       </c>
-      <c r="C20" s="431"/>
-      <c r="D20" s="432"/>
-      <c r="E20" s="433" t="s">
+      <c r="C20" s="447"/>
+      <c r="D20" s="448"/>
+      <c r="E20" s="449" t="s">
         <v>237</v>
       </c>
-      <c r="F20" s="434"/>
-      <c r="G20" s="347"/>
-      <c r="H20" s="442" t="s">
+      <c r="F20" s="450"/>
+      <c r="G20" s="346"/>
+      <c r="H20" s="456" t="s">
         <v>209</v>
       </c>
-      <c r="I20" s="443"/>
-      <c r="J20" s="444"/>
-      <c r="K20" s="448"/>
-      <c r="L20" s="449"/>
-      <c r="M20" s="347"/>
-      <c r="N20" s="347"/>
-      <c r="O20" s="347"/>
-      <c r="P20" s="340"/>
-      <c r="Q20" s="340"/>
-    </row>
-    <row r="21" spans="1:22" s="325" customFormat="1" ht="7.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="347"/>
-      <c r="B21" s="347"/>
-      <c r="C21" s="347"/>
-      <c r="D21" s="347"/>
-      <c r="E21" s="347"/>
-      <c r="F21" s="347"/>
-      <c r="G21" s="347"/>
-      <c r="H21" s="445"/>
-      <c r="I21" s="446"/>
-      <c r="J21" s="447"/>
-      <c r="K21" s="450"/>
-      <c r="L21" s="451"/>
-      <c r="M21" s="347"/>
-      <c r="N21" s="347"/>
-      <c r="O21" s="347"/>
-      <c r="P21" s="340"/>
-      <c r="Q21" s="340"/>
-    </row>
-    <row r="22" spans="1:22" s="325" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="347"/>
-      <c r="B22" s="430" t="s">
+      <c r="I20" s="457"/>
+      <c r="J20" s="458"/>
+      <c r="K20" s="462"/>
+      <c r="L20" s="463"/>
+      <c r="M20" s="346"/>
+      <c r="N20" s="346"/>
+      <c r="O20" s="346"/>
+      <c r="P20" s="339"/>
+      <c r="Q20" s="339"/>
+    </row>
+    <row r="21" spans="1:22" s="324" customFormat="1" ht="7.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="346"/>
+      <c r="B21" s="346"/>
+      <c r="C21" s="346"/>
+      <c r="D21" s="346"/>
+      <c r="E21" s="346"/>
+      <c r="F21" s="346"/>
+      <c r="G21" s="346"/>
+      <c r="H21" s="459"/>
+      <c r="I21" s="460"/>
+      <c r="J21" s="461"/>
+      <c r="K21" s="464"/>
+      <c r="L21" s="465"/>
+      <c r="M21" s="346"/>
+      <c r="N21" s="346"/>
+      <c r="O21" s="346"/>
+      <c r="P21" s="339"/>
+      <c r="Q21" s="339"/>
+    </row>
+    <row r="22" spans="1:22" s="324" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="346"/>
+      <c r="B22" s="446" t="s">
         <v>210</v>
       </c>
-      <c r="C22" s="431"/>
-      <c r="D22" s="432"/>
-      <c r="E22" s="452"/>
-      <c r="F22" s="453"/>
-      <c r="G22" s="347"/>
-      <c r="H22" s="435" t="s">
+      <c r="C22" s="447"/>
+      <c r="D22" s="448"/>
+      <c r="E22" s="466"/>
+      <c r="F22" s="467"/>
+      <c r="G22" s="346"/>
+      <c r="H22" s="451" t="s">
         <v>211</v>
       </c>
-      <c r="I22" s="436"/>
-      <c r="J22" s="437"/>
-      <c r="K22" s="435"/>
-      <c r="L22" s="437"/>
-      <c r="M22" s="347"/>
-      <c r="N22" s="347"/>
-      <c r="O22" s="347"/>
-      <c r="P22" s="340"/>
-      <c r="Q22" s="340"/>
-    </row>
-    <row r="23" spans="1:22" s="325" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="347"/>
-      <c r="B23" s="430" t="s">
+      <c r="I22" s="452"/>
+      <c r="J22" s="453"/>
+      <c r="K22" s="451"/>
+      <c r="L22" s="453"/>
+      <c r="M22" s="346"/>
+      <c r="N22" s="346"/>
+      <c r="O22" s="346"/>
+      <c r="P22" s="339"/>
+      <c r="Q22" s="339"/>
+    </row>
+    <row r="23" spans="1:22" s="324" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="346"/>
+      <c r="B23" s="446" t="s">
         <v>212</v>
       </c>
-      <c r="C23" s="431"/>
-      <c r="D23" s="432"/>
-      <c r="E23" s="452"/>
-      <c r="F23" s="453"/>
-      <c r="G23" s="347"/>
-      <c r="H23" s="454" t="s">
+      <c r="C23" s="447"/>
+      <c r="D23" s="448"/>
+      <c r="E23" s="466"/>
+      <c r="F23" s="467"/>
+      <c r="G23" s="346"/>
+      <c r="H23" s="434" t="s">
         <v>213</v>
       </c>
-      <c r="I23" s="455"/>
-      <c r="J23" s="456"/>
-      <c r="K23" s="454"/>
-      <c r="L23" s="456"/>
-      <c r="M23" s="347"/>
-      <c r="N23" s="347"/>
-      <c r="O23" s="347"/>
-      <c r="P23" s="340"/>
-      <c r="Q23" s="340"/>
-    </row>
-    <row r="24" spans="1:22" s="325" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="347"/>
-      <c r="B24" s="350" t="s">
+      <c r="I23" s="435"/>
+      <c r="J23" s="436"/>
+      <c r="K23" s="434"/>
+      <c r="L23" s="436"/>
+      <c r="M23" s="346"/>
+      <c r="N23" s="346"/>
+      <c r="O23" s="346"/>
+      <c r="P23" s="339"/>
+      <c r="Q23" s="339"/>
+    </row>
+    <row r="24" spans="1:22" s="324" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="346"/>
+      <c r="B24" s="349" t="s">
         <v>214</v>
       </c>
-      <c r="C24" s="351"/>
-      <c r="D24" s="351"/>
-      <c r="E24" s="351"/>
-      <c r="F24" s="351"/>
-      <c r="G24" s="347"/>
-      <c r="H24" s="347"/>
-      <c r="I24" s="347"/>
-      <c r="J24" s="347"/>
-      <c r="K24" s="347"/>
-      <c r="L24" s="347"/>
-      <c r="M24" s="347"/>
-      <c r="N24" s="457"/>
-      <c r="O24" s="457"/>
-      <c r="P24" s="340"/>
-      <c r="Q24" s="340"/>
-    </row>
-    <row r="25" spans="1:22" s="325" customFormat="1" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="347"/>
-      <c r="B25" s="352"/>
-      <c r="C25" s="352"/>
-      <c r="D25" s="352"/>
-      <c r="E25" s="352"/>
-      <c r="F25" s="352"/>
-      <c r="G25" s="347"/>
-      <c r="H25" s="347"/>
-      <c r="I25" s="347"/>
-      <c r="J25" s="347"/>
-      <c r="K25" s="347"/>
-      <c r="L25" s="347"/>
-      <c r="M25" s="347"/>
-      <c r="N25" s="347"/>
-      <c r="O25" s="347"/>
-      <c r="P25" s="340"/>
-      <c r="Q25" s="340"/>
-    </row>
-    <row r="26" spans="1:22" s="325" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="347"/>
-      <c r="B26" s="440" t="s">
+      <c r="C24" s="350"/>
+      <c r="D24" s="350"/>
+      <c r="E24" s="350"/>
+      <c r="F24" s="350"/>
+      <c r="G24" s="346"/>
+      <c r="H24" s="346"/>
+      <c r="I24" s="346"/>
+      <c r="J24" s="346"/>
+      <c r="K24" s="346"/>
+      <c r="L24" s="346"/>
+      <c r="M24" s="346"/>
+      <c r="N24" s="437"/>
+      <c r="O24" s="437"/>
+      <c r="P24" s="339"/>
+      <c r="Q24" s="339"/>
+    </row>
+    <row r="25" spans="1:22" s="324" customFormat="1" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="346"/>
+      <c r="B25" s="351"/>
+      <c r="C25" s="351"/>
+      <c r="D25" s="351"/>
+      <c r="E25" s="351"/>
+      <c r="F25" s="351"/>
+      <c r="G25" s="346"/>
+      <c r="H25" s="346"/>
+      <c r="I25" s="346"/>
+      <c r="J25" s="346"/>
+      <c r="K25" s="346"/>
+      <c r="L25" s="346"/>
+      <c r="M25" s="346"/>
+      <c r="N25" s="346"/>
+      <c r="O25" s="346"/>
+      <c r="P25" s="339"/>
+      <c r="Q25" s="339"/>
+    </row>
+    <row r="26" spans="1:22" s="324" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="346"/>
+      <c r="B26" s="454" t="s">
         <v>25</v>
       </c>
-      <c r="C26" s="440"/>
-      <c r="D26" s="440"/>
-      <c r="E26" s="440"/>
-      <c r="F26" s="440"/>
-      <c r="G26" s="440"/>
-      <c r="H26" s="440"/>
-      <c r="I26" s="440"/>
-      <c r="J26" s="347"/>
-      <c r="K26" s="441" t="s">
+      <c r="C26" s="454"/>
+      <c r="D26" s="454"/>
+      <c r="E26" s="454"/>
+      <c r="F26" s="454"/>
+      <c r="G26" s="454"/>
+      <c r="H26" s="454"/>
+      <c r="I26" s="454"/>
+      <c r="J26" s="346"/>
+      <c r="K26" s="455" t="s">
         <v>215</v>
       </c>
-      <c r="L26" s="441"/>
-      <c r="M26" s="441"/>
-      <c r="N26" s="441"/>
-      <c r="O26" s="353"/>
-      <c r="P26" s="340"/>
-      <c r="Q26" s="340"/>
-    </row>
-    <row r="27" spans="1:22" s="325" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="347"/>
-      <c r="B27" s="463" t="s">
+      <c r="L26" s="455"/>
+      <c r="M26" s="455"/>
+      <c r="N26" s="455"/>
+      <c r="O26" s="352"/>
+      <c r="P26" s="339"/>
+      <c r="Q26" s="339"/>
+    </row>
+    <row r="27" spans="1:22" s="324" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="346"/>
+      <c r="B27" s="439" t="s">
         <v>216</v>
       </c>
-      <c r="C27" s="464"/>
-      <c r="D27" s="464"/>
-      <c r="E27" s="464"/>
-      <c r="F27" s="464"/>
-      <c r="G27" s="465"/>
-      <c r="H27" s="466"/>
-      <c r="I27" s="467"/>
-      <c r="J27" s="347"/>
-      <c r="K27" s="468" t="s">
+      <c r="C27" s="440"/>
+      <c r="D27" s="440"/>
+      <c r="E27" s="440"/>
+      <c r="F27" s="440"/>
+      <c r="G27" s="441"/>
+      <c r="H27" s="442"/>
+      <c r="I27" s="443"/>
+      <c r="J27" s="346"/>
+      <c r="K27" s="423" t="s">
         <v>217</v>
       </c>
-      <c r="L27" s="468"/>
-      <c r="M27" s="468"/>
-      <c r="N27" s="468"/>
-      <c r="O27" s="353"/>
-      <c r="P27" s="340"/>
-      <c r="Q27" s="340"/>
-    </row>
-    <row r="28" spans="1:22" s="325" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="347"/>
-      <c r="B28" s="354" t="s">
+      <c r="L27" s="423"/>
+      <c r="M27" s="423"/>
+      <c r="N27" s="423"/>
+      <c r="O27" s="352"/>
+      <c r="P27" s="339"/>
+      <c r="Q27" s="339"/>
+    </row>
+    <row r="28" spans="1:22" s="324" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="346"/>
+      <c r="B28" s="353" t="s">
         <v>218</v>
       </c>
-      <c r="C28" s="355"/>
-      <c r="D28" s="355"/>
-      <c r="E28" s="355"/>
-      <c r="F28" s="355"/>
-      <c r="G28" s="355"/>
-      <c r="H28" s="469"/>
-      <c r="I28" s="470"/>
-      <c r="J28" s="347"/>
-      <c r="K28" s="468" t="s">
+      <c r="C28" s="354"/>
+      <c r="D28" s="354"/>
+      <c r="E28" s="354"/>
+      <c r="F28" s="354"/>
+      <c r="G28" s="354"/>
+      <c r="H28" s="444"/>
+      <c r="I28" s="445"/>
+      <c r="J28" s="346"/>
+      <c r="K28" s="423" t="s">
         <v>219</v>
       </c>
-      <c r="L28" s="468"/>
-      <c r="M28" s="468"/>
-      <c r="N28" s="468"/>
-      <c r="O28" s="353"/>
-      <c r="P28" s="340"/>
-      <c r="Q28" s="340"/>
-    </row>
-    <row r="29" spans="1:22" s="325" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="347"/>
-      <c r="B29" s="354" t="s">
+      <c r="L28" s="423"/>
+      <c r="M28" s="423"/>
+      <c r="N28" s="423"/>
+      <c r="O28" s="352"/>
+      <c r="P28" s="339"/>
+      <c r="Q28" s="339"/>
+    </row>
+    <row r="29" spans="1:22" s="324" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="346"/>
+      <c r="B29" s="353" t="s">
         <v>220</v>
       </c>
-      <c r="C29" s="355"/>
-      <c r="D29" s="355"/>
-      <c r="E29" s="355"/>
-      <c r="F29" s="355"/>
-      <c r="G29" s="355"/>
-      <c r="H29" s="469"/>
-      <c r="I29" s="470"/>
-      <c r="J29" s="347"/>
-      <c r="K29" s="468" t="s">
+      <c r="C29" s="354"/>
+      <c r="D29" s="354"/>
+      <c r="E29" s="354"/>
+      <c r="F29" s="354"/>
+      <c r="G29" s="354"/>
+      <c r="H29" s="444"/>
+      <c r="I29" s="445"/>
+      <c r="J29" s="346"/>
+      <c r="K29" s="423" t="s">
         <v>221</v>
       </c>
-      <c r="L29" s="468"/>
-      <c r="M29" s="468"/>
-      <c r="N29" s="468"/>
-      <c r="O29" s="353"/>
-      <c r="P29" s="340"/>
-      <c r="Q29" s="340"/>
-    </row>
-    <row r="30" spans="1:22" s="325" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="347"/>
-      <c r="B30" s="347"/>
-      <c r="C30" s="347"/>
-      <c r="D30" s="347"/>
-      <c r="E30" s="347"/>
-      <c r="F30" s="347"/>
-      <c r="G30" s="347"/>
-      <c r="H30" s="347"/>
-      <c r="I30" s="347"/>
-      <c r="J30" s="347"/>
-      <c r="K30" s="356"/>
-      <c r="L30" s="347"/>
-      <c r="M30" s="347"/>
-      <c r="N30" s="347"/>
-      <c r="O30" s="347"/>
-      <c r="P30" s="340"/>
-      <c r="Q30" s="340"/>
-    </row>
-    <row r="31" spans="1:22" s="325" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="347"/>
-      <c r="B31" s="458" t="s">
+      <c r="L29" s="423"/>
+      <c r="M29" s="423"/>
+      <c r="N29" s="423"/>
+      <c r="O29" s="352"/>
+      <c r="P29" s="339"/>
+      <c r="Q29" s="339"/>
+    </row>
+    <row r="30" spans="1:22" s="324" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="346"/>
+      <c r="B30" s="346"/>
+      <c r="C30" s="346"/>
+      <c r="D30" s="346"/>
+      <c r="E30" s="346"/>
+      <c r="F30" s="346"/>
+      <c r="G30" s="346"/>
+      <c r="H30" s="346"/>
+      <c r="I30" s="346"/>
+      <c r="J30" s="346"/>
+      <c r="K30" s="355"/>
+      <c r="L30" s="346"/>
+      <c r="M30" s="346"/>
+      <c r="N30" s="346"/>
+      <c r="O30" s="346"/>
+      <c r="P30" s="339"/>
+      <c r="Q30" s="339"/>
+    </row>
+    <row r="31" spans="1:22" s="324" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="346"/>
+      <c r="B31" s="438" t="s">
         <v>222</v>
       </c>
-      <c r="C31" s="458"/>
-      <c r="D31" s="458"/>
-      <c r="E31" s="458"/>
-      <c r="F31" s="458"/>
-      <c r="G31" s="458"/>
-      <c r="H31" s="458"/>
-      <c r="I31" s="458"/>
-      <c r="J31" s="458"/>
-      <c r="K31" s="458"/>
-      <c r="L31" s="458"/>
-      <c r="M31" s="458"/>
-      <c r="N31" s="458"/>
-      <c r="O31" s="458"/>
-      <c r="P31" s="340"/>
-      <c r="Q31" s="340"/>
-    </row>
-    <row r="32" spans="1:22" s="325" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B32" s="357"/>
-      <c r="C32" s="348"/>
-      <c r="D32" s="348"/>
-      <c r="E32" s="348"/>
-      <c r="F32" s="348"/>
-      <c r="G32" s="348"/>
-      <c r="H32" s="348"/>
-      <c r="I32" s="348"/>
-      <c r="J32" s="348"/>
-      <c r="K32" s="348"/>
-      <c r="L32" s="348"/>
-      <c r="M32" s="348"/>
-      <c r="N32" s="348"/>
-      <c r="O32" s="348"/>
-      <c r="Q32" s="340"/>
-      <c r="T32" s="358"/>
-      <c r="U32" s="358"/>
-      <c r="V32" s="358"/>
-    </row>
-    <row r="33" spans="1:28" s="325" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B33" s="459" t="s">
+      <c r="C31" s="438"/>
+      <c r="D31" s="438"/>
+      <c r="E31" s="438"/>
+      <c r="F31" s="438"/>
+      <c r="G31" s="438"/>
+      <c r="H31" s="438"/>
+      <c r="I31" s="438"/>
+      <c r="J31" s="438"/>
+      <c r="K31" s="438"/>
+      <c r="L31" s="438"/>
+      <c r="M31" s="438"/>
+      <c r="N31" s="438"/>
+      <c r="O31" s="438"/>
+      <c r="P31" s="339"/>
+      <c r="Q31" s="339"/>
+    </row>
+    <row r="32" spans="1:22" s="324" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B32" s="356"/>
+      <c r="C32" s="347"/>
+      <c r="D32" s="347"/>
+      <c r="E32" s="347"/>
+      <c r="F32" s="347"/>
+      <c r="G32" s="347"/>
+      <c r="H32" s="347"/>
+      <c r="I32" s="347"/>
+      <c r="J32" s="347"/>
+      <c r="K32" s="347"/>
+      <c r="L32" s="347"/>
+      <c r="M32" s="347"/>
+      <c r="N32" s="347"/>
+      <c r="O32" s="347"/>
+      <c r="Q32" s="339"/>
+      <c r="T32" s="357"/>
+      <c r="U32" s="357"/>
+      <c r="V32" s="357"/>
+    </row>
+    <row r="33" spans="1:28" s="324" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B33" s="430" t="s">
         <v>41</v>
       </c>
-      <c r="C33" s="460"/>
-      <c r="D33" s="460"/>
-      <c r="E33" s="460"/>
-      <c r="F33" s="460"/>
-      <c r="G33" s="460"/>
-      <c r="H33" s="460"/>
-      <c r="I33" s="460"/>
-      <c r="J33" s="460"/>
-      <c r="K33" s="461"/>
-      <c r="L33" s="359" t="s">
+      <c r="C33" s="431"/>
+      <c r="D33" s="431"/>
+      <c r="E33" s="431"/>
+      <c r="F33" s="431"/>
+      <c r="G33" s="431"/>
+      <c r="H33" s="431"/>
+      <c r="I33" s="431"/>
+      <c r="J33" s="431"/>
+      <c r="K33" s="432"/>
+      <c r="L33" s="358" t="s">
         <v>223</v>
       </c>
-      <c r="M33" s="462" t="s">
+      <c r="M33" s="433" t="s">
         <v>18</v>
       </c>
-      <c r="N33" s="462"/>
-      <c r="O33" s="462"/>
-      <c r="Q33" s="340"/>
-      <c r="R33" s="360"/>
-      <c r="T33" s="358"/>
-      <c r="U33" s="358"/>
-      <c r="V33" s="358"/>
-    </row>
-    <row r="34" spans="1:28" s="325" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B34" s="361" t="s">
+      <c r="N33" s="433"/>
+      <c r="O33" s="433"/>
+      <c r="Q33" s="339"/>
+      <c r="R33" s="359"/>
+      <c r="T33" s="357"/>
+      <c r="U33" s="357"/>
+      <c r="V33" s="357"/>
+    </row>
+    <row r="34" spans="1:28" s="324" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B34" s="360" t="s">
         <v>45</v>
       </c>
-      <c r="C34" s="362" t="s">
+      <c r="C34" s="361" t="s">
         <v>46</v>
       </c>
       <c r="D34" s="69"/>
@@ -9345,23 +9403,23 @@
       <c r="H34" s="69"/>
       <c r="I34" s="69"/>
       <c r="J34" s="69"/>
-      <c r="K34" s="363"/>
+      <c r="K34" s="362"/>
       <c r="L34" s="61" t="s">
         <v>47</v>
       </c>
-      <c r="M34" s="390"/>
-      <c r="N34" s="392"/>
-      <c r="O34" s="391"/>
-      <c r="R34" s="364"/>
-      <c r="T34" s="364"/>
-      <c r="U34" s="358"/>
-      <c r="V34" s="358"/>
-    </row>
-    <row r="35" spans="1:28" s="325" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B35" s="361" t="s">
+      <c r="M34" s="389"/>
+      <c r="N34" s="391"/>
+      <c r="O34" s="390"/>
+      <c r="R34" s="363"/>
+      <c r="T34" s="363"/>
+      <c r="U34" s="357"/>
+      <c r="V34" s="357"/>
+    </row>
+    <row r="35" spans="1:28" s="324" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B35" s="360" t="s">
         <v>48</v>
       </c>
-      <c r="C35" s="362" t="s">
+      <c r="C35" s="361" t="s">
         <v>49</v>
       </c>
       <c r="D35" s="69"/>
@@ -9371,23 +9429,23 @@
       <c r="H35" s="69"/>
       <c r="I35" s="69"/>
       <c r="J35" s="69"/>
-      <c r="K35" s="363"/>
+      <c r="K35" s="362"/>
       <c r="L35" s="61" t="s">
         <v>47</v>
       </c>
-      <c r="M35" s="390"/>
-      <c r="N35" s="392"/>
-      <c r="O35" s="391"/>
-      <c r="R35" s="365"/>
-      <c r="T35" s="366"/>
-      <c r="U35" s="358"/>
-      <c r="V35" s="358"/>
-    </row>
-    <row r="36" spans="1:28" s="325" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B36" s="361" t="s">
+      <c r="M35" s="389"/>
+      <c r="N35" s="391"/>
+      <c r="O35" s="390"/>
+      <c r="R35" s="364"/>
+      <c r="T35" s="365"/>
+      <c r="U35" s="357"/>
+      <c r="V35" s="357"/>
+    </row>
+    <row r="36" spans="1:28" s="324" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B36" s="360" t="s">
         <v>50</v>
       </c>
-      <c r="C36" s="362" t="s">
+      <c r="C36" s="361" t="s">
         <v>224</v>
       </c>
       <c r="D36" s="69"/>
@@ -9397,415 +9455,415 @@
       <c r="H36" s="69"/>
       <c r="I36" s="69"/>
       <c r="J36" s="69"/>
-      <c r="K36" s="363"/>
-      <c r="L36" s="367" t="s">
+      <c r="K36" s="362"/>
+      <c r="L36" s="366" t="s">
         <v>47</v>
       </c>
-      <c r="M36" s="390"/>
-      <c r="N36" s="392"/>
-      <c r="O36" s="391"/>
-      <c r="R36" s="365"/>
-      <c r="T36" s="366"/>
-      <c r="U36" s="358"/>
-      <c r="V36" s="358"/>
-    </row>
-    <row r="37" spans="1:28" s="325" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B37" s="471" t="s">
+      <c r="M36" s="389"/>
+      <c r="N36" s="391"/>
+      <c r="O36" s="390"/>
+      <c r="R36" s="364"/>
+      <c r="T36" s="365"/>
+      <c r="U36" s="357"/>
+      <c r="V36" s="357"/>
+    </row>
+    <row r="37" spans="1:28" s="324" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B37" s="419" t="s">
         <v>52</v>
       </c>
-      <c r="C37" s="472" t="s">
+      <c r="C37" s="420" t="s">
         <v>53</v>
       </c>
-      <c r="D37" s="472"/>
-      <c r="E37" s="472"/>
-      <c r="F37" s="472"/>
-      <c r="G37" s="472"/>
-      <c r="H37" s="472"/>
-      <c r="I37" s="472"/>
-      <c r="J37" s="472"/>
-      <c r="K37" s="472"/>
-      <c r="L37" s="473" t="s">
+      <c r="D37" s="420"/>
+      <c r="E37" s="420"/>
+      <c r="F37" s="420"/>
+      <c r="G37" s="420"/>
+      <c r="H37" s="420"/>
+      <c r="I37" s="420"/>
+      <c r="J37" s="420"/>
+      <c r="K37" s="420"/>
+      <c r="L37" s="421" t="s">
         <v>47</v>
       </c>
-      <c r="M37" s="474"/>
-      <c r="N37" s="474"/>
-      <c r="O37" s="368"/>
-      <c r="R37" s="365"/>
-      <c r="T37" s="366"/>
-      <c r="U37" s="358"/>
-      <c r="V37" s="358"/>
-    </row>
-    <row r="38" spans="1:28" s="325" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B38" s="471"/>
-      <c r="C38" s="472"/>
-      <c r="D38" s="472"/>
-      <c r="E38" s="472"/>
-      <c r="F38" s="472"/>
-      <c r="G38" s="472"/>
-      <c r="H38" s="472"/>
-      <c r="I38" s="472"/>
-      <c r="J38" s="472"/>
-      <c r="K38" s="472"/>
-      <c r="L38" s="473"/>
-      <c r="M38" s="389" t="s">
+      <c r="M37" s="422"/>
+      <c r="N37" s="422"/>
+      <c r="O37" s="367"/>
+      <c r="R37" s="364"/>
+      <c r="T37" s="365"/>
+      <c r="U37" s="357"/>
+      <c r="V37" s="357"/>
+    </row>
+    <row r="38" spans="1:28" s="324" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B38" s="419"/>
+      <c r="C38" s="420"/>
+      <c r="D38" s="420"/>
+      <c r="E38" s="420"/>
+      <c r="F38" s="420"/>
+      <c r="G38" s="420"/>
+      <c r="H38" s="420"/>
+      <c r="I38" s="420"/>
+      <c r="J38" s="420"/>
+      <c r="K38" s="420"/>
+      <c r="L38" s="421"/>
+      <c r="M38" s="388" t="s">
         <v>225</v>
       </c>
-      <c r="N38" s="389"/>
-      <c r="O38" s="389"/>
-      <c r="R38" s="365"/>
-      <c r="T38" s="366"/>
-      <c r="U38" s="358"/>
-      <c r="V38" s="358"/>
-    </row>
-    <row r="39" spans="1:28" s="325" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B39" s="369" t="s">
+      <c r="N38" s="388"/>
+      <c r="O38" s="388"/>
+      <c r="R38" s="364"/>
+      <c r="T38" s="365"/>
+      <c r="U38" s="357"/>
+      <c r="V38" s="357"/>
+    </row>
+    <row r="39" spans="1:28" s="324" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B39" s="368" t="s">
         <v>226</v>
       </c>
-      <c r="R39" s="365"/>
-      <c r="T39" s="366"/>
-      <c r="U39" s="358"/>
-      <c r="V39" s="358"/>
-    </row>
-    <row r="40" spans="1:28" s="325" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B40" s="459" t="s">
+      <c r="R39" s="364"/>
+      <c r="T39" s="365"/>
+      <c r="U39" s="357"/>
+      <c r="V39" s="357"/>
+    </row>
+    <row r="40" spans="1:28" s="324" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B40" s="430" t="s">
         <v>41</v>
       </c>
-      <c r="C40" s="460"/>
-      <c r="D40" s="460"/>
-      <c r="E40" s="460"/>
-      <c r="F40" s="460"/>
-      <c r="G40" s="460"/>
-      <c r="H40" s="460"/>
-      <c r="I40" s="460"/>
-      <c r="J40" s="460"/>
-      <c r="K40" s="461"/>
-      <c r="L40" s="359" t="s">
+      <c r="C40" s="431"/>
+      <c r="D40" s="431"/>
+      <c r="E40" s="431"/>
+      <c r="F40" s="431"/>
+      <c r="G40" s="431"/>
+      <c r="H40" s="431"/>
+      <c r="I40" s="431"/>
+      <c r="J40" s="431"/>
+      <c r="K40" s="432"/>
+      <c r="L40" s="358" t="s">
         <v>223</v>
       </c>
-      <c r="M40" s="462" t="s">
+      <c r="M40" s="433" t="s">
         <v>18</v>
       </c>
-      <c r="N40" s="462"/>
-      <c r="O40" s="462"/>
-      <c r="Q40" s="340"/>
-      <c r="R40" s="360"/>
-      <c r="S40" s="358"/>
-      <c r="T40" s="358"/>
-      <c r="U40" s="358"/>
-      <c r="V40" s="358"/>
-    </row>
-    <row r="41" spans="1:28" s="325" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B41" s="361" t="s">
+      <c r="N40" s="433"/>
+      <c r="O40" s="433"/>
+      <c r="Q40" s="339"/>
+      <c r="R40" s="359"/>
+      <c r="S40" s="357"/>
+      <c r="T40" s="357"/>
+      <c r="U40" s="357"/>
+      <c r="V40" s="357"/>
+    </row>
+    <row r="41" spans="1:28" s="324" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B41" s="360" t="s">
         <v>45</v>
       </c>
-      <c r="C41" s="475" t="s">
+      <c r="C41" s="424" t="s">
         <v>46</v>
       </c>
-      <c r="D41" s="476"/>
-      <c r="E41" s="476"/>
-      <c r="F41" s="476"/>
-      <c r="G41" s="476"/>
-      <c r="H41" s="476"/>
-      <c r="I41" s="476"/>
-      <c r="J41" s="476"/>
-      <c r="K41" s="477"/>
+      <c r="D41" s="425"/>
+      <c r="E41" s="425"/>
+      <c r="F41" s="425"/>
+      <c r="G41" s="425"/>
+      <c r="H41" s="425"/>
+      <c r="I41" s="425"/>
+      <c r="J41" s="425"/>
+      <c r="K41" s="426"/>
       <c r="L41" s="61" t="s">
         <v>47</v>
       </c>
-      <c r="M41" s="474"/>
-      <c r="N41" s="474"/>
-      <c r="O41" s="474"/>
-      <c r="Q41" s="340"/>
-      <c r="R41" s="360"/>
-      <c r="S41" s="358"/>
-      <c r="T41" s="358"/>
-      <c r="U41" s="358"/>
-      <c r="V41" s="358"/>
-    </row>
-    <row r="42" spans="1:28" s="325" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B42" s="361" t="s">
+      <c r="M41" s="422"/>
+      <c r="N41" s="422"/>
+      <c r="O41" s="422"/>
+      <c r="Q41" s="339"/>
+      <c r="R41" s="359"/>
+      <c r="S41" s="357"/>
+      <c r="T41" s="357"/>
+      <c r="U41" s="357"/>
+      <c r="V41" s="357"/>
+    </row>
+    <row r="42" spans="1:28" s="324" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B42" s="360" t="s">
         <v>48</v>
       </c>
-      <c r="C42" s="475" t="s">
+      <c r="C42" s="424" t="s">
         <v>49</v>
       </c>
-      <c r="D42" s="476"/>
-      <c r="E42" s="476"/>
-      <c r="F42" s="476"/>
-      <c r="G42" s="476"/>
-      <c r="H42" s="476"/>
-      <c r="I42" s="476"/>
-      <c r="J42" s="476"/>
-      <c r="K42" s="477"/>
+      <c r="D42" s="425"/>
+      <c r="E42" s="425"/>
+      <c r="F42" s="425"/>
+      <c r="G42" s="425"/>
+      <c r="H42" s="425"/>
+      <c r="I42" s="425"/>
+      <c r="J42" s="425"/>
+      <c r="K42" s="426"/>
       <c r="L42" s="61" t="s">
         <v>47</v>
       </c>
-      <c r="M42" s="474"/>
-      <c r="N42" s="474"/>
-      <c r="O42" s="474"/>
-      <c r="Q42" s="340"/>
-      <c r="R42" s="360"/>
-      <c r="S42" s="358"/>
-      <c r="T42" s="358"/>
-      <c r="U42" s="358"/>
-      <c r="V42" s="358"/>
-    </row>
-    <row r="43" spans="1:28" s="325" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B43" s="361" t="s">
+      <c r="M42" s="422"/>
+      <c r="N42" s="422"/>
+      <c r="O42" s="422"/>
+      <c r="Q42" s="339"/>
+      <c r="R42" s="359"/>
+      <c r="S42" s="357"/>
+      <c r="T42" s="357"/>
+      <c r="U42" s="357"/>
+      <c r="V42" s="357"/>
+    </row>
+    <row r="43" spans="1:28" s="324" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B43" s="360" t="s">
         <v>50</v>
       </c>
-      <c r="C43" s="475" t="s">
+      <c r="C43" s="424" t="s">
         <v>224</v>
       </c>
-      <c r="D43" s="476"/>
-      <c r="E43" s="476"/>
-      <c r="F43" s="476"/>
-      <c r="G43" s="476"/>
-      <c r="H43" s="476"/>
-      <c r="I43" s="476"/>
-      <c r="J43" s="476"/>
-      <c r="K43" s="477"/>
-      <c r="L43" s="367" t="s">
+      <c r="D43" s="425"/>
+      <c r="E43" s="425"/>
+      <c r="F43" s="425"/>
+      <c r="G43" s="425"/>
+      <c r="H43" s="425"/>
+      <c r="I43" s="425"/>
+      <c r="J43" s="425"/>
+      <c r="K43" s="426"/>
+      <c r="L43" s="366" t="s">
         <v>47</v>
       </c>
-      <c r="M43" s="438"/>
-      <c r="N43" s="478"/>
-      <c r="O43" s="439"/>
-      <c r="Q43" s="340"/>
-      <c r="R43" s="360"/>
-      <c r="S43" s="358"/>
-      <c r="T43" s="358"/>
-      <c r="U43" s="358"/>
-      <c r="V43" s="358"/>
-    </row>
-    <row r="44" spans="1:28" s="325" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B44" s="471" t="s">
+      <c r="M43" s="427"/>
+      <c r="N43" s="428"/>
+      <c r="O43" s="429"/>
+      <c r="Q43" s="339"/>
+      <c r="R43" s="359"/>
+      <c r="S43" s="357"/>
+      <c r="T43" s="357"/>
+      <c r="U43" s="357"/>
+      <c r="V43" s="357"/>
+    </row>
+    <row r="44" spans="1:28" s="324" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B44" s="419" t="s">
         <v>52</v>
       </c>
-      <c r="C44" s="472" t="s">
+      <c r="C44" s="420" t="s">
         <v>53</v>
       </c>
-      <c r="D44" s="472"/>
-      <c r="E44" s="472"/>
-      <c r="F44" s="472"/>
-      <c r="G44" s="472"/>
-      <c r="H44" s="472"/>
-      <c r="I44" s="472"/>
-      <c r="J44" s="472"/>
-      <c r="K44" s="472"/>
-      <c r="L44" s="473" t="s">
+      <c r="D44" s="420"/>
+      <c r="E44" s="420"/>
+      <c r="F44" s="420"/>
+      <c r="G44" s="420"/>
+      <c r="H44" s="420"/>
+      <c r="I44" s="420"/>
+      <c r="J44" s="420"/>
+      <c r="K44" s="420"/>
+      <c r="L44" s="421" t="s">
         <v>47</v>
       </c>
-      <c r="M44" s="474"/>
-      <c r="N44" s="474"/>
-      <c r="O44" s="368"/>
-      <c r="R44" s="360"/>
-      <c r="S44" s="358"/>
-      <c r="T44" s="358"/>
-      <c r="U44" s="358"/>
-      <c r="V44" s="358"/>
-    </row>
-    <row r="45" spans="1:28" s="325" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B45" s="471"/>
-      <c r="C45" s="472"/>
-      <c r="D45" s="472"/>
-      <c r="E45" s="472"/>
-      <c r="F45" s="472"/>
-      <c r="G45" s="472"/>
-      <c r="H45" s="472"/>
-      <c r="I45" s="472"/>
-      <c r="J45" s="472"/>
-      <c r="K45" s="472"/>
-      <c r="L45" s="473"/>
-      <c r="M45" s="468" t="s">
+      <c r="M44" s="422"/>
+      <c r="N44" s="422"/>
+      <c r="O44" s="367"/>
+      <c r="R44" s="359"/>
+      <c r="S44" s="357"/>
+      <c r="T44" s="357"/>
+      <c r="U44" s="357"/>
+      <c r="V44" s="357"/>
+    </row>
+    <row r="45" spans="1:28" s="324" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B45" s="419"/>
+      <c r="C45" s="420"/>
+      <c r="D45" s="420"/>
+      <c r="E45" s="420"/>
+      <c r="F45" s="420"/>
+      <c r="G45" s="420"/>
+      <c r="H45" s="420"/>
+      <c r="I45" s="420"/>
+      <c r="J45" s="420"/>
+      <c r="K45" s="420"/>
+      <c r="L45" s="421"/>
+      <c r="M45" s="423" t="s">
         <v>225</v>
       </c>
-      <c r="N45" s="468"/>
-      <c r="O45" s="468"/>
-      <c r="Q45" s="340"/>
-      <c r="S45" s="485"/>
-      <c r="T45" s="485"/>
-      <c r="U45" s="485"/>
-      <c r="V45" s="485"/>
-      <c r="W45" s="485"/>
-      <c r="X45" s="371"/>
-      <c r="Y45" s="480"/>
-      <c r="Z45" s="480"/>
-      <c r="AA45" s="480"/>
-      <c r="AB45" s="480"/>
-    </row>
-    <row r="46" spans="1:28" s="325" customFormat="1" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K46" s="373"/>
-      <c r="L46" s="374"/>
-      <c r="M46" s="375"/>
-      <c r="N46" s="375"/>
-      <c r="O46" s="375"/>
-      <c r="Q46" s="340"/>
-      <c r="S46" s="370"/>
-      <c r="T46" s="370"/>
-      <c r="U46" s="370"/>
-      <c r="V46" s="370"/>
-      <c r="W46" s="370"/>
-      <c r="X46" s="371"/>
-      <c r="Y46" s="372"/>
-      <c r="Z46" s="372"/>
-      <c r="AA46" s="372"/>
-      <c r="AB46" s="372"/>
-    </row>
-    <row r="47" spans="1:28" s="325" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N45" s="423"/>
+      <c r="O45" s="423"/>
+      <c r="Q45" s="339"/>
+      <c r="S45" s="417"/>
+      <c r="T45" s="417"/>
+      <c r="U45" s="417"/>
+      <c r="V45" s="417"/>
+      <c r="W45" s="417"/>
+      <c r="X45" s="370"/>
+      <c r="Y45" s="412"/>
+      <c r="Z45" s="412"/>
+      <c r="AA45" s="412"/>
+      <c r="AB45" s="412"/>
+    </row>
+    <row r="46" spans="1:28" s="324" customFormat="1" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K46" s="372"/>
+      <c r="L46" s="373"/>
+      <c r="M46" s="374"/>
+      <c r="N46" s="374"/>
+      <c r="O46" s="374"/>
+      <c r="Q46" s="339"/>
+      <c r="S46" s="369"/>
+      <c r="T46" s="369"/>
+      <c r="U46" s="369"/>
+      <c r="V46" s="369"/>
+      <c r="W46" s="369"/>
+      <c r="X46" s="370"/>
+      <c r="Y46" s="371"/>
+      <c r="Z46" s="371"/>
+      <c r="AA46" s="371"/>
+      <c r="AB46" s="371"/>
+    </row>
+    <row r="47" spans="1:28" s="324" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="53"/>
-      <c r="B47" s="481" t="s">
+      <c r="B47" s="413" t="s">
         <v>227</v>
       </c>
-      <c r="C47" s="481"/>
-      <c r="D47" s="481"/>
-      <c r="E47" s="481"/>
-      <c r="F47" s="481"/>
-      <c r="G47" s="481"/>
-      <c r="H47" s="481"/>
-      <c r="I47" s="481"/>
-      <c r="J47" s="481"/>
-      <c r="K47" s="481"/>
-      <c r="L47" s="481"/>
-      <c r="M47" s="481"/>
-      <c r="N47" s="481"/>
-      <c r="O47" s="481"/>
-      <c r="Q47" s="340"/>
-      <c r="S47" s="482"/>
-      <c r="T47" s="483"/>
-      <c r="U47" s="483"/>
-      <c r="V47" s="483"/>
-      <c r="W47" s="374"/>
-      <c r="X47" s="371"/>
-      <c r="Y47" s="484"/>
-      <c r="Z47" s="484"/>
-      <c r="AA47" s="376"/>
-      <c r="AB47" s="376"/>
-    </row>
-    <row r="48" spans="1:28" s="325" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="377" t="s">
+      <c r="C47" s="413"/>
+      <c r="D47" s="413"/>
+      <c r="E47" s="413"/>
+      <c r="F47" s="413"/>
+      <c r="G47" s="413"/>
+      <c r="H47" s="413"/>
+      <c r="I47" s="413"/>
+      <c r="J47" s="413"/>
+      <c r="K47" s="413"/>
+      <c r="L47" s="413"/>
+      <c r="M47" s="413"/>
+      <c r="N47" s="413"/>
+      <c r="O47" s="413"/>
+      <c r="Q47" s="339"/>
+      <c r="S47" s="414"/>
+      <c r="T47" s="415"/>
+      <c r="U47" s="415"/>
+      <c r="V47" s="415"/>
+      <c r="W47" s="373"/>
+      <c r="X47" s="370"/>
+      <c r="Y47" s="416"/>
+      <c r="Z47" s="416"/>
+      <c r="AA47" s="375"/>
+      <c r="AB47" s="375"/>
+    </row>
+    <row r="48" spans="1:28" s="324" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="376" t="s">
         <v>33</v>
       </c>
-      <c r="B48" s="378"/>
-      <c r="C48" s="379"/>
-      <c r="D48" s="380"/>
-      <c r="E48" s="380"/>
-      <c r="F48" s="380"/>
-      <c r="G48" s="381"/>
-      <c r="H48" s="381"/>
-      <c r="I48" s="381"/>
-      <c r="J48" s="381"/>
-      <c r="K48" s="381"/>
-      <c r="L48" s="381"/>
-      <c r="M48" s="381"/>
-      <c r="N48" s="381"/>
-      <c r="O48" s="381"/>
-      <c r="P48" s="340"/>
-      <c r="Q48" s="340"/>
-    </row>
-    <row r="49" spans="1:17" s="325" customFormat="1" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B49" s="378"/>
-      <c r="C49" s="379"/>
-      <c r="D49" s="379"/>
-      <c r="E49" s="379"/>
-      <c r="F49" s="379"/>
-      <c r="P49" s="340"/>
-      <c r="Q49" s="340"/>
-    </row>
-    <row r="50" spans="1:17" s="325" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="382"/>
-      <c r="B50" s="378"/>
-      <c r="C50" s="379"/>
-      <c r="D50" s="379"/>
-      <c r="E50" s="379"/>
-      <c r="F50" s="379"/>
-      <c r="G50" s="383"/>
-      <c r="H50" s="383"/>
-      <c r="I50" s="383"/>
-      <c r="J50" s="383"/>
-      <c r="K50" s="383"/>
-      <c r="L50" s="383"/>
-      <c r="M50" s="384"/>
-      <c r="N50" s="384"/>
-      <c r="O50" s="385"/>
-      <c r="P50" s="340"/>
-      <c r="Q50" s="340"/>
-    </row>
-    <row r="51" spans="1:17" s="325" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="382"/>
-      <c r="G51" s="383"/>
-      <c r="H51" s="383"/>
-      <c r="I51" s="383"/>
-      <c r="J51" s="383"/>
-      <c r="K51" s="383"/>
-      <c r="L51" s="383"/>
-      <c r="M51" s="384"/>
-      <c r="N51" s="384"/>
-      <c r="O51" s="385"/>
-      <c r="P51" s="340"/>
-      <c r="Q51" s="340"/>
-    </row>
-    <row r="52" spans="1:17" s="325" customFormat="1" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="386" t="s">
+      <c r="B48" s="377"/>
+      <c r="C48" s="378"/>
+      <c r="D48" s="379"/>
+      <c r="E48" s="379"/>
+      <c r="F48" s="379"/>
+      <c r="G48" s="380"/>
+      <c r="H48" s="380"/>
+      <c r="I48" s="380"/>
+      <c r="J48" s="380"/>
+      <c r="K48" s="380"/>
+      <c r="L48" s="380"/>
+      <c r="M48" s="380"/>
+      <c r="N48" s="380"/>
+      <c r="O48" s="380"/>
+      <c r="P48" s="339"/>
+      <c r="Q48" s="339"/>
+    </row>
+    <row r="49" spans="1:17" s="324" customFormat="1" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B49" s="377"/>
+      <c r="C49" s="378"/>
+      <c r="D49" s="378"/>
+      <c r="E49" s="378"/>
+      <c r="F49" s="378"/>
+      <c r="P49" s="339"/>
+      <c r="Q49" s="339"/>
+    </row>
+    <row r="50" spans="1:17" s="324" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A50" s="381"/>
+      <c r="B50" s="377"/>
+      <c r="C50" s="378"/>
+      <c r="D50" s="378"/>
+      <c r="E50" s="378"/>
+      <c r="F50" s="378"/>
+      <c r="G50" s="382"/>
+      <c r="H50" s="382"/>
+      <c r="I50" s="382"/>
+      <c r="J50" s="382"/>
+      <c r="K50" s="382"/>
+      <c r="L50" s="382"/>
+      <c r="M50" s="383"/>
+      <c r="N50" s="383"/>
+      <c r="O50" s="384"/>
+      <c r="P50" s="339"/>
+      <c r="Q50" s="339"/>
+    </row>
+    <row r="51" spans="1:17" s="324" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A51" s="381"/>
+      <c r="G51" s="382"/>
+      <c r="H51" s="382"/>
+      <c r="I51" s="382"/>
+      <c r="J51" s="382"/>
+      <c r="K51" s="382"/>
+      <c r="L51" s="382"/>
+      <c r="M51" s="383"/>
+      <c r="N51" s="383"/>
+      <c r="O51" s="384"/>
+      <c r="P51" s="339"/>
+      <c r="Q51" s="339"/>
+    </row>
+    <row r="52" spans="1:17" s="324" customFormat="1" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A52" s="385" t="s">
         <v>34</v>
       </c>
-      <c r="B52" s="379"/>
-      <c r="C52" s="379"/>
-      <c r="D52" s="379"/>
-      <c r="E52" s="379"/>
-      <c r="F52" s="379"/>
-      <c r="G52" s="379"/>
-      <c r="H52" s="379"/>
-      <c r="I52" s="379"/>
-      <c r="J52" s="379"/>
-      <c r="K52" s="379"/>
-      <c r="L52" s="379"/>
-      <c r="M52" s="379"/>
-      <c r="N52" s="379"/>
-      <c r="O52" s="379"/>
-      <c r="P52" s="340"/>
-      <c r="Q52" s="340"/>
-    </row>
-    <row r="53" spans="1:17" s="325" customFormat="1" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="348" t="s">
+      <c r="B52" s="378"/>
+      <c r="C52" s="378"/>
+      <c r="D52" s="378"/>
+      <c r="E52" s="378"/>
+      <c r="F52" s="378"/>
+      <c r="G52" s="378"/>
+      <c r="H52" s="378"/>
+      <c r="I52" s="378"/>
+      <c r="J52" s="378"/>
+      <c r="K52" s="378"/>
+      <c r="L52" s="378"/>
+      <c r="M52" s="378"/>
+      <c r="N52" s="378"/>
+      <c r="O52" s="378"/>
+      <c r="P52" s="339"/>
+      <c r="Q52" s="339"/>
+    </row>
+    <row r="53" spans="1:17" s="324" customFormat="1" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A53" s="347" t="s">
         <v>228</v>
       </c>
-      <c r="B53" s="379"/>
-      <c r="C53" s="379"/>
-      <c r="D53" s="379"/>
-      <c r="F53" s="379"/>
-      <c r="G53" s="379"/>
-      <c r="H53" s="387" t="s">
+      <c r="B53" s="378"/>
+      <c r="C53" s="378"/>
+      <c r="D53" s="378"/>
+      <c r="F53" s="378"/>
+      <c r="G53" s="378"/>
+      <c r="H53" s="386" t="s">
         <v>229</v>
       </c>
-      <c r="J53" s="379"/>
-      <c r="K53" s="379"/>
-      <c r="L53" s="379"/>
-      <c r="M53" s="379"/>
-      <c r="N53" s="379"/>
-      <c r="O53" s="379"/>
-      <c r="P53" s="340"/>
-      <c r="Q53" s="340"/>
-    </row>
-    <row r="54" spans="1:17" s="325" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="55" spans="1:17" s="325" customFormat="1" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="479" t="s">
+      <c r="J53" s="378"/>
+      <c r="K53" s="378"/>
+      <c r="L53" s="378"/>
+      <c r="M53" s="378"/>
+      <c r="N53" s="378"/>
+      <c r="O53" s="378"/>
+      <c r="P53" s="339"/>
+      <c r="Q53" s="339"/>
+    </row>
+    <row r="54" spans="1:17" s="324" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="55" spans="1:17" s="324" customFormat="1" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A55" s="418" t="s">
         <v>230</v>
       </c>
-      <c r="B55" s="479"/>
-      <c r="C55" s="479"/>
-      <c r="D55" s="479"/>
-      <c r="E55" s="479"/>
-      <c r="F55" s="479"/>
-      <c r="G55" s="479"/>
-      <c r="H55" s="479"/>
-      <c r="I55" s="479"/>
-      <c r="J55" s="479"/>
-      <c r="K55" s="479"/>
-      <c r="L55" s="479"/>
-      <c r="M55" s="479"/>
-      <c r="N55" s="479"/>
-      <c r="O55" s="479"/>
+      <c r="B55" s="418"/>
+      <c r="C55" s="418"/>
+      <c r="D55" s="418"/>
+      <c r="E55" s="418"/>
+      <c r="F55" s="418"/>
+      <c r="G55" s="418"/>
+      <c r="H55" s="418"/>
+      <c r="I55" s="418"/>
+      <c r="J55" s="418"/>
+      <c r="K55" s="418"/>
+      <c r="L55" s="418"/>
+      <c r="M55" s="418"/>
+      <c r="N55" s="418"/>
+      <c r="O55" s="418"/>
     </row>
   </sheetData>
   <protectedRanges>
@@ -9813,43 +9871,27 @@
     <protectedRange sqref="C10:C11 D11" name="Rango3_3_1_1_1_1_1_2_1"/>
   </protectedRanges>
   <mergeCells count="74">
-    <mergeCell ref="Y45:Z45"/>
-    <mergeCell ref="AA45:AB45"/>
-    <mergeCell ref="B47:O47"/>
-    <mergeCell ref="S47:V47"/>
-    <mergeCell ref="Y47:Z47"/>
-    <mergeCell ref="S45:W45"/>
-    <mergeCell ref="A55:O55"/>
-    <mergeCell ref="B44:B45"/>
-    <mergeCell ref="C44:K45"/>
-    <mergeCell ref="L44:L45"/>
-    <mergeCell ref="M44:N44"/>
-    <mergeCell ref="M45:O45"/>
-    <mergeCell ref="C41:K41"/>
-    <mergeCell ref="M41:O41"/>
-    <mergeCell ref="C42:K42"/>
-    <mergeCell ref="M42:O42"/>
-    <mergeCell ref="C43:K43"/>
-    <mergeCell ref="M43:O43"/>
-    <mergeCell ref="B37:B38"/>
-    <mergeCell ref="C37:K38"/>
-    <mergeCell ref="L37:L38"/>
-    <mergeCell ref="M37:N37"/>
-    <mergeCell ref="B40:K40"/>
-    <mergeCell ref="M40:O40"/>
-    <mergeCell ref="H23:J23"/>
-    <mergeCell ref="K23:L23"/>
-    <mergeCell ref="N24:O24"/>
-    <mergeCell ref="B31:O31"/>
-    <mergeCell ref="B33:K33"/>
-    <mergeCell ref="M33:O33"/>
-    <mergeCell ref="B27:G27"/>
-    <mergeCell ref="H27:I27"/>
-    <mergeCell ref="K27:N27"/>
-    <mergeCell ref="H28:I28"/>
-    <mergeCell ref="K28:N28"/>
-    <mergeCell ref="H29:I29"/>
-    <mergeCell ref="K29:N29"/>
+    <mergeCell ref="A14:O14"/>
+    <mergeCell ref="B16:F16"/>
+    <mergeCell ref="H16:J16"/>
+    <mergeCell ref="B11:D11"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="I11:K11"/>
+    <mergeCell ref="M11:O11"/>
+    <mergeCell ref="A13:O13"/>
+    <mergeCell ref="K16:L16"/>
+    <mergeCell ref="A7:O7"/>
+    <mergeCell ref="A8:O8"/>
+    <mergeCell ref="F10:G10"/>
+    <mergeCell ref="I10:K10"/>
+    <mergeCell ref="M10:O10"/>
+    <mergeCell ref="B18:D18"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="H18:J18"/>
+    <mergeCell ref="K18:L18"/>
+    <mergeCell ref="B17:D17"/>
+    <mergeCell ref="H17:J17"/>
+    <mergeCell ref="K17:L17"/>
     <mergeCell ref="B19:D19"/>
     <mergeCell ref="E19:F19"/>
     <mergeCell ref="H19:J19"/>
@@ -9866,27 +9908,43 @@
     <mergeCell ref="K22:L22"/>
     <mergeCell ref="B23:D23"/>
     <mergeCell ref="E23:F23"/>
-    <mergeCell ref="B18:D18"/>
-    <mergeCell ref="E18:F18"/>
-    <mergeCell ref="H18:J18"/>
-    <mergeCell ref="K18:L18"/>
-    <mergeCell ref="B17:D17"/>
-    <mergeCell ref="H17:J17"/>
-    <mergeCell ref="K17:L17"/>
-    <mergeCell ref="A7:O7"/>
-    <mergeCell ref="A8:O8"/>
-    <mergeCell ref="F10:G10"/>
-    <mergeCell ref="I10:K10"/>
-    <mergeCell ref="M10:O10"/>
-    <mergeCell ref="A14:O14"/>
-    <mergeCell ref="B16:F16"/>
-    <mergeCell ref="H16:J16"/>
-    <mergeCell ref="B11:D11"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="I11:K11"/>
-    <mergeCell ref="M11:O11"/>
-    <mergeCell ref="A13:O13"/>
-    <mergeCell ref="K16:L16"/>
+    <mergeCell ref="H23:J23"/>
+    <mergeCell ref="K23:L23"/>
+    <mergeCell ref="N24:O24"/>
+    <mergeCell ref="B31:O31"/>
+    <mergeCell ref="B33:K33"/>
+    <mergeCell ref="M33:O33"/>
+    <mergeCell ref="B27:G27"/>
+    <mergeCell ref="H27:I27"/>
+    <mergeCell ref="K27:N27"/>
+    <mergeCell ref="H28:I28"/>
+    <mergeCell ref="K28:N28"/>
+    <mergeCell ref="H29:I29"/>
+    <mergeCell ref="K29:N29"/>
+    <mergeCell ref="B37:B38"/>
+    <mergeCell ref="C37:K38"/>
+    <mergeCell ref="L37:L38"/>
+    <mergeCell ref="M37:N37"/>
+    <mergeCell ref="B40:K40"/>
+    <mergeCell ref="M40:O40"/>
+    <mergeCell ref="C41:K41"/>
+    <mergeCell ref="M41:O41"/>
+    <mergeCell ref="C42:K42"/>
+    <mergeCell ref="M42:O42"/>
+    <mergeCell ref="C43:K43"/>
+    <mergeCell ref="M43:O43"/>
+    <mergeCell ref="A55:O55"/>
+    <mergeCell ref="B44:B45"/>
+    <mergeCell ref="C44:K45"/>
+    <mergeCell ref="L44:L45"/>
+    <mergeCell ref="M44:N44"/>
+    <mergeCell ref="M45:O45"/>
+    <mergeCell ref="Y45:Z45"/>
+    <mergeCell ref="AA45:AB45"/>
+    <mergeCell ref="B47:O47"/>
+    <mergeCell ref="S47:V47"/>
+    <mergeCell ref="Y47:Z47"/>
+    <mergeCell ref="S45:W45"/>
   </mergeCells>
   <conditionalFormatting sqref="B36">
     <cfRule type="cellIs" priority="2" stopIfTrue="1" operator="between">
@@ -9926,36 +9984,36 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="490" t="s">
+      <c r="A2" s="494" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="490"/>
-      <c r="C2" s="490"/>
-      <c r="D2" s="490"/>
-      <c r="E2" s="490"/>
-      <c r="F2" s="490"/>
-      <c r="G2" s="490"/>
-      <c r="H2" s="490"/>
-      <c r="I2" s="490"/>
-      <c r="J2" s="490"/>
-      <c r="K2" s="490"/>
-      <c r="L2" s="490"/>
+      <c r="B2" s="494"/>
+      <c r="C2" s="494"/>
+      <c r="D2" s="494"/>
+      <c r="E2" s="494"/>
+      <c r="F2" s="494"/>
+      <c r="G2" s="494"/>
+      <c r="H2" s="494"/>
+      <c r="I2" s="494"/>
+      <c r="J2" s="494"/>
+      <c r="K2" s="494"/>
+      <c r="L2" s="494"/>
     </row>
     <row r="3" spans="1:12" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="497">
+      <c r="A3" s="501">
         <v>0</v>
       </c>
-      <c r="B3" s="497"/>
-      <c r="C3" s="497"/>
-      <c r="D3" s="497"/>
-      <c r="E3" s="497"/>
-      <c r="F3" s="497"/>
-      <c r="G3" s="497"/>
-      <c r="H3" s="497"/>
-      <c r="I3" s="497"/>
-      <c r="J3" s="497"/>
-      <c r="K3" s="497"/>
-      <c r="L3" s="497"/>
+      <c r="B3" s="501"/>
+      <c r="C3" s="501"/>
+      <c r="D3" s="501"/>
+      <c r="E3" s="501"/>
+      <c r="F3" s="501"/>
+      <c r="G3" s="501"/>
+      <c r="H3" s="501"/>
+      <c r="I3" s="501"/>
+      <c r="J3" s="501"/>
+      <c r="K3" s="501"/>
+      <c r="L3" s="501"/>
     </row>
     <row r="4" spans="1:12" ht="15.9" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="5" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -9965,16 +10023,16 @@
       <c r="B5" s="23" t="s">
         <v>2</v>
       </c>
-      <c r="C5" s="500">
+      <c r="C5" s="504">
         <f>+'FORMATO PEG'!U2</f>
         <v>0</v>
       </c>
-      <c r="D5" s="500"/>
-      <c r="E5" s="500"/>
-      <c r="F5" s="500"/>
-      <c r="G5" s="500"/>
-      <c r="H5" s="500"/>
-      <c r="I5" s="500"/>
+      <c r="D5" s="504"/>
+      <c r="E5" s="504"/>
+      <c r="F5" s="504"/>
+      <c r="G5" s="504"/>
+      <c r="H5" s="504"/>
+      <c r="I5" s="504"/>
       <c r="J5" s="25" t="s">
         <v>3</v>
       </c>
@@ -9992,23 +10050,23 @@
       <c r="B6" s="23" t="s">
         <v>2</v>
       </c>
-      <c r="C6" s="500">
+      <c r="C6" s="504">
         <f>+'FORMATO PEG'!U3</f>
         <v>0</v>
       </c>
-      <c r="D6" s="500"/>
-      <c r="E6" s="500"/>
-      <c r="F6" s="500"/>
-      <c r="G6" s="500"/>
-      <c r="H6" s="500"/>
-      <c r="I6" s="500"/>
+      <c r="D6" s="504"/>
+      <c r="E6" s="504"/>
+      <c r="F6" s="504"/>
+      <c r="G6" s="504"/>
+      <c r="H6" s="504"/>
+      <c r="I6" s="504"/>
       <c r="J6" s="25" t="s">
         <v>155</v>
       </c>
       <c r="K6" s="23" t="s">
         <v>2</v>
       </c>
-      <c r="L6" s="319">
+      <c r="L6" s="318">
         <f>+'FORMATO PEG'!U7</f>
         <v>0</v>
       </c>
@@ -10020,23 +10078,23 @@
       <c r="B7" s="23" t="s">
         <v>2</v>
       </c>
-      <c r="C7" s="500">
+      <c r="C7" s="504">
         <f>+'FORMATO PEG'!U4</f>
         <v>0</v>
       </c>
-      <c r="D7" s="500"/>
-      <c r="E7" s="500"/>
-      <c r="F7" s="500"/>
-      <c r="G7" s="500"/>
-      <c r="H7" s="500"/>
-      <c r="I7" s="500"/>
+      <c r="D7" s="504"/>
+      <c r="E7" s="504"/>
+      <c r="F7" s="504"/>
+      <c r="G7" s="504"/>
+      <c r="H7" s="504"/>
+      <c r="I7" s="504"/>
       <c r="J7" s="25" t="s">
         <v>156</v>
       </c>
       <c r="K7" s="23" t="s">
         <v>2</v>
       </c>
-      <c r="L7" s="319">
+      <c r="L7" s="318">
         <f>+'FORMATO PEG'!U9</f>
         <v>0</v>
       </c>
@@ -10048,23 +10106,23 @@
       <c r="B8" s="23" t="s">
         <v>2</v>
       </c>
-      <c r="C8" s="500">
+      <c r="C8" s="504">
         <f>+'FORMATO PEG'!U5</f>
         <v>0</v>
       </c>
-      <c r="D8" s="500"/>
-      <c r="E8" s="500"/>
-      <c r="F8" s="500"/>
-      <c r="G8" s="500"/>
-      <c r="H8" s="500"/>
-      <c r="I8" s="500"/>
+      <c r="D8" s="504"/>
+      <c r="E8" s="504"/>
+      <c r="F8" s="504"/>
+      <c r="G8" s="504"/>
+      <c r="H8" s="504"/>
+      <c r="I8" s="504"/>
       <c r="J8" s="25" t="s">
         <v>6</v>
       </c>
       <c r="K8" s="23" t="s">
         <v>2</v>
       </c>
-      <c r="L8" s="308">
+      <c r="L8" s="307">
         <f>+'FORMATO PEG'!U8</f>
         <v>0</v>
       </c>
@@ -10100,36 +10158,36 @@
       <c r="L10" s="18"/>
     </row>
     <row r="11" spans="1:12" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="491" t="s">
+      <c r="A11" s="495" t="s">
         <v>177</v>
       </c>
-      <c r="B11" s="492"/>
-      <c r="C11" s="492"/>
-      <c r="D11" s="492"/>
-      <c r="E11" s="492"/>
-      <c r="F11" s="492"/>
-      <c r="G11" s="492"/>
-      <c r="H11" s="492"/>
-      <c r="I11" s="492"/>
-      <c r="J11" s="492"/>
-      <c r="K11" s="492"/>
-      <c r="L11" s="493"/>
+      <c r="B11" s="496"/>
+      <c r="C11" s="496"/>
+      <c r="D11" s="496"/>
+      <c r="E11" s="496"/>
+      <c r="F11" s="496"/>
+      <c r="G11" s="496"/>
+      <c r="H11" s="496"/>
+      <c r="I11" s="496"/>
+      <c r="J11" s="496"/>
+      <c r="K11" s="496"/>
+      <c r="L11" s="497"/>
     </row>
     <row r="12" spans="1:12" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="494" t="s">
+      <c r="A12" s="498" t="s">
         <v>188</v>
       </c>
-      <c r="B12" s="495"/>
-      <c r="C12" s="495"/>
-      <c r="D12" s="495"/>
-      <c r="E12" s="495"/>
-      <c r="F12" s="495"/>
-      <c r="G12" s="495"/>
-      <c r="H12" s="495"/>
-      <c r="I12" s="495"/>
-      <c r="J12" s="495"/>
-      <c r="K12" s="495"/>
-      <c r="L12" s="496"/>
+      <c r="B12" s="499"/>
+      <c r="C12" s="499"/>
+      <c r="D12" s="499"/>
+      <c r="E12" s="499"/>
+      <c r="F12" s="499"/>
+      <c r="G12" s="499"/>
+      <c r="H12" s="499"/>
+      <c r="I12" s="499"/>
+      <c r="J12" s="499"/>
+      <c r="K12" s="499"/>
+      <c r="L12" s="500"/>
     </row>
     <row r="13" spans="1:12" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="28"/>
@@ -10149,16 +10207,16 @@
       <c r="A14" s="34" t="s">
         <v>9</v>
       </c>
-      <c r="B14" s="157"/>
-      <c r="C14" s="157"/>
-      <c r="D14" s="157"/>
-      <c r="E14" s="158"/>
-      <c r="F14" s="158"/>
-      <c r="G14" s="158"/>
-      <c r="H14" s="158"/>
-      <c r="I14" s="158"/>
-      <c r="J14" s="159"/>
-      <c r="K14" s="160"/>
+      <c r="B14" s="156"/>
+      <c r="C14" s="156"/>
+      <c r="D14" s="156"/>
+      <c r="E14" s="157"/>
+      <c r="F14" s="157"/>
+      <c r="G14" s="157"/>
+      <c r="H14" s="157"/>
+      <c r="I14" s="157"/>
+      <c r="J14" s="158"/>
+      <c r="K14" s="159"/>
       <c r="L14" s="35"/>
     </row>
     <row r="15" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -10167,24 +10225,24 @@
       </c>
       <c r="B15" s="53"/>
       <c r="C15" s="53"/>
-      <c r="D15" s="155" t="s">
+      <c r="D15" s="154" t="s">
         <v>2</v>
       </c>
       <c r="E15" s="53">
         <f>+'FORMATO PEG'!U15</f>
         <v>0</v>
       </c>
-      <c r="F15" s="156"/>
-      <c r="G15" s="161"/>
+      <c r="F15" s="155"/>
+      <c r="G15" s="160"/>
       <c r="H15" s="4"/>
-      <c r="I15" s="160"/>
-      <c r="J15" s="159" t="s">
+      <c r="I15" s="159"/>
+      <c r="J15" s="158" t="s">
         <v>11</v>
       </c>
-      <c r="K15" s="160" t="s">
+      <c r="K15" s="159" t="s">
         <v>2</v>
       </c>
-      <c r="L15" s="320">
+      <c r="L15" s="319">
         <f>+'FORMATO PEG'!U11</f>
         <v>0</v>
       </c>
@@ -10195,24 +10253,24 @@
       </c>
       <c r="B16" s="53"/>
       <c r="C16" s="53"/>
-      <c r="D16" s="155" t="s">
+      <c r="D16" s="154" t="s">
         <v>2</v>
       </c>
       <c r="E16" s="53">
         <f>+'FORMATO PEG'!U16</f>
         <v>0</v>
       </c>
-      <c r="F16" s="156"/>
-      <c r="G16" s="161"/>
+      <c r="F16" s="155"/>
+      <c r="G16" s="160"/>
       <c r="H16" s="4"/>
-      <c r="I16" s="160"/>
-      <c r="J16" s="159" t="s">
+      <c r="I16" s="159"/>
+      <c r="J16" s="158" t="s">
         <v>13</v>
       </c>
-      <c r="K16" s="160" t="s">
+      <c r="K16" s="159" t="s">
         <v>2</v>
       </c>
-      <c r="L16" s="309">
+      <c r="L16" s="308">
         <f>+'FORMATO PEG'!U12</f>
         <v>0</v>
       </c>
@@ -10223,24 +10281,24 @@
       </c>
       <c r="B17" s="53"/>
       <c r="C17" s="53"/>
-      <c r="D17" s="155" t="s">
+      <c r="D17" s="154" t="s">
         <v>2</v>
       </c>
-      <c r="E17" s="312">
+      <c r="E17" s="311">
         <f>+'FORMATO PEG'!U17</f>
         <v>0</v>
       </c>
-      <c r="F17" s="156"/>
-      <c r="G17" s="161"/>
+      <c r="F17" s="155"/>
+      <c r="G17" s="160"/>
       <c r="H17" s="4"/>
-      <c r="I17" s="160"/>
-      <c r="J17" s="159" t="s">
+      <c r="I17" s="159"/>
+      <c r="J17" s="158" t="s">
         <v>14</v>
       </c>
-      <c r="K17" s="160" t="s">
+      <c r="K17" s="159" t="s">
         <v>2</v>
       </c>
-      <c r="L17" s="309">
+      <c r="L17" s="308">
         <f>+'FORMATO PEG'!U13</f>
         <v>0</v>
       </c>
@@ -10255,7 +10313,7 @@
       </c>
       <c r="B18" s="53"/>
       <c r="C18" s="53"/>
-      <c r="D18" s="155" t="s">
+      <c r="D18" s="154" t="s">
         <v>2</v>
       </c>
       <c r="E18" s="4" t="s">
@@ -10263,7 +10321,7 @@
       </c>
       <c r="I18" s="22"/>
       <c r="J18" s="22"/>
-      <c r="K18" s="156"/>
+      <c r="K18" s="155"/>
       <c r="L18" s="14"/>
     </row>
     <row r="19" spans="1:13" ht="9" customHeight="1" x14ac:dyDescent="0.25">
@@ -10277,18 +10335,18 @@
       <c r="H19" s="19"/>
       <c r="I19" s="39"/>
       <c r="J19" s="39"/>
-      <c r="K19" s="134"/>
-      <c r="L19" s="162"/>
+      <c r="K19" s="133"/>
+      <c r="L19" s="161"/>
     </row>
     <row r="20" spans="1:13" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="41"/>
       <c r="B20" s="42"/>
       <c r="C20" s="42"/>
       <c r="D20" s="68"/>
-      <c r="E20" s="489"/>
-      <c r="F20" s="489"/>
-      <c r="G20" s="489"/>
-      <c r="H20" s="489"/>
+      <c r="E20" s="493"/>
+      <c r="F20" s="493"/>
+      <c r="G20" s="493"/>
+      <c r="H20" s="493"/>
       <c r="I20" s="22"/>
       <c r="J20" s="42"/>
       <c r="K20" s="42"/>
@@ -10296,15 +10354,15 @@
     </row>
     <row r="21" spans="1:13" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="41"/>
-      <c r="B21" s="498" t="s">
+      <c r="B21" s="502" t="s">
         <v>16</v>
       </c>
-      <c r="C21" s="499"/>
-      <c r="D21" s="499"/>
-      <c r="E21" s="499"/>
-      <c r="F21" s="499"/>
-      <c r="G21" s="499"/>
-      <c r="H21" s="499"/>
+      <c r="C21" s="503"/>
+      <c r="D21" s="503"/>
+      <c r="E21" s="503"/>
+      <c r="F21" s="503"/>
+      <c r="G21" s="503"/>
+      <c r="H21" s="503"/>
       <c r="I21" s="111" t="s">
         <v>17</v>
       </c>
@@ -10316,7 +10374,7 @@
     </row>
     <row r="22" spans="1:13" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="41"/>
-      <c r="B22" s="303" t="s">
+      <c r="B22" s="302" t="s">
         <v>19</v>
       </c>
       <c r="C22" s="40"/>
@@ -10324,11 +10382,11 @@
       <c r="E22" s="120"/>
       <c r="F22" s="121"/>
       <c r="G22" s="121"/>
-      <c r="H22" s="136"/>
-      <c r="I22" s="137" t="s">
+      <c r="H22" s="135"/>
+      <c r="I22" s="136" t="s">
         <v>20</v>
       </c>
-      <c r="J22" s="138" t="b">
+      <c r="J22" s="137" t="b">
         <f>DATOS!I25</f>
         <v>0</v>
       </c>
@@ -10337,7 +10395,7 @@
     </row>
     <row r="23" spans="1:13" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="41"/>
-      <c r="B23" s="237" t="s">
+      <c r="B23" s="236" t="s">
         <v>21</v>
       </c>
       <c r="C23" s="66"/>
@@ -10345,11 +10403,11 @@
       <c r="E23" s="67"/>
       <c r="F23" s="131"/>
       <c r="G23" s="131"/>
-      <c r="H23" s="139"/>
-      <c r="I23" s="137" t="s">
+      <c r="H23" s="138"/>
+      <c r="I23" s="136" t="s">
         <v>20</v>
       </c>
-      <c r="J23" s="138" t="b">
+      <c r="J23" s="137" t="b">
         <f>DATOS!I26</f>
         <v>0</v>
       </c>
@@ -10358,7 +10416,7 @@
     </row>
     <row r="24" spans="1:13" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="41"/>
-      <c r="B24" s="237" t="s">
+      <c r="B24" s="236" t="s">
         <v>22</v>
       </c>
       <c r="C24" s="66"/>
@@ -10366,11 +10424,11 @@
       <c r="E24" s="67"/>
       <c r="F24" s="70"/>
       <c r="G24" s="69"/>
-      <c r="H24" s="139"/>
-      <c r="I24" s="140" t="s">
+      <c r="H24" s="138"/>
+      <c r="I24" s="139" t="s">
         <v>20</v>
       </c>
-      <c r="J24" s="138" t="b">
+      <c r="J24" s="137" t="b">
         <f>DATOS!I27</f>
         <v>0</v>
       </c>
@@ -10379,7 +10437,7 @@
     </row>
     <row r="25" spans="1:13" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="41"/>
-      <c r="B25" s="304" t="s">
+      <c r="B25" s="303" t="s">
         <v>23</v>
       </c>
       <c r="C25" s="122"/>
@@ -10387,11 +10445,11 @@
       <c r="E25" s="19"/>
       <c r="F25" s="124"/>
       <c r="G25" s="123"/>
-      <c r="H25" s="141"/>
-      <c r="I25" s="140" t="s">
+      <c r="H25" s="140"/>
+      <c r="I25" s="139" t="s">
         <v>24</v>
       </c>
-      <c r="J25" s="154" t="b">
+      <c r="J25" s="153" t="b">
         <f>DATOS!I28</f>
         <v>0</v>
       </c>
@@ -10471,7 +10529,7 @@
         <f t="array" ref="J30:K30">+'FORMATO PEG'!H27:I27</f>
         <v>0</v>
       </c>
-      <c r="K30" s="562">
+      <c r="K30" s="411">
         <v>0</v>
       </c>
       <c r="L30" s="49"/>
@@ -10487,7 +10545,7 @@
       <c r="F31" s="21"/>
       <c r="G31" s="21"/>
       <c r="H31" s="21"/>
-      <c r="J31" s="182" t="str">
+      <c r="J31" s="181" t="str">
         <f>+DATOS!E7</f>
         <v>-</v>
       </c>
@@ -10509,7 +10567,7 @@
         <f t="array" ref="J32:K32">+'FORMATO PEG'!H28:I28</f>
         <v>0</v>
       </c>
-      <c r="K32" s="562">
+      <c r="K32" s="411">
         <v>0</v>
       </c>
       <c r="L32" s="49"/>
@@ -10523,7 +10581,7 @@
       <c r="F33" s="21"/>
       <c r="G33" s="21"/>
       <c r="H33" s="21"/>
-      <c r="J33" s="163"/>
+      <c r="J33" s="162"/>
       <c r="K33" s="49"/>
       <c r="L33" s="49"/>
     </row>
@@ -10574,20 +10632,20 @@
       <c r="L36" s="27"/>
     </row>
     <row r="37" spans="1:14" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="487" t="s">
+      <c r="A37" s="491" t="s">
         <v>172</v>
       </c>
-      <c r="B37" s="488"/>
-      <c r="C37" s="488"/>
-      <c r="D37" s="488"/>
-      <c r="E37" s="488"/>
-      <c r="F37" s="488"/>
-      <c r="G37" s="488"/>
-      <c r="H37" s="488"/>
-      <c r="I37" s="488"/>
-      <c r="J37" s="488"/>
-      <c r="K37" s="488"/>
-      <c r="L37" s="488"/>
+      <c r="B37" s="492"/>
+      <c r="C37" s="492"/>
+      <c r="D37" s="492"/>
+      <c r="E37" s="492"/>
+      <c r="F37" s="492"/>
+      <c r="G37" s="492"/>
+      <c r="H37" s="492"/>
+      <c r="I37" s="492"/>
+      <c r="J37" s="492"/>
+      <c r="K37" s="492"/>
+      <c r="L37" s="492"/>
     </row>
     <row r="38" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="59" t="s">
@@ -10606,22 +10664,22 @@
       <c r="L38" s="27"/>
     </row>
     <row r="39" spans="1:14" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="486" t="s">
+      <c r="A39" s="490" t="s">
         <v>185</v>
       </c>
-      <c r="B39" s="486"/>
-      <c r="C39" s="486"/>
-      <c r="D39" s="486"/>
-      <c r="E39" s="486"/>
-      <c r="F39" s="486"/>
-      <c r="G39" s="486"/>
-      <c r="H39" s="486"/>
-      <c r="I39" s="486"/>
-      <c r="J39" s="486"/>
-      <c r="K39" s="486"/>
-      <c r="L39" s="486"/>
-      <c r="M39" s="316"/>
-      <c r="N39" s="316"/>
+      <c r="B39" s="490"/>
+      <c r="C39" s="490"/>
+      <c r="D39" s="490"/>
+      <c r="E39" s="490"/>
+      <c r="F39" s="490"/>
+      <c r="G39" s="490"/>
+      <c r="H39" s="490"/>
+      <c r="I39" s="490"/>
+      <c r="J39" s="490"/>
+      <c r="K39" s="490"/>
+      <c r="L39" s="490"/>
+      <c r="M39" s="315"/>
+      <c r="N39" s="315"/>
     </row>
     <row r="40" spans="1:14" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="59"/>
@@ -10792,30 +10850,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="513" t="s">
+      <c r="A1" s="505" t="s">
         <v>189</v>
       </c>
-      <c r="B1" s="514"/>
-      <c r="C1" s="514"/>
-      <c r="D1" s="514"/>
-      <c r="E1" s="514"/>
-      <c r="F1" s="514"/>
-      <c r="G1" s="514"/>
-      <c r="H1" s="514"/>
-      <c r="I1" s="514"/>
-      <c r="J1" s="514"/>
-      <c r="K1" s="514"/>
-      <c r="L1" s="514"/>
-      <c r="M1" s="514"/>
-      <c r="N1" s="515"/>
+      <c r="B1" s="506"/>
+      <c r="C1" s="506"/>
+      <c r="D1" s="506"/>
+      <c r="E1" s="506"/>
+      <c r="F1" s="506"/>
+      <c r="G1" s="506"/>
+      <c r="H1" s="506"/>
+      <c r="I1" s="506"/>
+      <c r="J1" s="506"/>
+      <c r="K1" s="506"/>
+      <c r="L1" s="506"/>
+      <c r="M1" s="506"/>
+      <c r="N1" s="507"/>
       <c r="O1" s="64"/>
     </row>
     <row r="2" spans="1:20" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="168" t="s">
+      <c r="A2" s="167" t="s">
         <v>36</v>
       </c>
-      <c r="B2" s="169"/>
-      <c r="C2" s="169"/>
+      <c r="B2" s="168"/>
+      <c r="C2" s="168"/>
       <c r="D2" s="71"/>
       <c r="E2" s="71"/>
       <c r="F2" s="71"/>
@@ -10829,14 +10887,14 @@
       <c r="N2" s="72"/>
     </row>
     <row r="3" spans="1:20" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="170" t="s">
+      <c r="A3" s="169" t="s">
         <v>37</v>
       </c>
-      <c r="B3" s="298"/>
-      <c r="C3" s="298"/>
+      <c r="B3" s="297"/>
+      <c r="C3" s="297"/>
       <c r="D3" s="65"/>
       <c r="E3" s="65"/>
-      <c r="F3" s="174"/>
+      <c r="F3" s="173"/>
       <c r="G3" s="65"/>
       <c r="K3" s="65"/>
       <c r="L3" s="65"/>
@@ -10844,23 +10902,23 @@
       <c r="N3" s="73"/>
     </row>
     <row r="4" spans="1:20" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="170" t="s">
+      <c r="A4" s="169" t="s">
         <v>38</v>
       </c>
-      <c r="B4" s="298"/>
+      <c r="B4" s="297"/>
       <c r="C4" s="68">
         <f>+Balanza!C7</f>
         <v>-4.6299999999999997E-6</v>
       </c>
       <c r="D4" s="65"/>
       <c r="E4" s="65"/>
-      <c r="F4" s="174"/>
+      <c r="F4" s="173"/>
       <c r="G4" s="65"/>
-      <c r="H4" s="301" t="s">
+      <c r="H4" s="300" t="s">
         <v>40</v>
       </c>
-      <c r="I4" s="298"/>
-      <c r="J4" s="302">
+      <c r="I4" s="297"/>
+      <c r="J4" s="301">
         <f>+Balanza!D12</f>
         <v>46132</v>
       </c>
@@ -10870,7 +10928,7 @@
       <c r="N4" s="73"/>
     </row>
     <row r="5" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="171" t="s">
+      <c r="A5" s="170" t="s">
         <v>39</v>
       </c>
       <c r="B5" s="123"/>
@@ -10878,9 +10936,9 @@
         <f>+Balanza!C11</f>
         <v>EQP-0050</v>
       </c>
-      <c r="D5" s="299"/>
-      <c r="E5" s="299"/>
-      <c r="F5" s="300"/>
+      <c r="D5" s="298"/>
+      <c r="E5" s="298"/>
+      <c r="F5" s="299"/>
       <c r="G5" s="74"/>
       <c r="H5" s="74"/>
       <c r="I5" s="74"/>
@@ -10907,25 +10965,25 @@
     </row>
     <row r="7" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="107"/>
-      <c r="B7" s="178" t="s">
+      <c r="B7" s="177" t="s">
         <v>145</v>
       </c>
-      <c r="C7" s="179"/>
-      <c r="D7" s="180"/>
-      <c r="E7" s="524" t="s">
+      <c r="C7" s="178"/>
+      <c r="D7" s="179"/>
+      <c r="E7" s="516" t="s">
         <v>20</v>
       </c>
-      <c r="F7" s="525"/>
+      <c r="F7" s="517"/>
       <c r="G7" s="65"/>
-      <c r="H7" s="178" t="s">
+      <c r="H7" s="177" t="s">
         <v>162</v>
       </c>
-      <c r="I7" s="179"/>
-      <c r="J7" s="181"/>
-      <c r="K7" s="504" t="s">
+      <c r="I7" s="178"/>
+      <c r="J7" s="180"/>
+      <c r="K7" s="521" t="s">
         <v>20</v>
       </c>
-      <c r="L7" s="505"/>
+      <c r="L7" s="522"/>
       <c r="M7" s="65"/>
       <c r="N7" s="65"/>
     </row>
@@ -10946,82 +11004,82 @@
     </row>
     <row r="9" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="107"/>
-      <c r="B9" s="520" t="s">
+      <c r="B9" s="512" t="s">
         <v>152</v>
       </c>
-      <c r="C9" s="520"/>
-      <c r="D9" s="519" t="e">
+      <c r="C9" s="512"/>
+      <c r="D9" s="511" t="e">
         <f>+INDEX(P13:Q23,MATCH(E7,P13:P23,0),2)</f>
         <v>#N/A</v>
       </c>
-      <c r="E9" s="519"/>
-      <c r="F9" s="521" t="e">
+      <c r="E9" s="511"/>
+      <c r="F9" s="513" t="e">
         <f>+IF(I13/1000&gt;D9,"Cumple","No Cumple")</f>
         <v>#N/A</v>
       </c>
-      <c r="G9" s="521"/>
+      <c r="G9" s="513"/>
       <c r="H9" s="65"/>
-      <c r="J9" s="194" t="s">
+      <c r="J9" s="193" t="s">
         <v>168</v>
       </c>
-      <c r="K9" s="310" t="s">
+      <c r="K9" s="309" t="s">
         <v>20</v>
       </c>
-      <c r="O9" s="147"/>
+      <c r="O9" s="146"/>
     </row>
     <row r="10" spans="1:20" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="107"/>
-      <c r="B10" s="174"/>
-      <c r="C10" s="174"/>
-      <c r="D10" s="175"/>
-      <c r="E10" s="175"/>
-      <c r="F10" s="176"/>
-      <c r="G10" s="176"/>
+      <c r="B10" s="173"/>
+      <c r="C10" s="173"/>
+      <c r="D10" s="174"/>
+      <c r="E10" s="174"/>
+      <c r="F10" s="175"/>
+      <c r="G10" s="175"/>
       <c r="H10" s="65"/>
-      <c r="O10" s="147"/>
+      <c r="O10" s="146"/>
     </row>
     <row r="11" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="523" t="s">
+      <c r="A11" s="515" t="s">
         <v>41</v>
       </c>
-      <c r="B11" s="523"/>
-      <c r="C11" s="523"/>
-      <c r="D11" s="523"/>
-      <c r="E11" s="523"/>
-      <c r="F11" s="523"/>
-      <c r="G11" s="523"/>
-      <c r="H11" s="523" t="s">
+      <c r="B11" s="515"/>
+      <c r="C11" s="515"/>
+      <c r="D11" s="515"/>
+      <c r="E11" s="515"/>
+      <c r="F11" s="515"/>
+      <c r="G11" s="515"/>
+      <c r="H11" s="515" t="s">
         <v>42</v>
       </c>
-      <c r="I11" s="522" t="s">
+      <c r="I11" s="514" t="s">
         <v>134</v>
       </c>
-      <c r="J11" s="522"/>
-      <c r="K11" s="522" t="s">
+      <c r="J11" s="514"/>
+      <c r="K11" s="514" t="s">
         <v>135</v>
       </c>
-      <c r="L11" s="522"/>
-      <c r="M11" s="522" t="s">
+      <c r="L11" s="514"/>
+      <c r="M11" s="514" t="s">
         <v>136</v>
       </c>
-      <c r="N11" s="522"/>
-      <c r="O11" s="148"/>
-      <c r="P11" s="177" t="s">
+      <c r="N11" s="514"/>
+      <c r="O11" s="147"/>
+      <c r="P11" s="176" t="s">
         <v>159</v>
       </c>
-      <c r="Q11" s="177" t="s">
+      <c r="Q11" s="176" t="s">
         <v>158</v>
       </c>
     </row>
     <row r="12" spans="1:20" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="523"/>
-      <c r="B12" s="523"/>
-      <c r="C12" s="523"/>
-      <c r="D12" s="523"/>
-      <c r="E12" s="523"/>
-      <c r="F12" s="523"/>
-      <c r="G12" s="523"/>
-      <c r="H12" s="523"/>
+      <c r="A12" s="515"/>
+      <c r="B12" s="515"/>
+      <c r="C12" s="515"/>
+      <c r="D12" s="515"/>
+      <c r="E12" s="515"/>
+      <c r="F12" s="515"/>
+      <c r="G12" s="515"/>
+      <c r="H12" s="515"/>
       <c r="I12" s="111" t="s">
         <v>43</v>
       </c>
@@ -11040,164 +11098,164 @@
       <c r="N12" s="111" t="s">
         <v>151</v>
       </c>
-      <c r="O12" s="172"/>
-      <c r="P12" s="177" t="s">
+      <c r="O12" s="171"/>
+      <c r="P12" s="176" t="s">
         <v>161</v>
       </c>
-      <c r="Q12" s="177" t="s">
+      <c r="Q12" s="176" t="s">
         <v>160</v>
       </c>
     </row>
     <row r="13" spans="1:20" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="184"/>
-      <c r="B13" s="185" t="s">
+      <c r="A13" s="183"/>
+      <c r="B13" s="184" t="s">
         <v>146</v>
       </c>
-      <c r="C13" s="186"/>
-      <c r="D13" s="186"/>
-      <c r="E13" s="186"/>
-      <c r="F13" s="186"/>
-      <c r="G13" s="187"/>
-      <c r="H13" s="184"/>
-      <c r="I13" s="518">
+      <c r="C13" s="185"/>
+      <c r="D13" s="185"/>
+      <c r="E13" s="185"/>
+      <c r="F13" s="185"/>
+      <c r="G13" s="186"/>
+      <c r="H13" s="183"/>
+      <c r="I13" s="510">
         <f>+'FORMATO PEG'!O27</f>
         <v>0</v>
       </c>
-      <c r="J13" s="518"/>
-      <c r="K13" s="518"/>
-      <c r="L13" s="518"/>
-      <c r="M13" s="518"/>
-      <c r="N13" s="518"/>
-      <c r="O13" s="149"/>
-      <c r="P13" s="164" t="s">
+      <c r="J13" s="510"/>
+      <c r="K13" s="510"/>
+      <c r="L13" s="510"/>
+      <c r="M13" s="510"/>
+      <c r="N13" s="510"/>
+      <c r="O13" s="148"/>
+      <c r="P13" s="163" t="s">
         <v>144</v>
       </c>
-      <c r="Q13" s="164">
+      <c r="Q13" s="163">
         <v>40</v>
       </c>
     </row>
     <row r="14" spans="1:20" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="184"/>
-      <c r="B14" s="167" t="s">
+      <c r="A14" s="183"/>
+      <c r="B14" s="166" t="s">
         <v>153</v>
       </c>
-      <c r="C14" s="186"/>
-      <c r="D14" s="186"/>
-      <c r="E14" s="186"/>
-      <c r="F14" s="186"/>
-      <c r="G14" s="187"/>
-      <c r="H14" s="184" t="s">
+      <c r="C14" s="185"/>
+      <c r="D14" s="185"/>
+      <c r="E14" s="185"/>
+      <c r="F14" s="185"/>
+      <c r="G14" s="186"/>
+      <c r="H14" s="183" t="s">
         <v>47</v>
       </c>
-      <c r="I14" s="311">
+      <c r="I14" s="310">
         <f>+'FORMATO PEG'!O28</f>
         <v>0</v>
       </c>
-      <c r="J14" s="133">
+      <c r="J14" s="132">
         <f>I14+($C$4*I14)</f>
         <v>0</v>
       </c>
-      <c r="K14" s="188">
+      <c r="K14" s="187">
         <f>+'FORMATO PEG'!O29</f>
         <v>0</v>
       </c>
-      <c r="L14" s="133">
+      <c r="L14" s="132">
         <f>IF($K$7=1,"",K14+($C$4*K14))</f>
         <v>0</v>
       </c>
-      <c r="M14" s="188"/>
-      <c r="N14" s="133" t="str">
+      <c r="M14" s="187"/>
+      <c r="N14" s="132" t="str">
         <f>IF($K$7=3,M14+($C$4*M14),"")</f>
         <v/>
       </c>
-      <c r="O14" s="150"/>
-      <c r="P14" s="164" t="s">
+      <c r="O14" s="149"/>
+      <c r="P14" s="163" t="s">
         <v>143</v>
       </c>
-      <c r="Q14" s="164">
+      <c r="Q14" s="163">
         <v>25</v>
       </c>
     </row>
     <row r="15" spans="1:20" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="184"/>
-      <c r="B15" s="167" t="s">
+      <c r="A15" s="183"/>
+      <c r="B15" s="166" t="s">
         <v>154</v>
       </c>
-      <c r="C15" s="186"/>
-      <c r="D15" s="506" t="s">
+      <c r="C15" s="185"/>
+      <c r="D15" s="523" t="s">
         <v>147</v>
       </c>
-      <c r="E15" s="506"/>
-      <c r="F15" s="516" t="e">
+      <c r="E15" s="523"/>
+      <c r="F15" s="508" t="e">
         <f>+SUM(J15,L15,N15)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="G15" s="517"/>
-      <c r="H15" s="184" t="s">
+      <c r="G15" s="509"/>
+      <c r="H15" s="183" t="s">
         <v>24</v>
       </c>
-      <c r="I15" s="183"/>
-      <c r="J15" s="189" t="e">
+      <c r="I15" s="182"/>
+      <c r="J15" s="188" t="e">
         <f>+(J14/$I$13)*100</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="K15" s="183"/>
-      <c r="L15" s="189" t="e">
+      <c r="K15" s="182"/>
+      <c r="L15" s="188" t="e">
         <f>+IF($K$7=1,"",(L14/$I$13)*100)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="M15" s="183"/>
-      <c r="N15" s="189" t="str">
+      <c r="M15" s="182"/>
+      <c r="N15" s="188" t="str">
         <f>IF($K$7=3,(N14/$I$13)*100,"")</f>
         <v/>
       </c>
-      <c r="O15" s="151"/>
-      <c r="P15" s="164" t="s">
+      <c r="O15" s="150"/>
+      <c r="P15" s="163" t="s">
         <v>142</v>
       </c>
-      <c r="Q15" s="164">
+      <c r="Q15" s="163">
         <v>18</v>
       </c>
-      <c r="T15" s="305"/>
+      <c r="T15" s="304"/>
     </row>
     <row r="16" spans="1:20" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="61" t="s">
         <v>45</v>
       </c>
-      <c r="B16" s="167" t="s">
+      <c r="B16" s="166" t="s">
         <v>46</v>
       </c>
-      <c r="C16" s="186"/>
-      <c r="D16" s="186"/>
-      <c r="E16" s="186"/>
-      <c r="F16" s="186"/>
-      <c r="G16" s="187"/>
-      <c r="H16" s="143" t="s">
+      <c r="C16" s="185"/>
+      <c r="D16" s="185"/>
+      <c r="E16" s="185"/>
+      <c r="F16" s="185"/>
+      <c r="G16" s="186"/>
+      <c r="H16" s="142" t="s">
         <v>47</v>
       </c>
-      <c r="I16" s="190">
+      <c r="I16" s="189">
         <f>+'FORMATO PEG'!M34</f>
         <v>0</v>
       </c>
-      <c r="J16" s="133">
+      <c r="J16" s="132">
         <f>I16+($C$4*I16)</f>
         <v>0</v>
       </c>
-      <c r="K16" s="190"/>
-      <c r="L16" s="133">
+      <c r="K16" s="189"/>
+      <c r="L16" s="132">
         <f>IF($K$7=1,"",K16+($C$4*K16))</f>
         <v>0</v>
       </c>
-      <c r="M16" s="190"/>
-      <c r="N16" s="133" t="str">
+      <c r="M16" s="189"/>
+      <c r="N16" s="132" t="str">
         <f>IF($K$7=3,M16+($C$4*M16),"")</f>
         <v/>
       </c>
-      <c r="O16" s="150"/>
-      <c r="P16" s="165">
+      <c r="O16" s="149"/>
+      <c r="P16" s="164">
         <v>2.5</v>
       </c>
-      <c r="Q16" s="164">
+      <c r="Q16" s="163">
         <v>12</v>
       </c>
     </row>
@@ -11205,40 +11263,40 @@
       <c r="A17" s="61" t="s">
         <v>48</v>
       </c>
-      <c r="B17" s="475" t="s">
+      <c r="B17" s="424" t="s">
         <v>49</v>
       </c>
-      <c r="C17" s="476"/>
-      <c r="D17" s="476"/>
-      <c r="E17" s="476"/>
-      <c r="F17" s="476"/>
-      <c r="G17" s="477"/>
-      <c r="H17" s="143" t="s">
+      <c r="C17" s="425"/>
+      <c r="D17" s="425"/>
+      <c r="E17" s="425"/>
+      <c r="F17" s="425"/>
+      <c r="G17" s="426"/>
+      <c r="H17" s="142" t="s">
         <v>47</v>
       </c>
-      <c r="I17" s="190">
+      <c r="I17" s="189">
         <f>+'FORMATO PEG'!M35</f>
         <v>0</v>
       </c>
-      <c r="J17" s="133">
+      <c r="J17" s="132">
         <f>I17+($C$4*I17)</f>
         <v>0</v>
       </c>
-      <c r="K17" s="190"/>
-      <c r="L17" s="133">
+      <c r="K17" s="189"/>
+      <c r="L17" s="132">
         <f>IF($K$7=1,"",K17+($C$4*K17))</f>
         <v>0</v>
       </c>
-      <c r="M17" s="190"/>
-      <c r="N17" s="133" t="str">
+      <c r="M17" s="189"/>
+      <c r="N17" s="132" t="str">
         <f>IF($K$7=3,M17+($C$4*M17),"")</f>
         <v/>
       </c>
-      <c r="O17" s="150"/>
-      <c r="P17" s="166" t="s">
+      <c r="O17" s="149"/>
+      <c r="P17" s="165" t="s">
         <v>138</v>
       </c>
-      <c r="Q17" s="164">
+      <c r="Q17" s="163">
         <v>8</v>
       </c>
     </row>
@@ -11246,40 +11304,40 @@
       <c r="A18" s="61" t="s">
         <v>50</v>
       </c>
-      <c r="B18" s="501" t="s">
+      <c r="B18" s="518" t="s">
         <v>51</v>
       </c>
-      <c r="C18" s="502"/>
-      <c r="D18" s="502"/>
-      <c r="E18" s="502"/>
-      <c r="F18" s="502"/>
-      <c r="G18" s="503"/>
-      <c r="H18" s="143" t="s">
+      <c r="C18" s="519"/>
+      <c r="D18" s="519"/>
+      <c r="E18" s="519"/>
+      <c r="F18" s="519"/>
+      <c r="G18" s="520"/>
+      <c r="H18" s="142" t="s">
         <v>47</v>
       </c>
-      <c r="I18" s="190">
+      <c r="I18" s="189">
         <f>+'FORMATO PEG'!M36</f>
         <v>0</v>
       </c>
-      <c r="J18" s="133">
+      <c r="J18" s="132">
         <f>I18+($C$4*I18)</f>
         <v>0</v>
       </c>
-      <c r="K18" s="190"/>
-      <c r="L18" s="133">
+      <c r="K18" s="189"/>
+      <c r="L18" s="132">
         <f>IF($K$7=1,"",K18+($C$4*K18))</f>
         <v>0</v>
       </c>
-      <c r="M18" s="190"/>
-      <c r="N18" s="133" t="str">
+      <c r="M18" s="189"/>
+      <c r="N18" s="132" t="str">
         <f>IF($K$7=3,M18+($C$4*M18),"")</f>
         <v/>
       </c>
-      <c r="O18" s="150"/>
-      <c r="P18" s="166" t="s">
+      <c r="O18" s="149"/>
+      <c r="P18" s="165" t="s">
         <v>62</v>
       </c>
-      <c r="Q18" s="164">
+      <c r="Q18" s="163">
         <v>5</v>
       </c>
     </row>
@@ -11287,40 +11345,40 @@
       <c r="A19" s="61" t="s">
         <v>52</v>
       </c>
-      <c r="B19" s="167" t="s">
+      <c r="B19" s="166" t="s">
         <v>53</v>
       </c>
       <c r="C19" s="131"/>
       <c r="D19" s="131"/>
       <c r="E19" s="131"/>
       <c r="F19" s="131"/>
-      <c r="G19" s="135"/>
-      <c r="H19" s="144" t="s">
+      <c r="G19" s="134"/>
+      <c r="H19" s="143" t="s">
         <v>47</v>
       </c>
-      <c r="I19" s="142">
+      <c r="I19" s="141">
         <f>+'FORMATO PEG'!O38</f>
         <v>0</v>
       </c>
-      <c r="J19" s="133">
+      <c r="J19" s="132">
         <f>I19+($C$4*I19)</f>
         <v>0</v>
       </c>
-      <c r="K19" s="142"/>
-      <c r="L19" s="133">
+      <c r="K19" s="141"/>
+      <c r="L19" s="132">
         <f>IF($K$7=1,"",K19+($C$4*K19))</f>
         <v>0</v>
       </c>
-      <c r="M19" s="142"/>
-      <c r="N19" s="133" t="str">
+      <c r="M19" s="141"/>
+      <c r="N19" s="132" t="str">
         <f>IF($K$7=3,M19+($C$4*M19),"")</f>
         <v/>
       </c>
-      <c r="O19" s="150"/>
-      <c r="P19" s="166" t="s">
+      <c r="O19" s="149"/>
+      <c r="P19" s="165" t="s">
         <v>139</v>
       </c>
-      <c r="Q19" s="164">
+      <c r="Q19" s="163">
         <v>4</v>
       </c>
     </row>
@@ -11328,17 +11386,17 @@
       <c r="A20" s="61" t="s">
         <v>54</v>
       </c>
-      <c r="B20" s="167" t="s">
+      <c r="B20" s="166" t="s">
         <v>55</v>
       </c>
       <c r="C20" s="131"/>
       <c r="D20" s="131"/>
       <c r="E20" s="131"/>
       <c r="F20" s="131"/>
-      <c r="G20" s="135"/>
-      <c r="H20" s="145"/>
+      <c r="G20" s="134"/>
+      <c r="H20" s="144"/>
       <c r="I20" s="62"/>
-      <c r="J20" s="307" t="e">
+      <c r="J20" s="306" t="e">
         <f>J17/(J18-J19)</f>
         <v>#DIV/0!</v>
       </c>
@@ -11352,11 +11410,11 @@
         <f>IF(N19="","",N17/(N18-N19))</f>
         <v/>
       </c>
-      <c r="O20" s="152"/>
-      <c r="P20" s="166" t="s">
+      <c r="O20" s="151"/>
+      <c r="P20" s="165" t="s">
         <v>137</v>
       </c>
-      <c r="Q20" s="164">
+      <c r="Q20" s="163">
         <v>3</v>
       </c>
     </row>
@@ -11364,17 +11422,17 @@
       <c r="A21" s="61" t="s">
         <v>56</v>
       </c>
-      <c r="B21" s="167" t="s">
+      <c r="B21" s="166" t="s">
         <v>57</v>
       </c>
       <c r="C21" s="131"/>
       <c r="D21" s="131"/>
       <c r="E21" s="131"/>
       <c r="F21" s="131"/>
-      <c r="G21" s="135"/>
-      <c r="H21" s="145"/>
+      <c r="G21" s="134"/>
+      <c r="H21" s="144"/>
       <c r="I21" s="62"/>
-      <c r="J21" s="307" t="e">
+      <c r="J21" s="306" t="e">
         <f>J18/(J18-J19)</f>
         <v>#DIV/0!</v>
       </c>
@@ -11388,11 +11446,11 @@
         <f>IF(N19="","",N18/(N18-N19))</f>
         <v/>
       </c>
-      <c r="O21" s="152"/>
-      <c r="P21" s="166" t="s">
+      <c r="O21" s="151"/>
+      <c r="P21" s="165" t="s">
         <v>183</v>
       </c>
-      <c r="Q21" s="164">
+      <c r="Q21" s="163">
         <v>2</v>
       </c>
     </row>
@@ -11400,17 +11458,17 @@
       <c r="A22" s="61" t="s">
         <v>58</v>
       </c>
-      <c r="B22" s="167" t="s">
+      <c r="B22" s="166" t="s">
         <v>59</v>
       </c>
       <c r="C22" s="131"/>
       <c r="D22" s="131"/>
       <c r="E22" s="131"/>
       <c r="F22" s="131"/>
-      <c r="G22" s="135"/>
-      <c r="H22" s="145"/>
+      <c r="G22" s="134"/>
+      <c r="H22" s="144"/>
       <c r="I22" s="62"/>
-      <c r="J22" s="307" t="e">
+      <c r="J22" s="306" t="e">
         <f t="shared" ref="J22" si="0">J17/(J17-J19)</f>
         <v>#DIV/0!</v>
       </c>
@@ -11424,11 +11482,11 @@
         <f>IF(N19="","",N17/(N17-N19))</f>
         <v/>
       </c>
-      <c r="O22" s="152"/>
-      <c r="P22" s="166" t="s">
+      <c r="O22" s="151"/>
+      <c r="P22" s="165" t="s">
         <v>184</v>
       </c>
-      <c r="Q22" s="164">
+      <c r="Q22" s="163">
         <v>2</v>
       </c>
     </row>
@@ -11436,19 +11494,19 @@
       <c r="A23" s="61" t="s">
         <v>60</v>
       </c>
-      <c r="B23" s="167" t="s">
+      <c r="B23" s="166" t="s">
         <v>61</v>
       </c>
       <c r="C23" s="131"/>
       <c r="D23" s="131"/>
       <c r="E23" s="131"/>
       <c r="F23" s="131"/>
-      <c r="G23" s="135"/>
-      <c r="H23" s="146" t="s">
+      <c r="G23" s="134"/>
+      <c r="H23" s="145" t="s">
         <v>24</v>
       </c>
       <c r="I23" s="63"/>
-      <c r="J23" s="306" t="e">
+      <c r="J23" s="305" t="e">
         <f>(J18-J17)/J17*100</f>
         <v>#DIV/0!</v>
       </c>
@@ -11462,120 +11520,132 @@
         <f>IF(N19="","",(N18-N17)/N17*100)</f>
         <v/>
       </c>
-      <c r="O23" s="153"/>
-      <c r="P23" s="166" t="s">
+      <c r="O23" s="152"/>
+      <c r="P23" s="165" t="s">
         <v>140</v>
       </c>
-      <c r="Q23" s="164">
+      <c r="Q23" s="163">
         <v>2</v>
       </c>
     </row>
     <row r="24" spans="1:17" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="P24" s="166" t="s">
+      <c r="P24" s="165" t="s">
         <v>141</v>
       </c>
-      <c r="Q24" s="164"/>
+      <c r="Q24" s="163"/>
     </row>
     <row r="25" spans="1:17" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="68"/>
-      <c r="B25" s="475" t="s">
+      <c r="B25" s="424" t="s">
         <v>63</v>
       </c>
-      <c r="C25" s="476"/>
-      <c r="D25" s="476"/>
-      <c r="E25" s="476"/>
-      <c r="F25" s="476"/>
-      <c r="G25" s="477"/>
+      <c r="C25" s="425"/>
+      <c r="D25" s="425"/>
+      <c r="E25" s="425"/>
+      <c r="F25" s="425"/>
+      <c r="G25" s="426"/>
       <c r="H25" s="55"/>
-      <c r="I25" s="510" t="b">
+      <c r="I25" s="527" t="b">
         <f>IF(K7=1,J20,IF(K7=2,1/(($J$15/100)/J20+($L$15/100)/L20),IF(K7=3,1/(($J$15/100)/J20+($L$15/100)/L20+(N15/100)/N20))))</f>
         <v>0</v>
       </c>
-      <c r="J25" s="511"/>
-      <c r="K25" s="511"/>
-      <c r="L25" s="511"/>
-      <c r="M25" s="511"/>
-      <c r="N25" s="512"/>
-      <c r="O25" s="173"/>
-      <c r="P25" s="164" t="s">
+      <c r="J25" s="528"/>
+      <c r="K25" s="528"/>
+      <c r="L25" s="528"/>
+      <c r="M25" s="528"/>
+      <c r="N25" s="529"/>
+      <c r="O25" s="172"/>
+      <c r="P25" s="163" t="s">
         <v>20</v>
       </c>
-      <c r="Q25" s="194" t="e">
+      <c r="Q25" s="193" t="e">
         <f>+(I14-I16)/I16*100</f>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="26" spans="1:17" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="68"/>
-      <c r="B26" s="475" t="s">
+      <c r="B26" s="424" t="s">
         <v>64</v>
       </c>
-      <c r="C26" s="476"/>
-      <c r="D26" s="476"/>
-      <c r="E26" s="476"/>
-      <c r="F26" s="476"/>
-      <c r="G26" s="477"/>
+      <c r="C26" s="425"/>
+      <c r="D26" s="425"/>
+      <c r="E26" s="425"/>
+      <c r="F26" s="425"/>
+      <c r="G26" s="426"/>
       <c r="H26" s="55"/>
-      <c r="I26" s="510" t="b">
+      <c r="I26" s="527" t="b">
         <f>IF(K7=1,J21,IF(K7=2,1/(($J$15/100)/J21+($L$15/100)/L21),IF(K7=3,1/(($J$15/100)/J21+($L$15/100)/L21+(N15/100)/N21))))</f>
         <v>0</v>
       </c>
-      <c r="J26" s="511"/>
-      <c r="K26" s="511"/>
-      <c r="L26" s="511"/>
-      <c r="M26" s="511"/>
-      <c r="N26" s="512"/>
-      <c r="O26" s="173"/>
+      <c r="J26" s="528"/>
+      <c r="K26" s="528"/>
+      <c r="L26" s="528"/>
+      <c r="M26" s="528"/>
+      <c r="N26" s="529"/>
+      <c r="O26" s="172"/>
     </row>
     <row r="27" spans="1:17" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="68"/>
-      <c r="B27" s="475" t="s">
+      <c r="B27" s="424" t="s">
         <v>65</v>
       </c>
-      <c r="C27" s="476"/>
-      <c r="D27" s="476"/>
-      <c r="E27" s="476"/>
-      <c r="F27" s="476"/>
-      <c r="G27" s="477"/>
+      <c r="C27" s="425"/>
+      <c r="D27" s="425"/>
+      <c r="E27" s="425"/>
+      <c r="F27" s="425"/>
+      <c r="G27" s="426"/>
       <c r="H27" s="55"/>
-      <c r="I27" s="510" t="b">
+      <c r="I27" s="527" t="b">
         <f>IF(K7=1,J22,IF(K7=2,1/(($J$15/100)/J22+($L$15/100)/L22),IF(K7=3,1/(($J$15/100)/J22+($L$15/100)/L22+(N15/100)/N22))))</f>
         <v>0</v>
       </c>
-      <c r="J27" s="511"/>
-      <c r="K27" s="511"/>
-      <c r="L27" s="511"/>
-      <c r="M27" s="511"/>
-      <c r="N27" s="512"/>
-      <c r="O27" s="173"/>
+      <c r="J27" s="528"/>
+      <c r="K27" s="528"/>
+      <c r="L27" s="528"/>
+      <c r="M27" s="528"/>
+      <c r="N27" s="529"/>
+      <c r="O27" s="172"/>
     </row>
     <row r="28" spans="1:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="68"/>
-      <c r="B28" s="475" t="s">
+      <c r="B28" s="424" t="s">
         <v>66</v>
       </c>
-      <c r="C28" s="476"/>
-      <c r="D28" s="476"/>
-      <c r="E28" s="476"/>
-      <c r="F28" s="476"/>
-      <c r="G28" s="477"/>
+      <c r="C28" s="425"/>
+      <c r="D28" s="425"/>
+      <c r="E28" s="425"/>
+      <c r="F28" s="425"/>
+      <c r="G28" s="426"/>
       <c r="H28" s="56" t="s">
         <v>24</v>
       </c>
-      <c r="I28" s="507" t="b">
+      <c r="I28" s="524" t="b">
         <f>IF(K7=1,J23,IF(K7=2,1/(($J$15/100)/J23+($L$15/100)/L23),IF(K7=3,1/(($J$15/100)/J23+($L$15/100)/L23+(N15/100)/N23))))</f>
         <v>0</v>
       </c>
-      <c r="J28" s="508"/>
-      <c r="K28" s="508"/>
-      <c r="L28" s="508"/>
-      <c r="M28" s="508"/>
-      <c r="N28" s="509"/>
-      <c r="O28" s="153"/>
+      <c r="J28" s="525"/>
+      <c r="K28" s="525"/>
+      <c r="L28" s="525"/>
+      <c r="M28" s="525"/>
+      <c r="N28" s="526"/>
+      <c r="O28" s="152"/>
     </row>
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="W+ehWvk1+G4fxMwMlFFe24eUcB7dTRS6CSN4hdQEHiO/u8gs+lAQOb/9/FmIcet9iZVIOf5wG+i5LTmEs2xhcA==" saltValue="AwzUmQKx7HBfx5Grx49ElQ==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="24">
+    <mergeCell ref="B17:G17"/>
+    <mergeCell ref="B18:G18"/>
+    <mergeCell ref="K7:L7"/>
+    <mergeCell ref="D15:E15"/>
+    <mergeCell ref="I28:N28"/>
+    <mergeCell ref="I26:N26"/>
+    <mergeCell ref="I25:N25"/>
+    <mergeCell ref="I27:N27"/>
+    <mergeCell ref="B28:G28"/>
+    <mergeCell ref="B25:G25"/>
+    <mergeCell ref="B26:G26"/>
+    <mergeCell ref="B27:G27"/>
     <mergeCell ref="A1:N1"/>
     <mergeCell ref="F15:G15"/>
     <mergeCell ref="I13:N13"/>
@@ -11588,18 +11658,6 @@
     <mergeCell ref="A11:G12"/>
     <mergeCell ref="H11:H12"/>
     <mergeCell ref="E7:F7"/>
-    <mergeCell ref="B17:G17"/>
-    <mergeCell ref="B18:G18"/>
-    <mergeCell ref="K7:L7"/>
-    <mergeCell ref="D15:E15"/>
-    <mergeCell ref="I28:N28"/>
-    <mergeCell ref="I26:N26"/>
-    <mergeCell ref="I25:N25"/>
-    <mergeCell ref="I27:N27"/>
-    <mergeCell ref="B28:G28"/>
-    <mergeCell ref="B25:G25"/>
-    <mergeCell ref="B26:G26"/>
-    <mergeCell ref="B27:G27"/>
   </mergeCells>
   <conditionalFormatting sqref="F9:G10 O9:O10">
     <cfRule type="containsText" dxfId="0" priority="2" operator="containsText" text="no">
@@ -11646,16 +11704,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="527"/>
-      <c r="B1" s="530" t="s">
+      <c r="A1" s="539"/>
+      <c r="B1" s="542" t="s">
         <v>77</v>
       </c>
-      <c r="C1" s="531"/>
-      <c r="D1" s="531"/>
-      <c r="E1" s="531"/>
-      <c r="F1" s="531"/>
-      <c r="G1" s="531"/>
-      <c r="H1" s="532"/>
+      <c r="C1" s="543"/>
+      <c r="D1" s="543"/>
+      <c r="E1" s="543"/>
+      <c r="F1" s="543"/>
+      <c r="G1" s="543"/>
+      <c r="H1" s="544"/>
       <c r="I1" s="84" t="s">
         <v>78</v>
       </c>
@@ -11664,14 +11722,14 @@
       </c>
     </row>
     <row r="2" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="528"/>
-      <c r="B2" s="533"/>
-      <c r="C2" s="534"/>
-      <c r="D2" s="534"/>
-      <c r="E2" s="534"/>
-      <c r="F2" s="534"/>
-      <c r="G2" s="534"/>
-      <c r="H2" s="535"/>
+      <c r="A2" s="540"/>
+      <c r="B2" s="545"/>
+      <c r="C2" s="546"/>
+      <c r="D2" s="546"/>
+      <c r="E2" s="546"/>
+      <c r="F2" s="546"/>
+      <c r="G2" s="546"/>
+      <c r="H2" s="547"/>
       <c r="I2" s="84" t="s">
         <v>80</v>
       </c>
@@ -11680,14 +11738,14 @@
       </c>
     </row>
     <row r="3" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="528"/>
-      <c r="B3" s="533"/>
-      <c r="C3" s="534"/>
-      <c r="D3" s="534"/>
-      <c r="E3" s="534"/>
-      <c r="F3" s="534"/>
-      <c r="G3" s="534"/>
-      <c r="H3" s="535"/>
+      <c r="A3" s="540"/>
+      <c r="B3" s="545"/>
+      <c r="C3" s="546"/>
+      <c r="D3" s="546"/>
+      <c r="E3" s="546"/>
+      <c r="F3" s="546"/>
+      <c r="G3" s="546"/>
+      <c r="H3" s="547"/>
       <c r="I3" s="84" t="s">
         <v>81</v>
       </c>
@@ -11696,14 +11754,14 @@
       </c>
     </row>
     <row r="4" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="529"/>
-      <c r="B4" s="536"/>
-      <c r="C4" s="537"/>
-      <c r="D4" s="537"/>
-      <c r="E4" s="537"/>
-      <c r="F4" s="537"/>
-      <c r="G4" s="537"/>
-      <c r="H4" s="538"/>
+      <c r="A4" s="541"/>
+      <c r="B4" s="548"/>
+      <c r="C4" s="549"/>
+      <c r="D4" s="549"/>
+      <c r="E4" s="549"/>
+      <c r="F4" s="549"/>
+      <c r="G4" s="549"/>
+      <c r="H4" s="550"/>
       <c r="I4" s="84" t="s">
         <v>82</v>
       </c>
@@ -11712,16 +11770,16 @@
       </c>
     </row>
     <row r="6" spans="1:13" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="238" t="s">
+      <c r="A6" s="237" t="s">
         <v>84</v>
       </c>
-      <c r="B6" s="239" t="str">
+      <c r="B6" s="238" t="str">
         <f>+DATOS!A1</f>
         <v>Densidad relativa (peso específico) y absorción del agregado grueso ASTM C127-25</v>
       </c>
-      <c r="C6" s="240"/>
-      <c r="D6" s="240"/>
-      <c r="E6" s="240"/>
+      <c r="C6" s="239"/>
+      <c r="D6" s="239"/>
+      <c r="E6" s="239"/>
       <c r="F6" s="3"/>
       <c r="G6" s="3"/>
       <c r="H6" s="3"/>
@@ -11729,15 +11787,15 @@
       <c r="J6" s="2"/>
     </row>
     <row r="7" spans="1:13" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="238" t="s">
+      <c r="A7" s="237" t="s">
         <v>85</v>
       </c>
-      <c r="B7" s="239" t="s">
+      <c r="B7" s="238" t="s">
         <v>179</v>
       </c>
-      <c r="C7" s="240"/>
-      <c r="D7" s="240"/>
-      <c r="E7" s="240"/>
+      <c r="C7" s="239"/>
+      <c r="D7" s="239"/>
+      <c r="E7" s="239"/>
       <c r="F7" s="3"/>
       <c r="G7" s="3"/>
       <c r="H7" s="3"/>
@@ -11745,15 +11803,15 @@
       <c r="J7" s="2"/>
     </row>
     <row r="8" spans="1:13" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="238" t="s">
+      <c r="A8" s="237" t="s">
         <v>86</v>
       </c>
-      <c r="B8" s="239" t="s">
+      <c r="B8" s="238" t="s">
         <v>163</v>
       </c>
-      <c r="C8" s="240"/>
-      <c r="D8" s="240"/>
-      <c r="E8" s="240"/>
+      <c r="C8" s="239"/>
+      <c r="D8" s="239"/>
+      <c r="E8" s="239"/>
       <c r="F8" s="3"/>
       <c r="G8" s="3"/>
       <c r="H8" s="3"/>
@@ -11761,15 +11819,15 @@
       <c r="J8" s="2"/>
     </row>
     <row r="9" spans="1:13" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="238" t="s">
+      <c r="A9" s="237" t="s">
         <v>87</v>
       </c>
-      <c r="B9" s="239" t="s">
+      <c r="B9" s="238" t="s">
         <v>88</v>
       </c>
-      <c r="C9" s="240"/>
-      <c r="D9" s="240"/>
-      <c r="E9" s="240"/>
+      <c r="C9" s="239"/>
+      <c r="D9" s="239"/>
+      <c r="E9" s="239"/>
       <c r="F9" s="3"/>
       <c r="G9" s="3"/>
       <c r="H9" s="3"/>
@@ -11777,15 +11835,15 @@
       <c r="J9" s="2"/>
     </row>
     <row r="10" spans="1:13" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="238" t="s">
+      <c r="A10" s="237" t="s">
         <v>89</v>
       </c>
-      <c r="B10" s="239" t="s">
+      <c r="B10" s="238" t="s">
         <v>164</v>
       </c>
-      <c r="C10" s="240"/>
-      <c r="D10" s="240"/>
-      <c r="E10" s="240"/>
+      <c r="C10" s="239"/>
+      <c r="D10" s="239"/>
+      <c r="E10" s="239"/>
       <c r="F10" s="3"/>
       <c r="G10" s="3"/>
       <c r="H10" s="3"/>
@@ -11793,15 +11851,15 @@
       <c r="J10" s="2"/>
     </row>
     <row r="11" spans="1:13" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="241" t="s">
+      <c r="A11" s="240" t="s">
         <v>90</v>
       </c>
-      <c r="B11" s="239" t="s">
+      <c r="B11" s="238" t="s">
         <v>169</v>
       </c>
-      <c r="C11" s="240"/>
-      <c r="D11" s="240"/>
-      <c r="E11" s="240"/>
+      <c r="C11" s="239"/>
+      <c r="D11" s="239"/>
+      <c r="E11" s="239"/>
       <c r="F11" s="3"/>
       <c r="G11" s="3"/>
       <c r="H11" s="3"/>
@@ -11836,13 +11894,13 @@
       <c r="F16" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="G16" s="242"/>
+      <c r="G16" s="241"/>
     </row>
     <row r="17" spans="1:13" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="H17" s="242"/>
+      <c r="H17" s="241"/>
       <c r="K17" s="112"/>
     </row>
     <row r="18" spans="1:13" ht="12" customHeight="1" x14ac:dyDescent="0.25">
@@ -11855,11 +11913,11 @@
       <c r="M18" s="112"/>
     </row>
     <row r="19" spans="1:13" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="539"/>
-      <c r="B19" s="539"/>
-      <c r="C19" s="539"/>
-      <c r="D19" s="539"/>
-      <c r="E19" s="539"/>
+      <c r="A19" s="551"/>
+      <c r="B19" s="551"/>
+      <c r="C19" s="551"/>
+      <c r="D19" s="551"/>
+      <c r="E19" s="551"/>
     </row>
     <row r="20" spans="1:13" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="K20" s="112"/>
@@ -11871,7 +11929,7 @@
       <c r="M21" s="112"/>
     </row>
     <row r="22" spans="1:13" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="H22" s="242"/>
+      <c r="H22" s="241"/>
     </row>
     <row r="23" spans="1:13" ht="12" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="24" spans="1:13" ht="12" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -11882,91 +11940,91 @@
     <row r="29" spans="1:13" ht="12" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="30" spans="1:13" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="31" spans="1:13" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="540" t="s">
+      <c r="A31" s="552" t="s">
         <v>93</v>
       </c>
-      <c r="B31" s="541"/>
-      <c r="C31" s="541"/>
-      <c r="D31" s="541"/>
-      <c r="E31" s="541"/>
-      <c r="F31" s="541"/>
-      <c r="G31" s="541"/>
-      <c r="H31" s="542"/>
+      <c r="B31" s="553"/>
+      <c r="C31" s="553"/>
+      <c r="D31" s="553"/>
+      <c r="E31" s="553"/>
+      <c r="F31" s="553"/>
+      <c r="G31" s="553"/>
+      <c r="H31" s="554"/>
       <c r="I31" s="89"/>
       <c r="J31" s="89"/>
     </row>
     <row r="32" spans="1:13" ht="36.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="243" t="s">
+      <c r="A32" s="242" t="s">
         <v>100</v>
       </c>
-      <c r="B32" s="244" t="s">
+      <c r="B32" s="243" t="s">
         <v>101</v>
       </c>
-      <c r="C32" s="245" t="s">
+      <c r="C32" s="244" t="s">
         <v>102</v>
       </c>
-      <c r="D32" s="245" t="s">
+      <c r="D32" s="244" t="s">
         <v>103</v>
       </c>
-      <c r="E32" s="245" t="s">
+      <c r="E32" s="244" t="s">
         <v>104</v>
       </c>
-      <c r="F32" s="245" t="s">
+      <c r="F32" s="244" t="s">
         <v>175</v>
       </c>
-      <c r="G32" s="245" t="s">
+      <c r="G32" s="244" t="s">
         <v>105</v>
       </c>
-      <c r="H32" s="246" t="s">
+      <c r="H32" s="245" t="s">
         <v>176</v>
       </c>
       <c r="I32" s="89"/>
       <c r="J32" s="89"/>
     </row>
     <row r="33" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="247" t="s">
+      <c r="A33" s="246" t="s">
         <v>106</v>
       </c>
-      <c r="B33" s="248" t="e">
+      <c r="B33" s="247" t="e">
         <f>+B34/(B38-B42)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="C33" s="249"/>
-      <c r="D33" s="250"/>
-      <c r="E33" s="250"/>
-      <c r="F33" s="250"/>
-      <c r="G33" s="250"/>
-      <c r="H33" s="251"/>
+      <c r="C33" s="248"/>
+      <c r="D33" s="249"/>
+      <c r="E33" s="249"/>
+      <c r="F33" s="249"/>
+      <c r="G33" s="249"/>
+      <c r="H33" s="250"/>
       <c r="I33" s="89"/>
       <c r="J33" s="89"/>
     </row>
     <row r="34" spans="1:15" s="90" customFormat="1" ht="32.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="252" t="str">
+      <c r="A34" s="251" t="str">
         <f>+DATOS!B17</f>
         <v>Masa de la muestra secada al horno constante</v>
       </c>
-      <c r="B34" s="253">
+      <c r="B34" s="252">
         <f>+DATOS!I17</f>
         <v>0</v>
       </c>
-      <c r="C34" s="254" t="s">
+      <c r="C34" s="253" t="s">
         <v>107</v>
       </c>
-      <c r="D34" s="255" t="s">
+      <c r="D34" s="254" t="s">
         <v>47</v>
       </c>
-      <c r="E34" s="256" t="s">
+      <c r="E34" s="255" t="s">
         <v>107</v>
       </c>
-      <c r="F34" s="257">
+      <c r="F34" s="256">
         <f>SQRT((F35*F35)+(F36*F36)+(F37*F37))</f>
         <v>0.28867591401662412</v>
       </c>
-      <c r="G34" s="258" t="e">
+      <c r="G34" s="257" t="e">
         <f>1/(B38-B42)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="H34" s="235" t="e">
+      <c r="H34" s="234" t="e">
         <f>G34*F34</f>
         <v>#DIV/0!</v>
       </c>
@@ -11975,25 +12033,25 @@
       </c>
     </row>
     <row r="35" spans="1:15" s="90" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="259" t="s">
+      <c r="A35" s="258" t="s">
         <v>108</v>
       </c>
-      <c r="B35" s="248"/>
-      <c r="C35" s="249">
+      <c r="B35" s="247"/>
+      <c r="C35" s="248">
         <f>Balanza!$G$23</f>
         <v>0</v>
       </c>
-      <c r="D35" s="260" t="s">
+      <c r="D35" s="259" t="s">
         <v>47</v>
       </c>
-      <c r="E35" s="261" t="s">
+      <c r="E35" s="260" t="s">
         <v>109</v>
       </c>
-      <c r="F35" s="249">
+      <c r="F35" s="248">
         <f>+C35</f>
         <v>0</v>
       </c>
-      <c r="G35" s="262" t="s">
+      <c r="G35" s="261" t="s">
         <v>107</v>
       </c>
       <c r="H35" s="91" t="s">
@@ -12002,38 +12060,38 @@
       <c r="I35" s="89"/>
     </row>
     <row r="36" spans="1:15" s="90" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="259" t="s">
+      <c r="A36" s="258" t="s">
         <v>110</v>
       </c>
-      <c r="B36" s="248"/>
-      <c r="C36" s="249">
+      <c r="B36" s="247"/>
+      <c r="C36" s="248">
         <f>2*(SQRT(Balanza!$C$8+Balanza!$D$8*(POWER(B34,2))))</f>
         <v>1.3416407864998738E-3</v>
       </c>
-      <c r="D36" s="260" t="s">
+      <c r="D36" s="259" t="s">
         <v>47</v>
       </c>
-      <c r="E36" s="261" t="s">
+      <c r="E36" s="260" t="s">
         <v>111</v>
       </c>
-      <c r="F36" s="249">
+      <c r="F36" s="248">
         <f>+C36/2</f>
         <v>6.7082039324993688E-4</v>
       </c>
-      <c r="G36" s="262" t="s">
+      <c r="G36" s="261" t="s">
         <v>107</v>
       </c>
       <c r="H36" s="91" t="s">
         <v>107</v>
       </c>
       <c r="I36" s="89"/>
-      <c r="J36" s="200"/>
-      <c r="K36" s="201"/>
-      <c r="L36" s="202" t="s">
+      <c r="J36" s="199"/>
+      <c r="K36" s="200"/>
+      <c r="L36" s="201" t="s">
         <v>112</v>
       </c>
-      <c r="M36" s="203"/>
-      <c r="N36" s="191" t="s">
+      <c r="M36" s="202"/>
+      <c r="N36" s="190" t="s">
         <v>101</v>
       </c>
       <c r="O36" s="105" t="s">
@@ -12041,39 +12099,39 @@
       </c>
     </row>
     <row r="37" spans="1:15" s="90" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="259" t="s">
+      <c r="A37" s="258" t="s">
         <v>114</v>
       </c>
-      <c r="B37" s="248"/>
-      <c r="C37" s="249">
+      <c r="B37" s="247"/>
+      <c r="C37" s="248">
         <f>Balanza!$C$10</f>
         <v>1</v>
       </c>
-      <c r="D37" s="260" t="s">
+      <c r="D37" s="259" t="s">
         <v>47</v>
       </c>
-      <c r="E37" s="263" t="s">
+      <c r="E37" s="262" t="s">
         <v>115</v>
       </c>
-      <c r="F37" s="249">
+      <c r="F37" s="248">
         <f>C37/SQRT(3)/2</f>
         <v>0.28867513459481292</v>
       </c>
-      <c r="G37" s="262" t="s">
+      <c r="G37" s="261" t="s">
         <v>107</v>
       </c>
       <c r="H37" s="91" t="s">
         <v>107</v>
       </c>
       <c r="I37" s="89"/>
-      <c r="J37" s="210"/>
-      <c r="K37" s="211"/>
-      <c r="L37" s="211"/>
-      <c r="M37" s="212" t="str">
+      <c r="J37" s="209"/>
+      <c r="K37" s="210"/>
+      <c r="L37" s="210"/>
+      <c r="M37" s="211" t="str">
         <f>A34</f>
         <v>Masa de la muestra secada al horno constante</v>
       </c>
-      <c r="N37" s="198" t="e">
+      <c r="N37" s="197" t="e">
         <f>H34</f>
         <v>#DIV/0!</v>
       </c>
@@ -12083,26 +12141,26 @@
       </c>
     </row>
     <row r="38" spans="1:15" s="90" customFormat="1" ht="39" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="252" t="str">
+      <c r="A38" s="251" t="str">
         <f>+DATOS!B18</f>
         <v>Masa de la muestra de ensayo de superficie seca saturada en el aire</v>
       </c>
-      <c r="B38" s="253">
+      <c r="B38" s="252">
         <f>+DATOS!I18</f>
         <v>0</v>
       </c>
-      <c r="C38" s="254"/>
-      <c r="D38" s="264" t="s">
+      <c r="C38" s="253"/>
+      <c r="D38" s="263" t="s">
         <v>47</v>
       </c>
-      <c r="E38" s="265" t="s">
+      <c r="E38" s="264" t="s">
         <v>107</v>
       </c>
-      <c r="F38" s="257">
+      <c r="F38" s="256">
         <f>SQRT((F39*F39)+(F40*F40)+(F41*F41))</f>
         <v>0.28867591401662412</v>
       </c>
-      <c r="G38" s="255" t="e">
+      <c r="G38" s="254" t="e">
         <f>+B34/(B38-B42)^2</f>
         <v>#DIV/0!</v>
       </c>
@@ -12113,12 +12171,12 @@
       <c r="I38" s="89" t="s">
         <v>48</v>
       </c>
-      <c r="J38" s="204"/>
-      <c r="M38" s="205" t="str">
+      <c r="J38" s="203"/>
+      <c r="M38" s="204" t="str">
         <f>A38</f>
         <v>Masa de la muestra de ensayo de superficie seca saturada en el aire</v>
       </c>
-      <c r="N38" s="198" t="e">
+      <c r="N38" s="197" t="e">
         <f>H38</f>
         <v>#DIV/0!</v>
       </c>
@@ -12128,39 +12186,39 @@
       </c>
     </row>
     <row r="39" spans="1:15" s="90" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="259" t="s">
+      <c r="A39" s="258" t="s">
         <v>108</v>
       </c>
-      <c r="B39" s="248"/>
-      <c r="C39" s="249">
+      <c r="B39" s="247"/>
+      <c r="C39" s="248">
         <f>Balanza!$G$24</f>
         <v>0</v>
       </c>
-      <c r="D39" s="260" t="s">
+      <c r="D39" s="259" t="s">
         <v>47</v>
       </c>
-      <c r="E39" s="261" t="s">
+      <c r="E39" s="260" t="s">
         <v>109</v>
       </c>
-      <c r="F39" s="249">
+      <c r="F39" s="248">
         <f>+C39</f>
         <v>0</v>
       </c>
-      <c r="G39" s="262" t="s">
+      <c r="G39" s="261" t="s">
         <v>107</v>
       </c>
       <c r="H39" s="91" t="s">
         <v>107</v>
       </c>
       <c r="I39" s="89"/>
-      <c r="J39" s="210"/>
-      <c r="K39" s="211"/>
-      <c r="L39" s="211"/>
-      <c r="M39" s="212" t="str">
+      <c r="J39" s="209"/>
+      <c r="K39" s="210"/>
+      <c r="L39" s="210"/>
+      <c r="M39" s="211" t="str">
         <f>A42</f>
         <v>Masa aparente de la muestra de prueba sumergida en agua</v>
       </c>
-      <c r="N39" s="198" t="e">
+      <c r="N39" s="197" t="e">
         <f>+H42</f>
         <v>#DIV/0!</v>
       </c>
@@ -12170,39 +12228,39 @@
       </c>
     </row>
     <row r="40" spans="1:15" s="90" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="259" t="s">
+      <c r="A40" s="258" t="s">
         <v>110</v>
       </c>
-      <c r="B40" s="248"/>
-      <c r="C40" s="249">
+      <c r="B40" s="247"/>
+      <c r="C40" s="248">
         <f>2*(SQRT(Balanza!$C$8+Balanza!$D$8*(POWER(B38,2))))</f>
         <v>1.3416407864998738E-3</v>
       </c>
-      <c r="D40" s="260" t="s">
+      <c r="D40" s="259" t="s">
         <v>47</v>
       </c>
-      <c r="E40" s="261" t="s">
+      <c r="E40" s="260" t="s">
         <v>111</v>
       </c>
-      <c r="F40" s="249">
+      <c r="F40" s="248">
         <f>+C40/2</f>
         <v>6.7082039324993688E-4</v>
       </c>
-      <c r="G40" s="262" t="s">
+      <c r="G40" s="261" t="s">
         <v>107</v>
       </c>
       <c r="H40" s="91" t="s">
         <v>107</v>
       </c>
       <c r="I40" s="89"/>
-      <c r="J40" s="210"/>
-      <c r="K40" s="211"/>
-      <c r="L40" s="213"/>
-      <c r="M40" s="212" t="str">
+      <c r="J40" s="209"/>
+      <c r="K40" s="210"/>
+      <c r="L40" s="212"/>
+      <c r="M40" s="211" t="str">
         <f>A46</f>
         <v>factor de presición OD</v>
       </c>
-      <c r="N40" s="198">
+      <c r="N40" s="197">
         <f>H46</f>
         <v>4.1539806879132444E-3</v>
       </c>
@@ -12212,38 +12270,38 @@
       </c>
     </row>
     <row r="41" spans="1:15" s="90" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="259" t="s">
+      <c r="A41" s="258" t="s">
         <v>114</v>
       </c>
-      <c r="B41" s="248"/>
-      <c r="C41" s="249">
+      <c r="B41" s="247"/>
+      <c r="C41" s="248">
         <f>Balanza!$C$10</f>
         <v>1</v>
       </c>
-      <c r="D41" s="260" t="s">
+      <c r="D41" s="259" t="s">
         <v>47</v>
       </c>
-      <c r="E41" s="263" t="s">
+      <c r="E41" s="262" t="s">
         <v>115</v>
       </c>
-      <c r="F41" s="249">
+      <c r="F41" s="248">
         <f>C41/SQRT(3)/2</f>
         <v>0.28867513459481292</v>
       </c>
-      <c r="G41" s="262" t="s">
+      <c r="G41" s="261" t="s">
         <v>107</v>
       </c>
       <c r="H41" s="91" t="s">
         <v>107</v>
       </c>
       <c r="I41" s="89"/>
-      <c r="J41" s="206"/>
-      <c r="K41" s="207"/>
-      <c r="L41" s="208" t="s">
+      <c r="J41" s="205"/>
+      <c r="K41" s="206"/>
+      <c r="L41" s="207" t="s">
         <v>170</v>
       </c>
-      <c r="M41" s="209"/>
-      <c r="N41" s="199" t="e">
+      <c r="M41" s="208"/>
+      <c r="N41" s="198" t="e">
         <f>SUM(N37:N40)</f>
         <v>#DIV/0!</v>
       </c>
@@ -12253,26 +12311,26 @@
       </c>
     </row>
     <row r="42" spans="1:15" s="90" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="252" t="str">
+      <c r="A42" s="251" t="str">
         <f>+DATOS!B19</f>
         <v>Masa aparente de la muestra de prueba sumergida en agua</v>
       </c>
-      <c r="B42" s="253">
+      <c r="B42" s="252">
         <f>+DATOS!I19</f>
         <v>0</v>
       </c>
-      <c r="C42" s="254"/>
-      <c r="D42" s="264" t="s">
+      <c r="C42" s="253"/>
+      <c r="D42" s="263" t="s">
         <v>47</v>
       </c>
-      <c r="E42" s="265" t="s">
+      <c r="E42" s="264" t="s">
         <v>107</v>
       </c>
-      <c r="F42" s="257">
+      <c r="F42" s="256">
         <f>SQRT((F43*F43)+(F44*F44)+(F45*F45))</f>
         <v>0.28867591401662412</v>
       </c>
-      <c r="G42" s="255" t="e">
+      <c r="G42" s="254" t="e">
         <f>+B34/(B38-B42)^2</f>
         <v>#DIV/0!</v>
       </c>
@@ -12286,25 +12344,25 @@
       <c r="J42" s="89"/>
     </row>
     <row r="43" spans="1:15" s="90" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="259" t="s">
+      <c r="A43" s="258" t="s">
         <v>108</v>
       </c>
-      <c r="B43" s="248"/>
-      <c r="C43" s="249">
+      <c r="B43" s="247"/>
+      <c r="C43" s="248">
         <f>Balanza!$G$25</f>
         <v>0</v>
       </c>
-      <c r="D43" s="260" t="s">
+      <c r="D43" s="259" t="s">
         <v>47</v>
       </c>
-      <c r="E43" s="261" t="s">
+      <c r="E43" s="260" t="s">
         <v>109</v>
       </c>
-      <c r="F43" s="249">
+      <c r="F43" s="248">
         <f>+C43</f>
         <v>0</v>
       </c>
-      <c r="G43" s="262" t="s">
+      <c r="G43" s="261" t="s">
         <v>107</v>
       </c>
       <c r="H43" s="91" t="s">
@@ -12314,25 +12372,25 @@
       <c r="J43" s="89"/>
     </row>
     <row r="44" spans="1:15" s="90" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="259" t="s">
+      <c r="A44" s="258" t="s">
         <v>110</v>
       </c>
-      <c r="B44" s="248"/>
-      <c r="C44" s="249">
+      <c r="B44" s="247"/>
+      <c r="C44" s="248">
         <f>2*(SQRT(Balanza!$C$8+Balanza!$D$8*(POWER(B42,2))))</f>
         <v>1.3416407864998738E-3</v>
       </c>
-      <c r="D44" s="260" t="s">
+      <c r="D44" s="259" t="s">
         <v>47</v>
       </c>
-      <c r="E44" s="261" t="s">
+      <c r="E44" s="260" t="s">
         <v>111</v>
       </c>
-      <c r="F44" s="249">
+      <c r="F44" s="248">
         <f>+C44/2</f>
         <v>6.7082039324993688E-4</v>
       </c>
-      <c r="G44" s="262" t="s">
+      <c r="G44" s="261" t="s">
         <v>107</v>
       </c>
       <c r="H44" s="91" t="s">
@@ -12342,25 +12400,25 @@
       <c r="J44" s="89"/>
     </row>
     <row r="45" spans="1:15" s="90" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="259" t="s">
+      <c r="A45" s="258" t="s">
         <v>114</v>
       </c>
-      <c r="B45" s="248"/>
-      <c r="C45" s="249">
+      <c r="B45" s="247"/>
+      <c r="C45" s="248">
         <f>Balanza!$C$10</f>
         <v>1</v>
       </c>
-      <c r="D45" s="260" t="s">
+      <c r="D45" s="259" t="s">
         <v>47</v>
       </c>
-      <c r="E45" s="263" t="s">
+      <c r="E45" s="262" t="s">
         <v>115</v>
       </c>
-      <c r="F45" s="249">
+      <c r="F45" s="248">
         <f>C45/SQRT(3)/2</f>
         <v>0.28867513459481292</v>
       </c>
-      <c r="G45" s="262" t="s">
+      <c r="G45" s="261" t="s">
         <v>107</v>
       </c>
       <c r="H45" s="91" t="s">
@@ -12368,33 +12426,33 @@
       </c>
       <c r="I45" s="89"/>
       <c r="J45" s="89"/>
-      <c r="L45" s="234" t="s">
+      <c r="L45" s="233" t="s">
         <v>171</v>
       </c>
     </row>
     <row r="46" spans="1:15" s="90" customFormat="1" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="266" t="s">
+      <c r="A46" s="265" t="s">
         <v>116</v>
       </c>
-      <c r="B46" s="254">
+      <c r="B46" s="253">
         <f>+Precision!B8</f>
         <v>4.1539806879132444E-3</v>
       </c>
-      <c r="C46" s="254"/>
-      <c r="D46" s="267" t="s">
+      <c r="C46" s="253"/>
+      <c r="D46" s="266" t="s">
         <v>20</v>
       </c>
-      <c r="E46" s="268" t="s">
+      <c r="E46" s="267" t="s">
         <v>117</v>
       </c>
-      <c r="F46" s="269">
+      <c r="F46" s="268">
         <f>+B46</f>
         <v>4.1539806879132444E-3</v>
       </c>
-      <c r="G46" s="270">
+      <c r="G46" s="269">
         <v>1</v>
       </c>
-      <c r="H46" s="271">
+      <c r="H46" s="270">
         <f>+G46*F46</f>
         <v>4.1539806879132444E-3</v>
       </c>
@@ -12402,15 +12460,15 @@
       <c r="J46" s="89"/>
     </row>
     <row r="47" spans="1:15" s="90" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="272"/>
-      <c r="B47" s="273"/>
-      <c r="C47" s="274" t="s">
+      <c r="A47" s="271"/>
+      <c r="B47" s="272"/>
+      <c r="C47" s="273" t="s">
         <v>118</v>
       </c>
-      <c r="D47" s="275"/>
-      <c r="E47" s="273"/>
-      <c r="F47" s="273"/>
-      <c r="G47" s="273"/>
+      <c r="D47" s="274"/>
+      <c r="E47" s="272"/>
+      <c r="F47" s="272"/>
+      <c r="G47" s="272"/>
       <c r="H47" s="129" t="e">
         <f>SQRT((H34*H34+(H38*H38)+(H42*H42)+(H46*H46)))</f>
         <v>#DIV/0!</v>
@@ -12419,15 +12477,15 @@
       <c r="J47" s="89"/>
     </row>
     <row r="48" spans="1:15" s="90" customFormat="1" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="276"/>
-      <c r="B48" s="277"/>
-      <c r="C48" s="278" t="s">
+      <c r="A48" s="275"/>
+      <c r="B48" s="276"/>
+      <c r="C48" s="277" t="s">
         <v>180</v>
       </c>
-      <c r="D48" s="279"/>
-      <c r="E48" s="277"/>
-      <c r="F48" s="277"/>
-      <c r="G48" s="277"/>
+      <c r="D48" s="278"/>
+      <c r="E48" s="276"/>
+      <c r="F48" s="276"/>
+      <c r="G48" s="276"/>
       <c r="H48" s="130" t="e">
         <f>H47*2</f>
         <v>#DIV/0!</v>
@@ -12448,57 +12506,57 @@
       <c r="J49" s="89"/>
     </row>
     <row r="50" spans="1:20" s="90" customFormat="1" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="280"/>
-      <c r="B50" s="281"/>
-      <c r="C50" s="281"/>
-      <c r="D50" s="282" t="s">
+      <c r="A50" s="279"/>
+      <c r="B50" s="280"/>
+      <c r="C50" s="280"/>
+      <c r="D50" s="281" t="s">
         <v>94</v>
       </c>
-      <c r="E50" s="283"/>
-      <c r="F50" s="284"/>
-      <c r="G50" s="285"/>
-      <c r="H50" s="286"/>
+      <c r="E50" s="282"/>
+      <c r="F50" s="283"/>
+      <c r="G50" s="284"/>
+      <c r="H50" s="285"/>
       <c r="I50" s="89"/>
       <c r="J50" s="89"/>
     </row>
     <row r="51" spans="1:20" s="90" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A51" s="287" t="s">
+      <c r="A51" s="286" t="s">
         <v>119</v>
       </c>
-      <c r="B51" s="248" t="e">
+      <c r="B51" s="247" t="e">
         <f>+B52/(B52-B56)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="C51" s="249"/>
-      <c r="D51" s="288"/>
-      <c r="E51" s="289"/>
-      <c r="F51" s="290"/>
-      <c r="G51" s="291"/>
+      <c r="C51" s="248"/>
+      <c r="D51" s="287"/>
+      <c r="E51" s="288"/>
+      <c r="F51" s="289"/>
+      <c r="G51" s="290"/>
       <c r="H51" s="93"/>
       <c r="I51" s="89"/>
       <c r="J51" s="89"/>
     </row>
     <row r="52" spans="1:20" s="90" customFormat="1" ht="33.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A52" s="252" t="str">
+      <c r="A52" s="251" t="str">
         <f>+DATOS!B18</f>
         <v>Masa de la muestra de ensayo de superficie seca saturada en el aire</v>
       </c>
-      <c r="B52" s="253">
+      <c r="B52" s="252">
         <f>+DATOS!I18</f>
         <v>0</v>
       </c>
-      <c r="C52" s="254"/>
-      <c r="D52" s="264" t="s">
+      <c r="C52" s="253"/>
+      <c r="D52" s="263" t="s">
         <v>47</v>
       </c>
-      <c r="E52" s="265" t="s">
+      <c r="E52" s="264" t="s">
         <v>107</v>
       </c>
-      <c r="F52" s="257">
+      <c r="F52" s="256">
         <f>SQRT((F53*F53)+(F54*F54)+(F55*F55))</f>
         <v>0.28867591401662412</v>
       </c>
-      <c r="G52" s="255" t="e">
+      <c r="G52" s="254" t="e">
         <f>+B56/(B52-B56)^2</f>
         <v>#DIV/0!</v>
       </c>
@@ -12509,90 +12567,90 @@
       <c r="I52" s="89" t="s">
         <v>48</v>
       </c>
-      <c r="J52" s="210"/>
-      <c r="K52" s="211"/>
-      <c r="L52" s="220" t="s">
+      <c r="J52" s="209"/>
+      <c r="K52" s="210"/>
+      <c r="L52" s="219" t="s">
         <v>112</v>
       </c>
-      <c r="M52" s="220"/>
+      <c r="M52" s="219"/>
       <c r="N52" s="76" t="s">
         <v>101</v>
       </c>
-      <c r="O52" s="221" t="s">
+      <c r="O52" s="220" t="s">
         <v>113</v>
       </c>
     </row>
     <row r="53" spans="1:20" s="90" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A53" s="259" t="s">
+      <c r="A53" s="258" t="s">
         <v>108</v>
       </c>
-      <c r="B53" s="248"/>
-      <c r="C53" s="249">
+      <c r="B53" s="247"/>
+      <c r="C53" s="248">
         <f>+Balanza!G24</f>
         <v>0</v>
       </c>
-      <c r="D53" s="260" t="s">
+      <c r="D53" s="259" t="s">
         <v>47</v>
       </c>
-      <c r="E53" s="261" t="s">
+      <c r="E53" s="260" t="s">
         <v>109</v>
       </c>
-      <c r="F53" s="249">
+      <c r="F53" s="248">
         <f>+C53</f>
         <v>0</v>
       </c>
-      <c r="G53" s="262" t="s">
+      <c r="G53" s="261" t="s">
         <v>107</v>
       </c>
       <c r="H53" s="91" t="s">
         <v>107</v>
       </c>
       <c r="I53" s="89"/>
-      <c r="J53" s="204"/>
-      <c r="L53" s="216"/>
-      <c r="M53" s="233" t="str">
+      <c r="J53" s="203"/>
+      <c r="L53" s="215"/>
+      <c r="M53" s="232" t="str">
         <f>+A52</f>
         <v>Masa de la muestra de ensayo de superficie seca saturada en el aire</v>
       </c>
-      <c r="N53" s="222" t="e">
+      <c r="N53" s="221" t="e">
         <f>+H52</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="O53" s="218" t="e">
+      <c r="O53" s="217" t="e">
         <f>N53*100/$N$56</f>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="54" spans="1:20" s="90" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="259" t="s">
+      <c r="A54" s="258" t="s">
         <v>110</v>
       </c>
-      <c r="B54" s="248"/>
-      <c r="C54" s="249">
+      <c r="B54" s="247"/>
+      <c r="C54" s="248">
         <f>2*(SQRT(Balanza!$C$8+Balanza!$D$8*(POWER(B52,2))))</f>
         <v>1.3416407864998738E-3</v>
       </c>
-      <c r="D54" s="260" t="s">
+      <c r="D54" s="259" t="s">
         <v>47</v>
       </c>
-      <c r="E54" s="261" t="s">
+      <c r="E54" s="260" t="s">
         <v>111</v>
       </c>
-      <c r="F54" s="249">
+      <c r="F54" s="248">
         <f>+C54/2</f>
         <v>6.7082039324993688E-4</v>
       </c>
-      <c r="G54" s="262" t="s">
+      <c r="G54" s="261" t="s">
         <v>107</v>
       </c>
       <c r="H54" s="91" t="s">
         <v>107</v>
       </c>
       <c r="I54" s="89"/>
-      <c r="J54" s="210"/>
-      <c r="K54" s="211"/>
-      <c r="L54" s="225"/>
-      <c r="M54" s="226" t="str">
+      <c r="J54" s="209"/>
+      <c r="K54" s="210"/>
+      <c r="L54" s="224"/>
+      <c r="M54" s="225" t="str">
         <f>+A56</f>
         <v>Masa aparente de la muestra de prueba sumergida en agua</v>
       </c>
@@ -12600,47 +12658,47 @@
         <f>+H56</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="O54" s="224" t="e">
+      <c r="O54" s="223" t="e">
         <f>N54*100/$N$56</f>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="55" spans="1:20" s="90" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A55" s="259" t="s">
+      <c r="A55" s="258" t="s">
         <v>114</v>
       </c>
-      <c r="B55" s="248"/>
-      <c r="C55" s="249">
+      <c r="B55" s="247"/>
+      <c r="C55" s="248">
         <f>Balanza!$C$10</f>
         <v>1</v>
       </c>
-      <c r="D55" s="260" t="s">
+      <c r="D55" s="259" t="s">
         <v>47</v>
       </c>
-      <c r="E55" s="263" t="s">
+      <c r="E55" s="262" t="s">
         <v>115</v>
       </c>
-      <c r="F55" s="249">
+      <c r="F55" s="248">
         <f>C55/SQRT(3)/2</f>
         <v>0.28867513459481292</v>
       </c>
-      <c r="G55" s="262" t="s">
+      <c r="G55" s="261" t="s">
         <v>107</v>
       </c>
       <c r="H55" s="91" t="s">
         <v>107</v>
       </c>
       <c r="I55" s="89"/>
-      <c r="J55" s="204"/>
+      <c r="J55" s="203"/>
       <c r="M55" s="6" t="str">
         <f>+A60</f>
         <v>factor de presición SSD</v>
       </c>
-      <c r="N55" s="222">
+      <c r="N55" s="221">
         <f>+H60</f>
         <v>4.2163702135577961E-3</v>
       </c>
-      <c r="O55" s="218" t="e">
+      <c r="O55" s="217" t="e">
         <f>N55*100/$N$56</f>
         <v>#DIV/0!</v>
       </c>
@@ -12648,26 +12706,26 @@
       <c r="T55" s="89"/>
     </row>
     <row r="56" spans="1:20" s="90" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A56" s="252" t="str">
+      <c r="A56" s="251" t="str">
         <f>+DATOS!B19</f>
         <v>Masa aparente de la muestra de prueba sumergida en agua</v>
       </c>
-      <c r="B56" s="253">
+      <c r="B56" s="252">
         <f>+DATOS!I19</f>
         <v>0</v>
       </c>
-      <c r="C56" s="254"/>
-      <c r="D56" s="264" t="s">
+      <c r="C56" s="253"/>
+      <c r="D56" s="263" t="s">
         <v>47</v>
       </c>
-      <c r="E56" s="265" t="s">
+      <c r="E56" s="264" t="s">
         <v>107</v>
       </c>
-      <c r="F56" s="257">
+      <c r="F56" s="256">
         <f>SQRT((F57*F57)+(F58*F58)+(F59*F59))</f>
         <v>0.28867591401662412</v>
       </c>
-      <c r="G56" s="255" t="e">
+      <c r="G56" s="254" t="e">
         <f>+B52/(B52-B56)^2</f>
         <v>#DIV/0!</v>
       </c>
@@ -12678,17 +12736,17 @@
       <c r="I56" s="89" t="s">
         <v>50</v>
       </c>
-      <c r="J56" s="210"/>
-      <c r="K56" s="211"/>
-      <c r="L56" s="213" t="s">
+      <c r="J56" s="209"/>
+      <c r="K56" s="210"/>
+      <c r="L56" s="212" t="s">
         <v>170</v>
       </c>
-      <c r="M56" s="215"/>
+      <c r="M56" s="214"/>
       <c r="N56" s="94" t="e">
         <f>SUM(N53:N55)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="O56" s="224" t="e">
+      <c r="O56" s="223" t="e">
         <f>N56*100/$N$56</f>
         <v>#DIV/0!</v>
       </c>
@@ -12696,25 +12754,25 @@
       <c r="T56" s="89"/>
     </row>
     <row r="57" spans="1:20" s="90" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A57" s="259" t="s">
+      <c r="A57" s="258" t="s">
         <v>108</v>
       </c>
-      <c r="B57" s="248"/>
-      <c r="C57" s="249">
+      <c r="B57" s="247"/>
+      <c r="C57" s="248">
         <f>Balanza!$G$25</f>
         <v>0</v>
       </c>
-      <c r="D57" s="260" t="s">
+      <c r="D57" s="259" t="s">
         <v>47</v>
       </c>
-      <c r="E57" s="261" t="s">
+      <c r="E57" s="260" t="s">
         <v>109</v>
       </c>
-      <c r="F57" s="249">
+      <c r="F57" s="248">
         <f>+C57</f>
         <v>0</v>
       </c>
-      <c r="G57" s="262" t="s">
+      <c r="G57" s="261" t="s">
         <v>107</v>
       </c>
       <c r="H57" s="91" t="s">
@@ -12725,25 +12783,25 @@
       <c r="T57" s="89"/>
     </row>
     <row r="58" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="259" t="s">
+      <c r="A58" s="258" t="s">
         <v>110</v>
       </c>
-      <c r="B58" s="248"/>
-      <c r="C58" s="249">
+      <c r="B58" s="247"/>
+      <c r="C58" s="248">
         <f>2*(SQRT(Balanza!$C$8+Balanza!$D$8*(POWER(B56,2))))</f>
         <v>1.3416407864998738E-3</v>
       </c>
-      <c r="D58" s="260" t="s">
+      <c r="D58" s="259" t="s">
         <v>47</v>
       </c>
-      <c r="E58" s="261" t="s">
+      <c r="E58" s="260" t="s">
         <v>111</v>
       </c>
-      <c r="F58" s="249">
+      <c r="F58" s="248">
         <f>+C58/2</f>
         <v>6.7082039324993688E-4</v>
       </c>
-      <c r="G58" s="262" t="s">
+      <c r="G58" s="261" t="s">
         <v>107</v>
       </c>
       <c r="H58" s="91" t="s">
@@ -12761,25 +12819,25 @@
       <c r="T58" s="89"/>
     </row>
     <row r="59" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="259" t="s">
+      <c r="A59" s="258" t="s">
         <v>114</v>
       </c>
-      <c r="B59" s="248"/>
-      <c r="C59" s="249">
+      <c r="B59" s="247"/>
+      <c r="C59" s="248">
         <f>Balanza!$C$10</f>
         <v>1</v>
       </c>
-      <c r="D59" s="260" t="s">
+      <c r="D59" s="259" t="s">
         <v>47</v>
       </c>
-      <c r="E59" s="263" t="s">
+      <c r="E59" s="262" t="s">
         <v>115</v>
       </c>
-      <c r="F59" s="249">
+      <c r="F59" s="248">
         <f>C59/SQRT(3)/2</f>
         <v>0.28867513459481292</v>
       </c>
-      <c r="G59" s="262" t="s">
+      <c r="G59" s="261" t="s">
         <v>107</v>
       </c>
       <c r="H59" s="91" t="s">
@@ -12798,28 +12856,28 @@
       <c r="T59" s="89"/>
     </row>
     <row r="60" spans="1:20" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="292" t="s">
+      <c r="A60" s="291" t="s">
         <v>120</v>
       </c>
-      <c r="B60" s="254">
+      <c r="B60" s="253">
         <f>+Precision!G8</f>
         <v>4.2163702135577961E-3</v>
       </c>
-      <c r="C60" s="254"/>
-      <c r="D60" s="293" t="s">
+      <c r="C60" s="253"/>
+      <c r="D60" s="292" t="s">
         <v>20</v>
       </c>
-      <c r="E60" s="294" t="s">
+      <c r="E60" s="293" t="s">
         <v>117</v>
       </c>
-      <c r="F60" s="295">
+      <c r="F60" s="294">
         <f>+B60</f>
         <v>4.2163702135577961E-3</v>
       </c>
-      <c r="G60" s="296">
+      <c r="G60" s="295">
         <v>1</v>
       </c>
-      <c r="H60" s="236">
+      <c r="H60" s="235">
         <f>+G60*F60</f>
         <v>4.2163702135577961E-3</v>
       </c>
@@ -12836,15 +12894,15 @@
       <c r="T60" s="89"/>
     </row>
     <row r="61" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="272"/>
-      <c r="B61" s="273"/>
-      <c r="C61" s="274" t="s">
+      <c r="A61" s="271"/>
+      <c r="B61" s="272"/>
+      <c r="C61" s="273" t="s">
         <v>121</v>
       </c>
-      <c r="D61" s="275"/>
-      <c r="E61" s="273"/>
-      <c r="F61" s="273"/>
-      <c r="G61" s="273"/>
+      <c r="D61" s="274"/>
+      <c r="E61" s="272"/>
+      <c r="F61" s="272"/>
+      <c r="G61" s="272"/>
       <c r="H61" s="129" t="e">
         <f>SQRT(((H52*H52)+(H56*H56)+(H60*H60)))</f>
         <v>#DIV/0!</v>
@@ -12862,15 +12920,15 @@
       <c r="T61" s="89"/>
     </row>
     <row r="62" spans="1:20" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A62" s="276"/>
-      <c r="B62" s="277"/>
-      <c r="C62" s="278" t="s">
+      <c r="A62" s="275"/>
+      <c r="B62" s="276"/>
+      <c r="C62" s="277" t="s">
         <v>181</v>
       </c>
-      <c r="D62" s="279"/>
-      <c r="E62" s="277"/>
-      <c r="F62" s="277"/>
-      <c r="G62" s="277"/>
+      <c r="D62" s="278"/>
+      <c r="E62" s="276"/>
+      <c r="F62" s="276"/>
+      <c r="G62" s="276"/>
       <c r="H62" s="130" t="e">
         <f>H61*2</f>
         <v>#DIV/0!</v>
@@ -12895,16 +12953,16 @@
       <c r="R63" s="89"/>
     </row>
     <row r="64" spans="1:20" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A64" s="280"/>
-      <c r="B64" s="281"/>
-      <c r="C64" s="281"/>
-      <c r="D64" s="282" t="s">
+      <c r="A64" s="279"/>
+      <c r="B64" s="280"/>
+      <c r="C64" s="280"/>
+      <c r="D64" s="281" t="s">
         <v>95</v>
       </c>
-      <c r="E64" s="283"/>
-      <c r="F64" s="284"/>
-      <c r="G64" s="285"/>
-      <c r="H64" s="286"/>
+      <c r="E64" s="282"/>
+      <c r="F64" s="283"/>
+      <c r="G64" s="284"/>
+      <c r="H64" s="285"/>
       <c r="K64" s="89"/>
       <c r="L64" s="89"/>
       <c r="M64" s="89"/>
@@ -12915,18 +12973,18 @@
       <c r="R64" s="89"/>
     </row>
     <row r="65" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A65" s="287" t="s">
+      <c r="A65" s="286" t="s">
         <v>122</v>
       </c>
-      <c r="B65" s="248" t="e">
+      <c r="B65" s="247" t="e">
         <f>+B66/(B66-B70)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="C65" s="249"/>
-      <c r="D65" s="288"/>
-      <c r="E65" s="289"/>
-      <c r="F65" s="290"/>
-      <c r="G65" s="291"/>
+      <c r="C65" s="248"/>
+      <c r="D65" s="287"/>
+      <c r="E65" s="288"/>
+      <c r="F65" s="289"/>
+      <c r="G65" s="290"/>
       <c r="H65" s="93"/>
       <c r="K65" s="89"/>
       <c r="L65" s="89"/>
@@ -12938,32 +12996,32 @@
       <c r="R65" s="89"/>
     </row>
     <row r="66" spans="1:18" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A66" s="252" t="str">
+      <c r="A66" s="251" t="str">
         <f>+DATOS!B17</f>
         <v>Masa de la muestra secada al horno constante</v>
       </c>
-      <c r="B66" s="253">
+      <c r="B66" s="252">
         <f>+DATOS!I17</f>
         <v>0</v>
       </c>
-      <c r="C66" s="254" t="s">
+      <c r="C66" s="253" t="s">
         <v>107</v>
       </c>
-      <c r="D66" s="255" t="s">
+      <c r="D66" s="254" t="s">
         <v>47</v>
       </c>
-      <c r="E66" s="256" t="s">
+      <c r="E66" s="255" t="s">
         <v>107</v>
       </c>
-      <c r="F66" s="257">
+      <c r="F66" s="256">
         <f>SQRT((F67*F67)+(F68*F68)+(F69*F69))</f>
         <v>0.28867591401662412</v>
       </c>
-      <c r="G66" s="258" t="e">
+      <c r="G66" s="257" t="e">
         <f>+B70/(B66-B70)^2</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="H66" s="235" t="e">
+      <c r="H66" s="234" t="e">
         <f>ABS(G66*F66)</f>
         <v>#DIV/0!</v>
       </c>
@@ -12980,25 +13038,25 @@
       <c r="R66" s="89"/>
     </row>
     <row r="67" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A67" s="259" t="s">
+      <c r="A67" s="258" t="s">
         <v>108</v>
       </c>
-      <c r="B67" s="248"/>
-      <c r="C67" s="249">
+      <c r="B67" s="247"/>
+      <c r="C67" s="248">
         <f>Balanza!$G$23</f>
         <v>0</v>
       </c>
-      <c r="D67" s="260" t="s">
+      <c r="D67" s="259" t="s">
         <v>47</v>
       </c>
-      <c r="E67" s="261" t="s">
+      <c r="E67" s="260" t="s">
         <v>109</v>
       </c>
-      <c r="F67" s="249">
+      <c r="F67" s="248">
         <f>+C67</f>
         <v>0</v>
       </c>
-      <c r="G67" s="262" t="s">
+      <c r="G67" s="261" t="s">
         <v>107</v>
       </c>
       <c r="H67" s="91" t="s">
@@ -13015,25 +13073,25 @@
       <c r="R67" s="89"/>
     </row>
     <row r="68" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A68" s="259" t="s">
+      <c r="A68" s="258" t="s">
         <v>110</v>
       </c>
-      <c r="B68" s="248"/>
-      <c r="C68" s="249">
+      <c r="B68" s="247"/>
+      <c r="C68" s="248">
         <f>2*(SQRT(Balanza!$C$8+Balanza!$D$8*(POWER(B66,2))))</f>
         <v>1.3416407864998738E-3</v>
       </c>
-      <c r="D68" s="260" t="s">
+      <c r="D68" s="259" t="s">
         <v>47</v>
       </c>
-      <c r="E68" s="261" t="s">
+      <c r="E68" s="260" t="s">
         <v>111</v>
       </c>
-      <c r="F68" s="249">
+      <c r="F68" s="248">
         <f>+C68/2</f>
         <v>6.7082039324993688E-4</v>
       </c>
-      <c r="G68" s="262" t="s">
+      <c r="G68" s="261" t="s">
         <v>107</v>
       </c>
       <c r="H68" s="91" t="s">
@@ -13041,15 +13099,15 @@
       </c>
       <c r="I68" s="89"/>
       <c r="J68" s="87"/>
-      <c r="K68" s="227"/>
-      <c r="L68" s="526" t="s">
+      <c r="K68" s="226"/>
+      <c r="L68" s="538" t="s">
         <v>112</v>
       </c>
-      <c r="M68" s="526"/>
-      <c r="N68" s="231" t="s">
+      <c r="M68" s="538"/>
+      <c r="N68" s="230" t="s">
         <v>101</v>
       </c>
-      <c r="O68" s="217" t="s">
+      <c r="O68" s="216" t="s">
         <v>113</v>
       </c>
       <c r="P68" s="89"/>
@@ -13057,25 +13115,25 @@
       <c r="R68" s="89"/>
     </row>
     <row r="69" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="259" t="s">
+      <c r="A69" s="258" t="s">
         <v>114</v>
       </c>
-      <c r="B69" s="248"/>
-      <c r="C69" s="249">
+      <c r="B69" s="247"/>
+      <c r="C69" s="248">
         <f>Balanza!$C$10</f>
         <v>1</v>
       </c>
-      <c r="D69" s="260" t="s">
+      <c r="D69" s="259" t="s">
         <v>47</v>
       </c>
-      <c r="E69" s="263" t="s">
+      <c r="E69" s="262" t="s">
         <v>115</v>
       </c>
-      <c r="F69" s="249">
+      <c r="F69" s="248">
         <f>C69/SQRT(3)/2</f>
         <v>0.28867513459481292</v>
       </c>
-      <c r="G69" s="262" t="s">
+      <c r="G69" s="261" t="s">
         <v>107</v>
       </c>
       <c r="H69" s="91" t="s">
@@ -13085,7 +13143,7 @@
       <c r="J69" s="97"/>
       <c r="K69" s="3"/>
       <c r="L69" s="3"/>
-      <c r="M69" s="226" t="str">
+      <c r="M69" s="225" t="str">
         <f>+A66</f>
         <v>Masa de la muestra secada al horno constante</v>
       </c>
@@ -13093,7 +13151,7 @@
         <f>+H66</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="O69" s="224" t="e">
+      <c r="O69" s="223" t="e">
         <f>N69*100/$N$72</f>
         <v>#DIV/0!</v>
       </c>
@@ -13102,26 +13160,26 @@
       <c r="R69" s="89"/>
     </row>
     <row r="70" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A70" s="252" t="str">
+      <c r="A70" s="251" t="str">
         <f>+DATOS!B19</f>
         <v>Masa aparente de la muestra de prueba sumergida en agua</v>
       </c>
-      <c r="B70" s="253">
+      <c r="B70" s="252">
         <f>+DATOS!I19</f>
         <v>0</v>
       </c>
-      <c r="C70" s="254"/>
-      <c r="D70" s="264" t="s">
+      <c r="C70" s="253"/>
+      <c r="D70" s="263" t="s">
         <v>47</v>
       </c>
-      <c r="E70" s="265" t="s">
+      <c r="E70" s="264" t="s">
         <v>107</v>
       </c>
-      <c r="F70" s="257">
+      <c r="F70" s="256">
         <f>SQRT((F71*F71)+(F72*F72)+(F73*F73))</f>
         <v>0.28867591401662412</v>
       </c>
-      <c r="G70" s="255" t="e">
+      <c r="G70" s="254" t="e">
         <f>+B66/(B66-B70)^2</f>
         <v>#DIV/0!</v>
       </c>
@@ -13132,16 +13190,16 @@
       <c r="I70" s="89" t="s">
         <v>50</v>
       </c>
-      <c r="J70" s="228"/>
+      <c r="J70" s="227"/>
       <c r="M70" s="6" t="str">
         <f>+A70</f>
         <v>Masa aparente de la muestra de prueba sumergida en agua</v>
       </c>
-      <c r="N70" s="222" t="e">
+      <c r="N70" s="221" t="e">
         <f>+H70</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="O70" s="224" t="e">
+      <c r="O70" s="223" t="e">
         <f t="shared" ref="O70:O72" si="0">N70*100/$N$72</f>
         <v>#DIV/0!</v>
       </c>
@@ -13150,25 +13208,25 @@
       <c r="R70" s="89"/>
     </row>
     <row r="71" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A71" s="259" t="s">
+      <c r="A71" s="258" t="s">
         <v>108</v>
       </c>
-      <c r="B71" s="248"/>
-      <c r="C71" s="249">
+      <c r="B71" s="247"/>
+      <c r="C71" s="248">
         <f>Balanza!$G$25</f>
         <v>0</v>
       </c>
-      <c r="D71" s="260" t="s">
+      <c r="D71" s="259" t="s">
         <v>47</v>
       </c>
-      <c r="E71" s="261" t="s">
+      <c r="E71" s="260" t="s">
         <v>109</v>
       </c>
-      <c r="F71" s="249">
+      <c r="F71" s="248">
         <f>+C71</f>
         <v>0</v>
       </c>
-      <c r="G71" s="262" t="s">
+      <c r="G71" s="261" t="s">
         <v>107</v>
       </c>
       <c r="H71" s="91" t="s">
@@ -13178,7 +13236,7 @@
       <c r="J71" s="97"/>
       <c r="K71" s="3"/>
       <c r="L71" s="3"/>
-      <c r="M71" s="226" t="str">
+      <c r="M71" s="225" t="str">
         <f>+A74</f>
         <v>factor de presición DA</v>
       </c>
@@ -13186,7 +13244,7 @@
         <f>+H74</f>
         <v>4.4397197108725995E-3</v>
       </c>
-      <c r="O71" s="224" t="e">
+      <c r="O71" s="223" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
@@ -13195,25 +13253,25 @@
       <c r="R71" s="89"/>
     </row>
     <row r="72" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A72" s="259" t="s">
+      <c r="A72" s="258" t="s">
         <v>110</v>
       </c>
-      <c r="B72" s="248"/>
-      <c r="C72" s="249">
+      <c r="B72" s="247"/>
+      <c r="C72" s="248">
         <f>2*(SQRT(Balanza!$C$8+Balanza!$D$8*(POWER(B70,2))))</f>
         <v>1.3416407864998738E-3</v>
       </c>
-      <c r="D72" s="260" t="s">
+      <c r="D72" s="259" t="s">
         <v>47</v>
       </c>
-      <c r="E72" s="261" t="s">
+      <c r="E72" s="260" t="s">
         <v>111</v>
       </c>
-      <c r="F72" s="249">
+      <c r="F72" s="248">
         <f>+C72/2</f>
         <v>6.7082039324993688E-4</v>
       </c>
-      <c r="G72" s="262" t="s">
+      <c r="G72" s="261" t="s">
         <v>107</v>
       </c>
       <c r="H72" s="91" t="s">
@@ -13221,16 +13279,16 @@
       </c>
       <c r="I72" s="89"/>
       <c r="J72" s="88"/>
-      <c r="K72" s="229"/>
-      <c r="L72" s="208" t="s">
+      <c r="K72" s="228"/>
+      <c r="L72" s="207" t="s">
         <v>170</v>
       </c>
-      <c r="M72" s="230"/>
-      <c r="N72" s="223" t="e">
+      <c r="M72" s="229"/>
+      <c r="N72" s="222" t="e">
         <f>SUM(N69:N71)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="O72" s="224" t="e">
+      <c r="O72" s="223" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
@@ -13239,25 +13297,25 @@
       <c r="R72" s="89"/>
     </row>
     <row r="73" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A73" s="259" t="s">
+      <c r="A73" s="258" t="s">
         <v>114</v>
       </c>
-      <c r="B73" s="248"/>
-      <c r="C73" s="249">
+      <c r="B73" s="247"/>
+      <c r="C73" s="248">
         <f>Balanza!$C$10</f>
         <v>1</v>
       </c>
-      <c r="D73" s="260" t="s">
+      <c r="D73" s="259" t="s">
         <v>47</v>
       </c>
-      <c r="E73" s="263" t="s">
+      <c r="E73" s="262" t="s">
         <v>115</v>
       </c>
-      <c r="F73" s="249">
+      <c r="F73" s="248">
         <f>C73/SQRT(3)/2</f>
         <v>0.28867513459481292</v>
       </c>
-      <c r="G73" s="262" t="s">
+      <c r="G73" s="261" t="s">
         <v>107</v>
       </c>
       <c r="H73" s="91" t="s">
@@ -13269,28 +13327,28 @@
       <c r="R73" s="89"/>
     </row>
     <row r="74" spans="1:18" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A74" s="292" t="s">
+      <c r="A74" s="291" t="s">
         <v>123</v>
       </c>
-      <c r="B74" s="254">
+      <c r="B74" s="253">
         <f>+Precision!L8</f>
         <v>4.4397197108725995E-3</v>
       </c>
-      <c r="C74" s="254"/>
-      <c r="D74" s="293" t="s">
+      <c r="C74" s="253"/>
+      <c r="D74" s="292" t="s">
         <v>20</v>
       </c>
-      <c r="E74" s="294" t="s">
+      <c r="E74" s="293" t="s">
         <v>117</v>
       </c>
-      <c r="F74" s="295">
+      <c r="F74" s="294">
         <f>+B74</f>
         <v>4.4397197108725995E-3</v>
       </c>
-      <c r="G74" s="296">
+      <c r="G74" s="295">
         <v>1</v>
       </c>
-      <c r="H74" s="236">
+      <c r="H74" s="235">
         <f>+G74*F74</f>
         <v>4.4397197108725995E-3</v>
       </c>
@@ -13303,15 +13361,15 @@
       <c r="R74" s="89"/>
     </row>
     <row r="75" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A75" s="272"/>
-      <c r="B75" s="273"/>
-      <c r="C75" s="274" t="s">
+      <c r="A75" s="271"/>
+      <c r="B75" s="272"/>
+      <c r="C75" s="273" t="s">
         <v>124</v>
       </c>
-      <c r="D75" s="275"/>
-      <c r="E75" s="273"/>
-      <c r="F75" s="273"/>
-      <c r="G75" s="273"/>
+      <c r="D75" s="274"/>
+      <c r="E75" s="272"/>
+      <c r="F75" s="272"/>
+      <c r="G75" s="272"/>
       <c r="H75" s="129" t="e">
         <f>SQRT(((H66*H66)+(H70*H70)+(H74*H74)))</f>
         <v>#DIV/0!</v>
@@ -13325,15 +13383,15 @@
       <c r="R75" s="89"/>
     </row>
     <row r="76" spans="1:18" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A76" s="276"/>
-      <c r="B76" s="277"/>
-      <c r="C76" s="278" t="s">
+      <c r="A76" s="275"/>
+      <c r="B76" s="276"/>
+      <c r="C76" s="277" t="s">
         <v>182</v>
       </c>
-      <c r="D76" s="279"/>
-      <c r="E76" s="277"/>
-      <c r="F76" s="277"/>
-      <c r="G76" s="277"/>
+      <c r="D76" s="278"/>
+      <c r="E76" s="276"/>
+      <c r="F76" s="276"/>
+      <c r="G76" s="276"/>
       <c r="H76" s="130" t="e">
         <f>H75*2</f>
         <v>#DIV/0!</v>
@@ -13354,16 +13412,16 @@
       <c r="R77" s="89"/>
     </row>
     <row r="78" spans="1:18" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A78" s="280"/>
-      <c r="B78" s="281"/>
-      <c r="C78" s="281"/>
-      <c r="D78" s="282" t="s">
+      <c r="A78" s="279"/>
+      <c r="B78" s="280"/>
+      <c r="C78" s="280"/>
+      <c r="D78" s="281" t="s">
         <v>125</v>
       </c>
-      <c r="E78" s="283"/>
-      <c r="F78" s="284"/>
-      <c r="G78" s="285"/>
-      <c r="H78" s="286"/>
+      <c r="E78" s="282"/>
+      <c r="F78" s="283"/>
+      <c r="G78" s="284"/>
+      <c r="H78" s="285"/>
       <c r="K78" s="89"/>
       <c r="N78" s="89"/>
       <c r="O78" s="89"/>
@@ -13372,29 +13430,29 @@
       <c r="R78" s="89"/>
     </row>
     <row r="79" spans="1:18" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A79" s="287" t="s">
+      <c r="A79" s="286" t="s">
         <v>126</v>
       </c>
-      <c r="B79" s="297" t="e">
+      <c r="B79" s="296" t="e">
         <f>100*((B84-B80)/B80)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="C79" s="249"/>
-      <c r="D79" s="288"/>
-      <c r="E79" s="289"/>
-      <c r="F79" s="290"/>
-      <c r="G79" s="291"/>
+      <c r="C79" s="248"/>
+      <c r="D79" s="287"/>
+      <c r="E79" s="288"/>
+      <c r="F79" s="289"/>
+      <c r="G79" s="290"/>
       <c r="H79" s="93"/>
       <c r="J79" s="87"/>
-      <c r="K79" s="227"/>
-      <c r="L79" s="526" t="s">
+      <c r="K79" s="226"/>
+      <c r="L79" s="538" t="s">
         <v>112</v>
       </c>
-      <c r="M79" s="526"/>
-      <c r="N79" s="231" t="s">
+      <c r="M79" s="538"/>
+      <c r="N79" s="230" t="s">
         <v>101</v>
       </c>
-      <c r="O79" s="217" t="s">
+      <c r="O79" s="216" t="s">
         <v>113</v>
       </c>
       <c r="P79" s="89"/>
@@ -13402,26 +13460,26 @@
       <c r="R79" s="89"/>
     </row>
     <row r="80" spans="1:18" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="252" t="str">
+      <c r="A80" s="251" t="str">
         <f>+DATOS!B17</f>
         <v>Masa de la muestra secada al horno constante</v>
       </c>
-      <c r="B80" s="253">
+      <c r="B80" s="252">
         <f>+DATOS!I17</f>
         <v>0</v>
       </c>
-      <c r="C80" s="254"/>
-      <c r="D80" s="264" t="s">
+      <c r="C80" s="253"/>
+      <c r="D80" s="263" t="s">
         <v>47</v>
       </c>
-      <c r="E80" s="265" t="s">
+      <c r="E80" s="264" t="s">
         <v>107</v>
       </c>
-      <c r="F80" s="257">
+      <c r="F80" s="256">
         <f>SQRT((F81*F81)+(F82*F82)+(F83*F83))</f>
         <v>0.28867591401662412</v>
       </c>
-      <c r="G80" s="255" t="e">
+      <c r="G80" s="254" t="e">
         <f>+(B84/B80^2)*100</f>
         <v>#DIV/0!</v>
       </c>
@@ -13435,7 +13493,7 @@
       <c r="J80" s="97"/>
       <c r="K80" s="3"/>
       <c r="L80" s="3"/>
-      <c r="M80" s="226" t="str">
+      <c r="M80" s="225" t="str">
         <f>+A80</f>
         <v>Masa de la muestra secada al horno constante</v>
       </c>
@@ -13443,7 +13501,7 @@
         <f>+H80</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="O80" s="224" t="e">
+      <c r="O80" s="223" t="e">
         <f>N80*100/$N$83</f>
         <v>#DIV/0!</v>
       </c>
@@ -13452,41 +13510,41 @@
       <c r="R80" s="89"/>
     </row>
     <row r="81" spans="1:18" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A81" s="259" t="s">
+      <c r="A81" s="258" t="s">
         <v>108</v>
       </c>
-      <c r="B81" s="248"/>
-      <c r="C81" s="249">
+      <c r="B81" s="247"/>
+      <c r="C81" s="248">
         <f>+Balanza!G23</f>
         <v>0</v>
       </c>
-      <c r="D81" s="260" t="s">
+      <c r="D81" s="259" t="s">
         <v>47</v>
       </c>
-      <c r="E81" s="261" t="s">
+      <c r="E81" s="260" t="s">
         <v>109</v>
       </c>
-      <c r="F81" s="249">
+      <c r="F81" s="248">
         <f>+C81</f>
         <v>0</v>
       </c>
-      <c r="G81" s="262" t="s">
+      <c r="G81" s="261" t="s">
         <v>107</v>
       </c>
       <c r="H81" s="91" t="s">
         <v>107</v>
       </c>
       <c r="I81" s="89"/>
-      <c r="J81" s="228"/>
-      <c r="M81" s="233" t="str">
+      <c r="J81" s="227"/>
+      <c r="M81" s="232" t="str">
         <f>+A84</f>
         <v>Masa de la muestra de ensayo de superficie seca saturada en el aire</v>
       </c>
-      <c r="N81" s="222" t="e">
+      <c r="N81" s="221" t="e">
         <f>+H84</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="O81" s="218" t="e">
+      <c r="O81" s="217" t="e">
         <f>N81*100/$N$83</f>
         <v>#DIV/0!</v>
       </c>
@@ -13495,25 +13553,25 @@
       <c r="R81" s="89"/>
     </row>
     <row r="82" spans="1:18" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A82" s="259" t="s">
+      <c r="A82" s="258" t="s">
         <v>110</v>
       </c>
-      <c r="B82" s="248"/>
-      <c r="C82" s="249">
+      <c r="B82" s="247"/>
+      <c r="C82" s="248">
         <f>2*(SQRT(Balanza!$C$8+Balanza!$D$8*(POWER(B80,2))))</f>
         <v>1.3416407864998738E-3</v>
       </c>
-      <c r="D82" s="260" t="s">
+      <c r="D82" s="259" t="s">
         <v>47</v>
       </c>
-      <c r="E82" s="261" t="s">
+      <c r="E82" s="260" t="s">
         <v>111</v>
       </c>
-      <c r="F82" s="249">
+      <c r="F82" s="248">
         <f>+C82/2</f>
         <v>6.7082039324993688E-4</v>
       </c>
-      <c r="G82" s="262" t="s">
+      <c r="G82" s="261" t="s">
         <v>107</v>
       </c>
       <c r="H82" s="91" t="s">
@@ -13523,7 +13581,7 @@
       <c r="J82" s="97"/>
       <c r="K82" s="3"/>
       <c r="L82" s="3"/>
-      <c r="M82" s="226" t="str">
+      <c r="M82" s="225" t="str">
         <f>+A88</f>
         <v>factor de presición ABS</v>
       </c>
@@ -13531,7 +13589,7 @@
         <f>+H88</f>
         <v>2.923088169119166E-2</v>
       </c>
-      <c r="O82" s="224" t="e">
+      <c r="O82" s="223" t="e">
         <f>N82*100/$N$83</f>
         <v>#DIV/0!</v>
       </c>
@@ -13540,25 +13598,25 @@
       <c r="R82" s="89"/>
     </row>
     <row r="83" spans="1:18" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A83" s="259" t="s">
+      <c r="A83" s="258" t="s">
         <v>114</v>
       </c>
-      <c r="B83" s="248"/>
-      <c r="C83" s="249">
+      <c r="B83" s="247"/>
+      <c r="C83" s="248">
         <f>Balanza!$C$10</f>
         <v>1</v>
       </c>
-      <c r="D83" s="260" t="s">
+      <c r="D83" s="259" t="s">
         <v>47</v>
       </c>
-      <c r="E83" s="263" t="s">
+      <c r="E83" s="262" t="s">
         <v>115</v>
       </c>
-      <c r="F83" s="249">
+      <c r="F83" s="248">
         <f>C83/SQRT(3)/2</f>
         <v>0.28867513459481292</v>
       </c>
-      <c r="G83" s="262" t="s">
+      <c r="G83" s="261" t="s">
         <v>107</v>
       </c>
       <c r="H83" s="91" t="s">
@@ -13566,16 +13624,16 @@
       </c>
       <c r="I83" s="89"/>
       <c r="J83" s="88"/>
-      <c r="K83" s="229"/>
-      <c r="L83" s="208" t="s">
+      <c r="K83" s="228"/>
+      <c r="L83" s="207" t="s">
         <v>170</v>
       </c>
-      <c r="M83" s="229"/>
-      <c r="N83" s="232" t="e">
+      <c r="M83" s="228"/>
+      <c r="N83" s="231" t="e">
         <f>SUM(N80:N82)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="O83" s="219" t="e">
+      <c r="O83" s="218" t="e">
         <f>N83*100/$N$83</f>
         <v>#DIV/0!</v>
       </c>
@@ -13584,32 +13642,32 @@
       <c r="R83" s="89"/>
     </row>
     <row r="84" spans="1:18" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A84" s="252" t="str">
+      <c r="A84" s="251" t="str">
         <f>+DATOS!B18</f>
         <v>Masa de la muestra de ensayo de superficie seca saturada en el aire</v>
       </c>
-      <c r="B84" s="253">
+      <c r="B84" s="252">
         <f>+DATOS!I18</f>
         <v>0</v>
       </c>
-      <c r="C84" s="254" t="s">
+      <c r="C84" s="253" t="s">
         <v>107</v>
       </c>
-      <c r="D84" s="255" t="s">
+      <c r="D84" s="254" t="s">
         <v>47</v>
       </c>
-      <c r="E84" s="256" t="s">
+      <c r="E84" s="255" t="s">
         <v>107</v>
       </c>
-      <c r="F84" s="257">
+      <c r="F84" s="256">
         <f>SQRT((F85*F85)+(F86*F86)+(F87*F87))</f>
         <v>0.28867591401662412</v>
       </c>
-      <c r="G84" s="258" t="e">
+      <c r="G84" s="257" t="e">
         <f>100/B80</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="H84" s="235" t="e">
+      <c r="H84" s="234" t="e">
         <f>G84*F84</f>
         <v>#DIV/0!</v>
       </c>
@@ -13626,31 +13684,31 @@
       <c r="R84" s="89"/>
     </row>
     <row r="85" spans="1:18" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A85" s="259" t="s">
+      <c r="A85" s="258" t="s">
         <v>108</v>
       </c>
-      <c r="B85" s="249"/>
-      <c r="C85" s="249">
+      <c r="B85" s="248"/>
+      <c r="C85" s="248">
         <f>+Balanza!G24</f>
         <v>0</v>
       </c>
-      <c r="D85" s="260" t="s">
+      <c r="D85" s="259" t="s">
         <v>47</v>
       </c>
-      <c r="E85" s="261" t="s">
+      <c r="E85" s="260" t="s">
         <v>109</v>
       </c>
-      <c r="F85" s="249">
+      <c r="F85" s="248">
         <f>+C85</f>
         <v>0</v>
       </c>
-      <c r="G85" s="262" t="s">
+      <c r="G85" s="261" t="s">
         <v>107</v>
       </c>
       <c r="H85" s="91" t="s">
         <v>107</v>
       </c>
-      <c r="I85" s="192"/>
+      <c r="I85" s="191"/>
       <c r="K85" s="6"/>
       <c r="L85" s="7"/>
       <c r="N85" s="89"/>
@@ -13660,31 +13718,31 @@
       <c r="R85" s="89"/>
     </row>
     <row r="86" spans="1:18" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A86" s="259" t="s">
+      <c r="A86" s="258" t="s">
         <v>110</v>
       </c>
-      <c r="B86" s="249"/>
-      <c r="C86" s="249">
+      <c r="B86" s="248"/>
+      <c r="C86" s="248">
         <f>2*(SQRT(Balanza!$C$8+Balanza!$D$8*(POWER(B84,2))))</f>
         <v>1.3416407864998738E-3</v>
       </c>
-      <c r="D86" s="260" t="s">
+      <c r="D86" s="259" t="s">
         <v>47</v>
       </c>
-      <c r="E86" s="261" t="s">
+      <c r="E86" s="260" t="s">
         <v>111</v>
       </c>
-      <c r="F86" s="249">
+      <c r="F86" s="248">
         <f>+C86/2</f>
         <v>6.7082039324993688E-4</v>
       </c>
-      <c r="G86" s="262" t="s">
+      <c r="G86" s="261" t="s">
         <v>107</v>
       </c>
       <c r="H86" s="91" t="s">
         <v>107</v>
       </c>
-      <c r="I86" s="192"/>
+      <c r="I86" s="191"/>
       <c r="K86" s="89"/>
       <c r="N86" s="89"/>
       <c r="O86" s="89"/>
@@ -13693,31 +13751,31 @@
       <c r="R86" s="89"/>
     </row>
     <row r="87" spans="1:18" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A87" s="259" t="s">
+      <c r="A87" s="258" t="s">
         <v>114</v>
       </c>
-      <c r="B87" s="249"/>
-      <c r="C87" s="249">
+      <c r="B87" s="248"/>
+      <c r="C87" s="248">
         <f>Balanza!$C$10</f>
         <v>1</v>
       </c>
-      <c r="D87" s="260" t="s">
+      <c r="D87" s="259" t="s">
         <v>47</v>
       </c>
-      <c r="E87" s="263" t="s">
+      <c r="E87" s="262" t="s">
         <v>115</v>
       </c>
-      <c r="F87" s="249">
+      <c r="F87" s="248">
         <f>C87/SQRT(3)/2</f>
         <v>0.28867513459481292</v>
       </c>
-      <c r="G87" s="262" t="s">
+      <c r="G87" s="261" t="s">
         <v>107</v>
       </c>
       <c r="H87" s="91" t="s">
         <v>107</v>
       </c>
-      <c r="I87" s="192"/>
+      <c r="I87" s="191"/>
       <c r="K87" s="89"/>
       <c r="N87" s="89"/>
       <c r="O87" s="89"/>
@@ -13726,32 +13784,32 @@
       <c r="R87" s="89"/>
     </row>
     <row r="88" spans="1:18" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A88" s="292" t="s">
+      <c r="A88" s="291" t="s">
         <v>127</v>
       </c>
-      <c r="B88" s="254">
+      <c r="B88" s="253">
         <f>+Precision!Q8</f>
         <v>2.923088169119166E-2</v>
       </c>
-      <c r="C88" s="254"/>
-      <c r="D88" s="293" t="s">
+      <c r="C88" s="253"/>
+      <c r="D88" s="292" t="s">
         <v>24</v>
       </c>
-      <c r="E88" s="294" t="s">
+      <c r="E88" s="293" t="s">
         <v>117</v>
       </c>
-      <c r="F88" s="295">
+      <c r="F88" s="294">
         <f>+B88</f>
         <v>2.923088169119166E-2</v>
       </c>
-      <c r="G88" s="296">
+      <c r="G88" s="295">
         <v>1</v>
       </c>
-      <c r="H88" s="236">
+      <c r="H88" s="235">
         <f>+G88*F88</f>
         <v>2.923088169119166E-2</v>
       </c>
-      <c r="I88" s="193"/>
+      <c r="I88" s="192"/>
       <c r="K88" s="89"/>
       <c r="N88" s="89"/>
       <c r="O88" s="89"/>
@@ -13760,15 +13818,15 @@
       <c r="R88" s="89"/>
     </row>
     <row r="89" spans="1:18" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A89" s="272"/>
-      <c r="B89" s="273"/>
-      <c r="C89" s="274" t="s">
+      <c r="A89" s="271"/>
+      <c r="B89" s="272"/>
+      <c r="C89" s="273" t="s">
         <v>128</v>
       </c>
-      <c r="D89" s="275"/>
-      <c r="E89" s="273"/>
-      <c r="F89" s="273"/>
-      <c r="G89" s="273"/>
+      <c r="D89" s="274"/>
+      <c r="E89" s="272"/>
+      <c r="F89" s="272"/>
+      <c r="G89" s="272"/>
       <c r="H89" s="129" t="e">
         <f>SQRT((H84*H84)+(H80*H80)+(H88*H88))</f>
         <v>#DIV/0!</v>
@@ -13781,15 +13839,15 @@
       <c r="R89" s="89"/>
     </row>
     <row r="90" spans="1:18" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A90" s="276"/>
-      <c r="B90" s="277"/>
-      <c r="C90" s="278" t="s">
+      <c r="A90" s="275"/>
+      <c r="B90" s="276"/>
+      <c r="C90" s="277" t="s">
         <v>182</v>
       </c>
-      <c r="D90" s="279"/>
-      <c r="E90" s="277"/>
-      <c r="F90" s="277"/>
-      <c r="G90" s="279" t="s">
+      <c r="D90" s="278"/>
+      <c r="E90" s="276"/>
+      <c r="F90" s="276"/>
+      <c r="G90" s="278" t="s">
         <v>24</v>
       </c>
       <c r="H90" s="130" t="e">
@@ -13822,22 +13880,22 @@
       <c r="R92" s="89"/>
     </row>
     <row r="93" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A93" s="549" t="s">
+      <c r="A93" s="407" t="s">
         <v>238</v>
       </c>
-      <c r="B93" s="550" t="s">
+      <c r="B93" s="530" t="s">
         <v>239</v>
       </c>
-      <c r="C93" s="551"/>
-      <c r="D93" s="552"/>
-      <c r="E93" s="553" t="s">
+      <c r="C93" s="531"/>
+      <c r="D93" s="408"/>
+      <c r="E93" s="532" t="s">
         <v>240</v>
       </c>
-      <c r="F93" s="553"/>
-      <c r="G93" s="554" t="s">
+      <c r="F93" s="532"/>
+      <c r="G93" s="533" t="s">
         <v>241</v>
       </c>
-      <c r="H93" s="555"/>
+      <c r="H93" s="534"/>
       <c r="K93" s="89"/>
       <c r="L93" s="89"/>
       <c r="M93" s="89"/>
@@ -13848,50 +13906,50 @@
       <c r="R93" s="89"/>
     </row>
     <row r="94" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A94" s="556"/>
-      <c r="B94" s="556"/>
-      <c r="C94" s="556"/>
-      <c r="D94" s="556"/>
-      <c r="E94" s="556"/>
-      <c r="F94" s="556"/>
-      <c r="G94" s="556"/>
-      <c r="H94" s="556"/>
+      <c r="A94" s="409"/>
+      <c r="B94" s="409"/>
+      <c r="C94" s="409"/>
+      <c r="D94" s="409"/>
+      <c r="E94" s="409"/>
+      <c r="F94" s="409"/>
+      <c r="G94" s="409"/>
+      <c r="H94" s="409"/>
     </row>
     <row r="95" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A95" s="557" t="s">
+      <c r="A95" s="410" t="s">
         <v>242</v>
       </c>
-      <c r="B95" s="558">
+      <c r="B95" s="535">
         <v>44869</v>
       </c>
-      <c r="C95" s="559"/>
-      <c r="D95" s="556"/>
-      <c r="E95" s="560" t="s">
+      <c r="C95" s="536"/>
+      <c r="D95" s="409"/>
+      <c r="E95" s="537" t="s">
         <v>243</v>
       </c>
-      <c r="F95" s="560"/>
-      <c r="G95" s="558">
+      <c r="F95" s="537"/>
+      <c r="G95" s="535">
         <v>44870</v>
       </c>
-      <c r="H95" s="559"/>
+      <c r="H95" s="536"/>
     </row>
     <row r="100" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H100" s="100"/>
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="L68:M68"/>
+    <mergeCell ref="L79:M79"/>
+    <mergeCell ref="A1:A4"/>
+    <mergeCell ref="B1:H4"/>
+    <mergeCell ref="A19:E19"/>
+    <mergeCell ref="A31:H31"/>
     <mergeCell ref="B93:C93"/>
     <mergeCell ref="E93:F93"/>
     <mergeCell ref="G93:H93"/>
     <mergeCell ref="B95:C95"/>
     <mergeCell ref="E95:F95"/>
     <mergeCell ref="G95:H95"/>
-    <mergeCell ref="L68:M68"/>
-    <mergeCell ref="L79:M79"/>
-    <mergeCell ref="A1:A4"/>
-    <mergeCell ref="B1:H4"/>
-    <mergeCell ref="A19:E19"/>
-    <mergeCell ref="A31:H31"/>
   </mergeCells>
   <pageMargins left="0.70866141732283472" right="0.31496062992125984" top="0.74803149606299213" bottom="0.55118110236220474" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" scale="70" orientation="portrait" r:id="rId1"/>
@@ -13975,45 +14033,45 @@
         <v>187</v>
       </c>
       <c r="C12" s="78"/>
-      <c r="D12" s="317">
+      <c r="D12" s="316">
         <v>46132</v>
       </c>
     </row>
     <row r="13" spans="2:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="196" t="s">
+      <c r="B13" s="195" t="s">
         <v>73</v>
       </c>
-      <c r="C13" s="197" t="s">
+      <c r="C13" s="196" t="s">
         <v>74</v>
       </c>
-      <c r="D13" s="314">
+      <c r="D13" s="313">
         <v>500</v>
       </c>
-      <c r="E13" s="314">
+      <c r="E13" s="313">
         <v>1000</v>
       </c>
-      <c r="F13" s="314">
+      <c r="F13" s="313">
         <v>5000</v>
       </c>
-      <c r="G13" s="314">
+      <c r="G13" s="313">
         <v>10000</v>
       </c>
-      <c r="H13" s="314">
+      <c r="H13" s="313">
         <v>15000</v>
       </c>
     </row>
     <row r="14" spans="2:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="318"/>
-      <c r="C14" s="313"/>
-      <c r="D14" s="315"/>
-      <c r="E14" s="315"/>
-      <c r="F14" s="315"/>
-      <c r="G14" s="315"/>
-      <c r="H14" s="315"/>
+      <c r="B14" s="317"/>
+      <c r="C14" s="312"/>
+      <c r="D14" s="314"/>
+      <c r="E14" s="314"/>
+      <c r="F14" s="314"/>
+      <c r="G14" s="314"/>
+      <c r="H14" s="314"/>
     </row>
     <row r="15" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B15" s="395"/>
-      <c r="C15" s="396"/>
+      <c r="B15" s="394"/>
+      <c r="C15" s="395"/>
     </row>
     <row r="16" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B16" s="80"/>
@@ -14091,18 +14149,18 @@
       <c r="I22" s="83"/>
     </row>
     <row r="23" spans="2:9" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B23" s="544" t="str">
+      <c r="B23" s="556" t="str">
         <f>+DATOS!B17</f>
         <v>Masa de la muestra secada al horno constante</v>
       </c>
-      <c r="C23" s="544"/>
-      <c r="D23" s="544"/>
-      <c r="E23" s="544"/>
-      <c r="F23" s="214">
+      <c r="C23" s="556"/>
+      <c r="D23" s="556"/>
+      <c r="E23" s="556"/>
+      <c r="F23" s="213">
         <f>+DATOS!I17</f>
         <v>0</v>
       </c>
-      <c r="G23" s="195">
+      <c r="G23" s="194">
         <f>IF(F23&lt;=$D$20,$D$21,IF(AND(F23&gt;$D$20,F23&lt;=$E$20),$E$21,IF(AND(F23&gt;$E$20,F23&lt;=$F$20),$F$21,IF(AND(F23&gt;$F$20,F23&lt;=$G$20),$G$21,IF(AND(F23&gt;$G$20,F23&lt;=$H$20),$H$21,$H$21)))))</f>
         <v>0</v>
       </c>
@@ -14111,18 +14169,18 @@
       </c>
     </row>
     <row r="24" spans="2:9" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B24" s="543" t="str">
+      <c r="B24" s="555" t="str">
         <f>+DATOS!B18</f>
         <v>Masa de la muestra de ensayo de superficie seca saturada en el aire</v>
       </c>
-      <c r="C24" s="543"/>
-      <c r="D24" s="543"/>
-      <c r="E24" s="543"/>
-      <c r="F24" s="214">
+      <c r="C24" s="555"/>
+      <c r="D24" s="555"/>
+      <c r="E24" s="555"/>
+      <c r="F24" s="213">
         <f>+DATOS!I18</f>
         <v>0</v>
       </c>
-      <c r="G24" s="195">
+      <c r="G24" s="194">
         <f t="shared" ref="G24:G25" si="0">IF(F24&lt;=$D$20,$D$21,IF(AND(F24&gt;$D$20,F24&lt;=$E$20),$E$21,IF(AND(F24&gt;$E$20,F24&lt;=$F$20),$F$21,IF(AND(F24&gt;$F$20,F24&lt;=$G$20),$G$21,IF(AND(F24&gt;$G$20,F24&lt;=$H$20),$H$21,$H$21)))))</f>
         <v>0</v>
       </c>
@@ -14131,18 +14189,18 @@
       </c>
     </row>
     <row r="25" spans="2:9" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B25" s="545" t="str">
+      <c r="B25" s="557" t="str">
         <f>+DATOS!B19</f>
         <v>Masa aparente de la muestra de prueba sumergida en agua</v>
       </c>
-      <c r="C25" s="545"/>
-      <c r="D25" s="545"/>
-      <c r="E25" s="545"/>
-      <c r="F25" s="214">
+      <c r="C25" s="557"/>
+      <c r="D25" s="557"/>
+      <c r="E25" s="557"/>
+      <c r="F25" s="213">
         <f>+DATOS!I19</f>
         <v>0</v>
       </c>
-      <c r="G25" s="195">
+      <c r="G25" s="194">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -15339,112 +15397,112 @@
       <c r="A5" s="125" t="s">
         <v>129</v>
       </c>
-      <c r="B5" s="399"/>
+      <c r="B5" s="398"/>
     </row>
     <row r="6" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="7" spans="1:25" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="548" t="s">
+      <c r="A7" s="560" t="s">
         <v>130</v>
       </c>
-      <c r="B7" s="548"/>
-      <c r="C7" s="548"/>
-      <c r="D7" s="548"/>
-      <c r="F7" s="548" t="s">
+      <c r="B7" s="560"/>
+      <c r="C7" s="560"/>
+      <c r="D7" s="560"/>
+      <c r="F7" s="560" t="s">
         <v>131</v>
       </c>
-      <c r="G7" s="548"/>
-      <c r="H7" s="548"/>
-      <c r="I7" s="548"/>
-      <c r="K7" s="548" t="s">
+      <c r="G7" s="560"/>
+      <c r="H7" s="560"/>
+      <c r="I7" s="560"/>
+      <c r="K7" s="560" t="s">
         <v>132</v>
       </c>
-      <c r="L7" s="548"/>
-      <c r="M7" s="548"/>
-      <c r="N7" s="548"/>
-      <c r="P7" s="548" t="s">
+      <c r="L7" s="560"/>
+      <c r="M7" s="560"/>
+      <c r="N7" s="560"/>
+      <c r="P7" s="560" t="s">
         <v>133</v>
       </c>
-      <c r="Q7" s="548"/>
-      <c r="R7" s="548"/>
-      <c r="S7" s="548"/>
+      <c r="Q7" s="560"/>
+      <c r="R7" s="560"/>
+      <c r="S7" s="560"/>
     </row>
     <row r="8" spans="1:25" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="398" t="s">
+      <c r="A8" s="397" t="s">
         <v>232</v>
       </c>
-      <c r="B8" s="546">
+      <c r="B8" s="558">
         <v>4.1539806879132444E-3</v>
       </c>
-      <c r="C8" s="546"/>
-      <c r="D8" s="546"/>
-      <c r="F8" s="398" t="s">
+      <c r="C8" s="558"/>
+      <c r="D8" s="558"/>
+      <c r="F8" s="397" t="s">
         <v>232</v>
       </c>
-      <c r="G8" s="546">
+      <c r="G8" s="558">
         <v>4.2163702135577961E-3</v>
       </c>
-      <c r="H8" s="546"/>
-      <c r="I8" s="546"/>
-      <c r="K8" s="398" t="s">
+      <c r="H8" s="558"/>
+      <c r="I8" s="558"/>
+      <c r="K8" s="397" t="s">
         <v>232</v>
       </c>
-      <c r="L8" s="546">
+      <c r="L8" s="558">
         <v>4.4397197108725995E-3</v>
       </c>
-      <c r="M8" s="546"/>
-      <c r="N8" s="546"/>
-      <c r="P8" s="398" t="s">
+      <c r="M8" s="558"/>
+      <c r="N8" s="558"/>
+      <c r="P8" s="397" t="s">
         <v>232</v>
       </c>
-      <c r="Q8" s="546">
+      <c r="Q8" s="558">
         <v>2.923088169119166E-2</v>
       </c>
-      <c r="R8" s="546"/>
-      <c r="S8" s="546"/>
-      <c r="U8" s="397"/>
-      <c r="V8" s="397"/>
-      <c r="W8" s="397"/>
-      <c r="X8" s="397"/>
-      <c r="Y8" s="397"/>
+      <c r="R8" s="558"/>
+      <c r="S8" s="558"/>
+      <c r="U8" s="396"/>
+      <c r="V8" s="396"/>
+      <c r="W8" s="396"/>
+      <c r="X8" s="396"/>
+      <c r="Y8" s="396"/>
     </row>
     <row r="9" spans="1:25" ht="30.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="398" t="s">
+      <c r="A9" s="397" t="s">
         <v>233</v>
       </c>
-      <c r="B9" s="546">
+      <c r="B9" s="558">
         <v>4.5030853616677231E-3</v>
       </c>
-      <c r="C9" s="546"/>
-      <c r="D9" s="546"/>
-      <c r="F9" s="398" t="s">
+      <c r="C9" s="558"/>
+      <c r="D9" s="558"/>
+      <c r="F9" s="397" t="s">
         <v>233</v>
       </c>
-      <c r="G9" s="546">
+      <c r="G9" s="558">
         <v>4.4762749065281162E-3</v>
       </c>
-      <c r="H9" s="546"/>
-      <c r="I9" s="546"/>
-      <c r="K9" s="398" t="s">
+      <c r="H9" s="558"/>
+      <c r="I9" s="558"/>
+      <c r="K9" s="397" t="s">
         <v>233</v>
       </c>
-      <c r="L9" s="546">
+      <c r="L9" s="558">
         <v>4.4855735834586023E-3</v>
       </c>
-      <c r="M9" s="546"/>
-      <c r="N9" s="546"/>
-      <c r="P9" s="398" t="s">
+      <c r="M9" s="558"/>
+      <c r="N9" s="558"/>
+      <c r="P9" s="397" t="s">
         <v>233</v>
       </c>
-      <c r="Q9" s="546">
+      <c r="Q9" s="558">
         <v>6.1433493096797555E-2</v>
       </c>
-      <c r="R9" s="546"/>
-      <c r="S9" s="546"/>
-      <c r="U9" s="397"/>
-      <c r="V9" s="397"/>
-      <c r="W9" s="397"/>
-      <c r="X9" s="397"/>
-      <c r="Y9" s="397"/>
+      <c r="R9" s="558"/>
+      <c r="S9" s="558"/>
+      <c r="U9" s="396"/>
+      <c r="V9" s="396"/>
+      <c r="W9" s="396"/>
+      <c r="X9" s="396"/>
+      <c r="Y9" s="396"/>
     </row>
     <row r="10" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="128"/>
@@ -15463,11 +15521,11 @@
       <c r="Q10" s="128"/>
       <c r="R10" s="128"/>
       <c r="S10" s="126"/>
-      <c r="U10" s="397"/>
-      <c r="V10" s="397"/>
-      <c r="W10" s="397"/>
-      <c r="X10" s="397"/>
-      <c r="Y10" s="397"/>
+      <c r="U10" s="396"/>
+      <c r="V10" s="396"/>
+      <c r="W10" s="396"/>
+      <c r="X10" s="396"/>
+      <c r="Y10" s="396"/>
     </row>
     <row r="11" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="128"/>
@@ -15486,41 +15544,41 @@
       <c r="Q11" s="128"/>
       <c r="R11" s="128"/>
       <c r="S11" s="126"/>
-      <c r="U11" s="397"/>
-      <c r="V11" s="397"/>
-      <c r="W11" s="397"/>
-      <c r="X11" s="397"/>
-      <c r="Y11" s="397"/>
+      <c r="U11" s="396"/>
+      <c r="V11" s="396"/>
+      <c r="W11" s="396"/>
+      <c r="X11" s="396"/>
+      <c r="Y11" s="396"/>
     </row>
     <row r="12" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="V12" s="547"/>
-      <c r="W12" s="547"/>
-      <c r="X12" s="547"/>
-      <c r="Y12" s="547"/>
+      <c r="V12" s="559"/>
+      <c r="W12" s="559"/>
+      <c r="X12" s="559"/>
+      <c r="Y12" s="559"/>
     </row>
     <row r="13" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="V13" s="547"/>
-      <c r="W13" s="547"/>
-      <c r="X13" s="547"/>
-      <c r="Y13" s="547"/>
+      <c r="V13" s="559"/>
+      <c r="W13" s="559"/>
+      <c r="X13" s="559"/>
+      <c r="Y13" s="559"/>
     </row>
     <row r="14" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="V14" s="547"/>
-      <c r="W14" s="547"/>
-      <c r="X14" s="547"/>
-      <c r="Y14" s="547"/>
+      <c r="V14" s="559"/>
+      <c r="W14" s="559"/>
+      <c r="X14" s="559"/>
+      <c r="Y14" s="559"/>
     </row>
     <row r="15" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="V15" s="547"/>
-      <c r="W15" s="547"/>
-      <c r="X15" s="547"/>
-      <c r="Y15" s="547"/>
+      <c r="V15" s="559"/>
+      <c r="W15" s="559"/>
+      <c r="X15" s="559"/>
+      <c r="Y15" s="559"/>
     </row>
     <row r="16" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="V16" s="547"/>
-      <c r="W16" s="547"/>
-      <c r="X16" s="547"/>
-      <c r="Y16" s="547"/>
+      <c r="V16" s="559"/>
+      <c r="W16" s="559"/>
+      <c r="X16" s="559"/>
+      <c r="Y16" s="559"/>
     </row>
   </sheetData>
   <mergeCells count="13">
